--- a/Testing/TestCases_KLCN_CoTuong (1).xlsx
+++ b/Testing/TestCases_KLCN_CoTuong (1).xlsx
@@ -2046,12 +2046,12 @@
       </c>
       <c r="I6" s="24" t="inlineStr">
         <is>
-          <t>Tài khoản thường (User) cố tình truy cập /Admin bị chặn và trả về 403 Forbidden / Access Denied.</t>
-        </is>
-      </c>
-      <c r="J6" s="62" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>HTTP 302 Found, chuyển hướng (Redirect) về /Auth/Login?ReturnUrl=%2FAdmin</t>
+        </is>
+      </c>
+      <c r="J6" s="63" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="K6" s="26" t="inlineStr">
@@ -2059,7 +2059,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="L6" s="35" t="n"/>
+      <c r="L6" s="35" t="inlineStr">
+        <is>
+          <t>BUG_003</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55.2" customHeight="1">
       <c r="A7" s="20" t="n">
@@ -2449,12 +2453,12 @@
       </c>
       <c r="I13" s="24" t="inlineStr">
         <is>
-          <t>Chỉnh sửa thông tin và xóa bài cờ thế trong CMS cập nhật chính xác.</t>
-        </is>
-      </c>
-      <c r="J13" s="62" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>HTTP 200 OK (hoặc redirect thành công) gây sai lệch trạng thái CMS</t>
+        </is>
+      </c>
+      <c r="J13" s="63" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="K13" s="27" t="inlineStr">
@@ -2462,7 +2466,11 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="L13" s="35" t="n"/>
+      <c r="L13" s="35" t="inlineStr">
+        <is>
+          <t>BUG_007</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="55.2" customHeight="1">
       <c r="A14" s="20" t="n">
@@ -3565,12 +3573,12 @@
       </c>
       <c r="C5" s="35" t="inlineStr">
         <is>
-          <t>Cho phép đăng ký mật khẩu yếu dưới 6 ký tự</t>
+          <t>Cho phép đăng ký mật khẩu yếu dưới 6 ký tự qua API</t>
         </is>
       </c>
       <c r="D5" s="35" t="inlineStr">
         <is>
-          <t>Xác thực &amp; Tài khoản</t>
+          <t>Xác thực &amp; Tài khoản (04_TC_Auth_Profile)</t>
         </is>
       </c>
       <c r="E5" s="35" t="inlineStr">
@@ -3585,17 +3593,19 @@
       </c>
       <c r="G5" s="35" t="inlineStr">
         <is>
-          <t>Gửi password 123</t>
+          <t>1. Gửi POST /api/auth/register
+2. Body chứa password = '123'
+3. Kiểm tra mã phản hồi</t>
         </is>
       </c>
       <c r="H5" s="35" t="inlineStr">
         <is>
-          <t>Chặn lỗi mật khẩu ngắn</t>
+          <t>HTTP 400 Bad Request, báo lỗi mật khẩu phải &gt;= 6 ký tự</t>
         </is>
       </c>
       <c r="I5" s="35" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 200 OK, hệ thống tạo tài khoản thành công với mật khẩu 3 ký tự</t>
         </is>
       </c>
       <c r="J5" s="35" t="inlineStr">
@@ -3608,7 +3618,7 @@
           <t>Tester độc lập</t>
         </is>
       </c>
-      <c r="L5" s="64" t="inlineStr">
+      <c r="L5" s="63" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -3623,16 +3633,58 @@
           <t>BUG_002</t>
         </is>
       </c>
-      <c r="C6" s="35" t="n"/>
-      <c r="D6" s="35" t="n"/>
-      <c r="E6" s="35" t="n"/>
-      <c r="F6" s="35" t="n"/>
-      <c r="G6" s="35" t="n"/>
-      <c r="H6" s="35" t="n"/>
-      <c r="I6" s="35" t="n"/>
-      <c r="J6" s="35" t="n"/>
-      <c r="K6" s="35" t="n"/>
-      <c r="L6" s="20" t="n"/>
+      <c r="C6" s="35" t="inlineStr">
+        <is>
+          <t>Thiếu Regex kiểm tra định dạng Email khi đăng ký tài khoản</t>
+        </is>
+      </c>
+      <c r="D6" s="35" t="inlineStr">
+        <is>
+          <t>Xác thực &amp; Tài khoản (04_TC_Auth_Profile)</t>
+        </is>
+      </c>
+      <c r="E6" s="35" t="inlineStr">
+        <is>
+          <t>P2 - Major</t>
+        </is>
+      </c>
+      <c r="F6" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G6" s="35" t="inlineStr">
+        <is>
+          <t>1. Gửi POST /api/auth/register
+2. Body email = 'not_an_email_at_all' (không có @ và domain)
+3. Bấm đăng ký</t>
+        </is>
+      </c>
+      <c r="H6" s="35" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request, từ chối định dạng email không hợp lệ</t>
+        </is>
+      </c>
+      <c r="I6" s="35" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK, tài khoản vẫn được tạo với email rác trong CSDL</t>
+        </is>
+      </c>
+      <c r="J6" s="35" t="inlineStr">
+        <is>
+          <t>E2E_SCREENSHOTS/TC_AUTH_001.png</t>
+        </is>
+      </c>
+      <c r="K6" s="35" t="inlineStr">
+        <is>
+          <t>Tester độc lập</t>
+        </is>
+      </c>
+      <c r="L6" s="63" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="28.05" customHeight="1">
       <c r="A7" s="20" t="n">
@@ -3643,16 +3695,57 @@
           <t>BUG_003</t>
         </is>
       </c>
-      <c r="C7" s="35" t="n"/>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n"/>
-      <c r="F7" s="35" t="n"/>
-      <c r="G7" s="35" t="n"/>
-      <c r="H7" s="35" t="n"/>
-      <c r="I7" s="35" t="n"/>
-      <c r="J7" s="35" t="n"/>
-      <c r="K7" s="35" t="n"/>
-      <c r="L7" s="20" t="n"/>
+      <c r="C7" s="35" t="inlineStr">
+        <is>
+          <t>Truy cập /Admin khi chưa phân quyền trả về 302 Redirect thay vì 403 Forbidden</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="inlineStr">
+        <is>
+          <t>Phân hệ Quản trị viên (10_TC_Admin_System)</t>
+        </is>
+      </c>
+      <c r="E7" s="35" t="inlineStr">
+        <is>
+          <t>P2 - Major</t>
+        </is>
+      </c>
+      <c r="F7" s="35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G7" s="35" t="inlineStr">
+        <is>
+          <t>1. Người dùng chưa đăng nhập hoặc role User truy cập URL /Admin
+2. Kiểm tra HTTP Status Code trả về</t>
+        </is>
+      </c>
+      <c r="H7" s="35" t="inlineStr">
+        <is>
+          <t>HTTP 403 Forbidden (hoặc trang Access Denied 403)</t>
+        </is>
+      </c>
+      <c r="I7" s="35" t="inlineStr">
+        <is>
+          <t>HTTP 302 Found, chuyển hướng (Redirect) về /Auth/Login?ReturnUrl=%2FAdmin</t>
+        </is>
+      </c>
+      <c r="J7" s="35" t="inlineStr">
+        <is>
+          <t>E2E_SCREENSHOTS/TC_ADM_002.png</t>
+        </is>
+      </c>
+      <c r="K7" s="35" t="inlineStr">
+        <is>
+          <t>Tester độc lập</t>
+        </is>
+      </c>
+      <c r="L7" s="63" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="28.05" customHeight="1">
       <c r="A8" s="20" t="n">
@@ -3663,16 +3756,58 @@
           <t>BUG_004</t>
         </is>
       </c>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="35" t="n"/>
-      <c r="F8" s="35" t="n"/>
-      <c r="G8" s="35" t="n"/>
-      <c r="H8" s="35" t="n"/>
-      <c r="I8" s="35" t="n"/>
-      <c r="J8" s="35" t="n"/>
-      <c r="K8" s="35" t="n"/>
-      <c r="L8" s="20" t="n"/>
+      <c r="C8" s="35" t="inlineStr">
+        <is>
+          <t>Vẫn cho phép đi quân cờ sau khi người chơi đã bấm Xin hàng (Surrender)</t>
+        </is>
+      </c>
+      <c r="D8" s="35" t="inlineStr">
+        <is>
+          <t>Đấu trực tuyến &amp; Vận hành ván cờ (07_TC_Online_SignalR)</t>
+        </is>
+      </c>
+      <c r="E8" s="35" t="inlineStr">
+        <is>
+          <t>P1 - Blocker</t>
+        </is>
+      </c>
+      <c r="F8" s="35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G8" s="35" t="inlineStr">
+        <is>
+          <t>1. Tạo ván cờ mới
+2. Bên Đỏ gọi POST /api/games/{id}/surrender
+3. Bên Đỏ tiếp tục gửi nước đi POST /api/games/{id}/moves</t>
+        </is>
+      </c>
+      <c r="H8" s="35" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request, ván cờ đã kết thúc không thể đi thêm nước cờ</t>
+        </is>
+      </c>
+      <c r="I8" s="35" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK, server tiếp tục nhận nước cờ và đổi trạng thái về InProgress</t>
+        </is>
+      </c>
+      <c r="J8" s="35" t="inlineStr">
+        <is>
+          <t>E2E_SCREENSHOTS/TC_ONL_015.png</t>
+        </is>
+      </c>
+      <c r="K8" s="35" t="inlineStr">
+        <is>
+          <t>Tester độc lập</t>
+        </is>
+      </c>
+      <c r="L8" s="63" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="28.05" customHeight="1">
       <c r="A9" s="20" t="n">
@@ -3683,16 +3818,58 @@
           <t>BUG_005</t>
         </is>
       </c>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n"/>
-      <c r="F9" s="35" t="n"/>
-      <c r="G9" s="35" t="n"/>
-      <c r="H9" s="35" t="n"/>
-      <c r="I9" s="35" t="n"/>
-      <c r="J9" s="35" t="n"/>
-      <c r="K9" s="35" t="n"/>
-      <c r="L9" s="20" t="n"/>
+      <c r="C9" s="35" t="inlineStr">
+        <is>
+          <t>Cấp Chứng chỉ tốt nghiệp cho người dùng chưa hoàn thành khóa học (0% tiến độ)</t>
+        </is>
+      </c>
+      <c r="D9" s="35" t="inlineStr">
+        <is>
+          <t>Học viện &amp; Kỳ phổ (09_TC_Course_Master)</t>
+        </is>
+      </c>
+      <c r="E9" s="35" t="inlineStr">
+        <is>
+          <t>P2 - Major</t>
+        </is>
+      </c>
+      <c r="F9" s="35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G9" s="35" t="inlineStr">
+        <is>
+          <t>1. Người dùng mới tạo chưa học bài nào
+2. Truy cập trực tiếp /Course/Certificate?courseId=1
+3. Kiểm tra trang hiển thị</t>
+        </is>
+      </c>
+      <c r="H9" s="35" t="inlineStr">
+        <is>
+          <t>Từ chối cấp chứng chỉ, thông báo học viên cần hoàn thành 100% khóa học</t>
+        </is>
+      </c>
+      <c r="I9" s="35" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK, hệ thống vẫn kết xuất chứng chỉ tốt nghiệp hoàn chỉnh</t>
+        </is>
+      </c>
+      <c r="J9" s="35" t="inlineStr">
+        <is>
+          <t>E2E_SCREENSHOTS/TC_COU_009.png</t>
+        </is>
+      </c>
+      <c r="K9" s="35" t="inlineStr">
+        <is>
+          <t>Tester độc lập</t>
+        </is>
+      </c>
+      <c r="L9" s="63" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="28.05" customHeight="1">
       <c r="A10" s="20" t="n">
@@ -3703,16 +3880,57 @@
           <t>BUG_006</t>
         </is>
       </c>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n"/>
-      <c r="F10" s="35" t="n"/>
-      <c r="G10" s="35" t="n"/>
-      <c r="H10" s="35" t="n"/>
-      <c r="I10" s="35" t="n"/>
-      <c r="J10" s="35" t="n"/>
-      <c r="K10" s="35" t="n"/>
-      <c r="L10" s="20" t="n"/>
+      <c r="C10" s="35" t="inlineStr">
+        <is>
+          <t>API tiến độ khóa học không chặn ngưỡng điểm Quiz (Chấp nhận điểm 999999%)</t>
+        </is>
+      </c>
+      <c r="D10" s="35" t="inlineStr">
+        <is>
+          <t>Học viện &amp; Kỳ phổ (09_TC_Course_Master)</t>
+        </is>
+      </c>
+      <c r="E10" s="35" t="inlineStr">
+        <is>
+          <t>P3 - Minor</t>
+        </is>
+      </c>
+      <c r="F10" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G10" s="35" t="inlineStr">
+        <is>
+          <t>1. Gửi POST /api/courses/progress với quizScore = 999999
+2. Kiểm tra phản hồi máy chủ</t>
+        </is>
+      </c>
+      <c r="H10" s="35" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request, điểm số Quiz phải nằm trong khoảng 0 đến 100%</t>
+        </is>
+      </c>
+      <c r="I10" s="35" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK, máy chủ lưu nguyên vẹn bestQuizScore = 999999</t>
+        </is>
+      </c>
+      <c r="J10" s="35" t="inlineStr">
+        <is>
+          <t>E2E_SCREENSHOTS/TC_COU_008.png</t>
+        </is>
+      </c>
+      <c r="K10" s="35" t="inlineStr">
+        <is>
+          <t>Tester độc lập</t>
+        </is>
+      </c>
+      <c r="L10" s="63" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="28.05" customHeight="1">
       <c r="A11" s="20" t="n">
@@ -3723,16 +3941,57 @@
           <t>BUG_007</t>
         </is>
       </c>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n"/>
-      <c r="F11" s="35" t="n"/>
-      <c r="G11" s="35" t="n"/>
-      <c r="H11" s="35" t="n"/>
-      <c r="I11" s="35" t="n"/>
-      <c r="J11" s="35" t="n"/>
-      <c r="K11" s="35" t="n"/>
-      <c r="L11" s="20" t="n"/>
+      <c r="C11" s="35" t="inlineStr">
+        <is>
+          <t>Chức năng Xóa bài cờ thế trong Admin trả về HTTP 200 khi ID không tồn tại</t>
+        </is>
+      </c>
+      <c r="D11" s="35" t="inlineStr">
+        <is>
+          <t>Phân hệ Quản trị viên (10_TC_Admin_System)</t>
+        </is>
+      </c>
+      <c r="E11" s="35" t="inlineStr">
+        <is>
+          <t>P3 - Minor</t>
+        </is>
+      </c>
+      <c r="F11" s="35" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G11" s="35" t="inlineStr">
+        <is>
+          <t>1. Gửi POST /Admin/DeletePuzzle với id = 999999 không có trong CSDL
+2. Kiểm tra mã phản hồi</t>
+        </is>
+      </c>
+      <c r="H11" s="35" t="inlineStr">
+        <is>
+          <t>HTTP 404 Not Found hoặc báo lỗi không tìm thấy bài cờ cần xóa</t>
+        </is>
+      </c>
+      <c r="I11" s="35" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK (hoặc redirect thành công) gây sai lệch trạng thái CMS</t>
+        </is>
+      </c>
+      <c r="J11" s="35" t="inlineStr">
+        <is>
+          <t>E2E_SCREENSHOTS/TC_ADM_009.png</t>
+        </is>
+      </c>
+      <c r="K11" s="35" t="inlineStr">
+        <is>
+          <t>Tester độc lập</t>
+        </is>
+      </c>
+      <c r="L11" s="63" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="28.05" customHeight="1">
       <c r="A12" s="20" t="n">
@@ -5082,12 +5341,12 @@
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
-          <t>Đăng ký thành công tài khoản kythu_1793112405, cấp PlayerId và Token phiên.</t>
-        </is>
-      </c>
-      <c r="J5" s="62" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>HTTP 200 OK, tài khoản vẫn được tạo với email rác trong CSDL</t>
+        </is>
+      </c>
+      <c r="J5" s="63" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="K5" s="16" t="inlineStr">
@@ -5095,7 +5354,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="L5" s="13" t="n"/>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>BUG_002</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="52.8" customHeight="1">
       <c r="A6" s="11" t="n">
@@ -5256,7 +5519,7 @@
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>Không chặn pass ngắn: HTTP 200</t>
+          <t>HTTP 200 OK, hệ thống tạo tài khoản thành công với mật khẩu 3 ký tự</t>
         </is>
       </c>
       <c r="J8" s="63" t="inlineStr">
@@ -9723,12 +9986,12 @@
       </c>
       <c r="I19" s="24" t="inlineStr">
         <is>
-          <t>Người chơi bấm Xin hàng (Resign): Hệ thống xử thua ngay lập tức và cập nhật Elo.</t>
-        </is>
-      </c>
-      <c r="J19" s="62" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>HTTP 200 OK, server tiếp tục nhận nước cờ và đổi trạng thái về InProgress</t>
+        </is>
+      </c>
+      <c r="J19" s="63" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="K19" s="26" t="inlineStr">
@@ -9736,7 +9999,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="L19" s="35" t="n"/>
+      <c r="L19" s="35" t="inlineStr">
+        <is>
+          <t>BUG_004</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="41.4" customFormat="1" customHeight="1" s="28">
       <c r="A20" s="20" t="n">
@@ -11607,12 +11874,12 @@
       </c>
       <c r="I12" s="24" t="inlineStr">
         <is>
-          <t>Lưu tiến độ qua API /api/courses/progress: Ghi nhận isCompleted = true và cập nhật % khóa học.</t>
-        </is>
-      </c>
-      <c r="J12" s="62" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>HTTP 200 OK, máy chủ lưu nguyên vẹn bestQuizScore = 999999</t>
+        </is>
+      </c>
+      <c r="J12" s="63" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="K12" s="26" t="inlineStr">
@@ -11620,7 +11887,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="L12" s="35" t="n"/>
+      <c r="L12" s="35" t="inlineStr">
+        <is>
+          <t>BUG_006</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="55.2" customFormat="1" customHeight="1" s="28">
       <c r="A13" s="20" t="n">
@@ -11664,12 +11935,12 @@
       </c>
       <c r="I13" s="24" t="inlineStr">
         <is>
-          <t>Hoàn thành 100% khóa học: Cấp Chứng chỉ tốt nghiệp điện tử trang trọng kèm mã xác thực.</t>
-        </is>
-      </c>
-      <c r="J13" s="62" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>HTTP 200 OK, hệ thống vẫn kết xuất chứng chỉ tốt nghiệp hoàn chỉnh</t>
+        </is>
+      </c>
+      <c r="J13" s="63" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="K13" s="27" t="inlineStr">
@@ -11677,7 +11948,11 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="L13" s="35" t="n"/>
+      <c r="L13" s="35" t="inlineStr">
+        <is>
+          <t>BUG_005</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="55.2" customFormat="1" customHeight="1" s="28">
       <c r="A14" s="20" t="n">

--- a/Testing/TestCases_KLCN_CoTuong (1).xlsx
+++ b/Testing/TestCases_KLCN_CoTuong (1).xlsx
@@ -4520,44 +4520,127 @@
       </c>
     </row>
     <row r="20" ht="28.05" customHeight="1" s="34">
-      <c r="A20" s="19" t="n">
+      <c r="A20" s="64" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="65" t="inlineStr">
         <is>
           <t>BUG_016</t>
         </is>
       </c>
-      <c r="C20" s="38" t="n"/>
-      <c r="D20" s="38" t="n"/>
-      <c r="E20" s="38" t="n"/>
-      <c r="F20" s="38" t="n"/>
-      <c r="G20" s="38" t="n"/>
-      <c r="H20" s="38" t="n"/>
-      <c r="I20" s="38" t="n"/>
-      <c r="J20" s="38" t="n"/>
-      <c r="K20" s="38" t="n"/>
-      <c r="L20" s="19" t="n"/>
+      <c r="C20" s="66" t="inlineStr">
+        <is>
+          <t>Cho phép đăng ký Username chứa mã độc XSS &lt;script&gt; không được lọc rửa (Stored XSS)</t>
+        </is>
+      </c>
+      <c r="D20" s="66" t="inlineStr">
+        <is>
+          <t>Xác thực &amp; Tài khoản (04_TC_Auth_Profile)</t>
+        </is>
+      </c>
+      <c r="E20" s="64" t="inlineStr">
+        <is>
+          <t>P2 - Major</t>
+        </is>
+      </c>
+      <c r="F20" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G20" s="66" t="inlineStr">
+        <is>
+          <t>1. Gửi POST /api/auth/register
+2. Body username = "&lt;script&gt;alert(1)&lt;/script&gt;"
+3. Kiểm tra phản hồi và dữ liệu lưu</t>
+        </is>
+      </c>
+      <c r="H20" s="66" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request, từ chối username chứa ký tự đặc biệt hoặc thẻ HTML script</t>
+        </is>
+      </c>
+      <c r="I20" s="66" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK, server lưu nguyên vẹn payload XSS vào bảng Users trong CSDL SQLite</t>
+        </is>
+      </c>
+      <c r="J20" s="66" t="inlineStr">
+        <is>
+          <t>E2E_SCREENSHOTS/TC_AUTH_002.png</t>
+        </is>
+      </c>
+      <c r="K20" s="64" t="inlineStr">
+        <is>
+          <t>Tester độc lập</t>
+        </is>
+      </c>
+      <c r="L20" s="67" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="28.05" customHeight="1" s="34">
-      <c r="A21" s="19" t="n">
+      <c r="A21" s="64" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="65" t="inlineStr">
         <is>
           <t>BUG_017</t>
         </is>
       </c>
-      <c r="C21" s="38" t="n"/>
-      <c r="D21" s="38" t="n"/>
-      <c r="E21" s="38" t="n"/>
-      <c r="F21" s="38" t="n"/>
-      <c r="G21" s="38" t="n"/>
-      <c r="H21" s="38" t="n"/>
-      <c r="I21" s="38" t="n"/>
-      <c r="J21" s="38" t="n"/>
-      <c r="K21" s="38" t="n"/>
-      <c r="L21" s="19" t="n"/>
+      <c r="C21" s="66" t="inlineStr">
+        <is>
+          <t>API tạo ván cờ chấp nhận thời gian thi đấu âm (timeControl = -999)</t>
+        </is>
+      </c>
+      <c r="D21" s="66" t="inlineStr">
+        <is>
+          <t>Chế độ chơi &amp; AI (06_TC_Game_Play)</t>
+        </is>
+      </c>
+      <c r="E21" s="64" t="inlineStr">
+        <is>
+          <t>P3 - Minor</t>
+        </is>
+      </c>
+      <c r="F21" s="64" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G21" s="66" t="inlineStr">
+        <is>
+          <t>1. Gửi POST /api/games với body timeControl = -999
+2. Kiểm tra mã phản hồi và trạng thái ván</t>
+        </is>
+      </c>
+      <c r="H21" s="66" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request, thời gian thi đấu timeControl phải nằm trong khoảng dương (ví dụ 1-60 phút)</t>
+        </is>
+      </c>
+      <c r="I21" s="66" t="inlineStr">
+        <is>
+          <t>HTTP 201 Created, server tạo thành công ván đấu với thời gian âm gây lỗi đồng hồ đếm ngược</t>
+        </is>
+      </c>
+      <c r="J21" s="66" t="inlineStr">
+        <is>
+          <t>E2E_SCREENSHOTS/TC_GAME_001.png</t>
+        </is>
+      </c>
+      <c r="K21" s="64" t="inlineStr">
+        <is>
+          <t>Tester độc lập</t>
+        </is>
+      </c>
+      <c r="L21" s="67" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="28.05" customHeight="1" s="34">
       <c r="A22" s="19" t="n">
@@ -5126,11 +5209,11 @@
       </c>
       <c r="D6" s="46" t="n"/>
       <c r="E6" s="49" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F6" s="50" t="n"/>
       <c r="G6" s="59" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H6" s="60" t="n"/>
       <c r="I6" s="47">
@@ -5215,10 +5298,10 @@
         <v/>
       </c>
       <c r="F11" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H11" s="5">
         <f>COUNTIF('04_TC_Auth_Profile'!J5:J21, "Blocked")</f>
@@ -5291,10 +5374,10 @@
         <v/>
       </c>
       <c r="F13" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="5">
         <f>COUNTIF('06_TC_Game_Play'!J5:J22, "Blocked")</f>
@@ -5511,10 +5594,10 @@
         <v/>
       </c>
       <c r="F19" s="42" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G19" s="42" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H19" s="42">
         <f>SUM(H11:H18)</f>
@@ -5755,12 +5838,12 @@
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>Hệ thống từ chối đăng ký username trùng lặp và trả về thông báo lỗi chính xác.</t>
-        </is>
-      </c>
-      <c r="J6" s="28" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>HTTP 200 OK, server lưu nguyên vẹn payload XSS vào bảng Users trong CSDL SQLite</t>
+        </is>
+      </c>
+      <c r="J6" s="63" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="K6" s="15" t="inlineStr">
@@ -5768,7 +5851,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="L6" s="13" t="n"/>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>BUG_016</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="39.6" customHeight="1" s="34">
       <c r="A7" s="11" t="n">
@@ -8405,12 +8492,12 @@
       </c>
       <c r="I5" s="23" t="inlineStr">
         <is>
-          <t>Khởi tạo bàn cờ mới đầy đủ 32 quân trong chế độ Pass &amp; Play, Đỏ đi trước, không giới hạn giờ.</t>
-        </is>
-      </c>
-      <c r="J5" s="28" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>HTTP 201 Created, server tạo thành công ván đấu với thời gian âm gây lỗi đồng hồ đếm ngược</t>
+        </is>
+      </c>
+      <c r="J5" s="63" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="K5" s="24" t="inlineStr">
@@ -8418,7 +8505,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="L5" s="38" t="n"/>
+      <c r="L5" s="38" t="inlineStr">
+        <is>
+          <t>BUG_017</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="41.4" customFormat="1" customHeight="1" s="26">
       <c r="A6" s="19" t="n">

--- a/Testing/TestCases_KLCN_CoTuong (1).xlsx
+++ b/Testing/TestCases_KLCN_CoTuong (1).xlsx
@@ -29,7 +29,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="37">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -269,8 +269,19 @@
       <color rgb="00990000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -365,6 +376,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
         <bgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F497D"/>
+        <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
   </fills>
@@ -959,7 +976,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1131,6 +1148,12 @@
     </xf>
     <xf numFmtId="0" fontId="34" fillId="16" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3505,7 +3528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6.6640625" customWidth="1" style="34" min="1" max="1"/>
@@ -3520,6 +3543,8 @@
     <col width="20.6640625" customWidth="1" style="34" min="10" max="10"/>
     <col width="16.6640625" customWidth="1" style="34" min="11" max="11"/>
     <col width="14.6640625" customWidth="1" style="34" min="12" max="12"/>
+    <col width="46" customWidth="1" style="34" min="13" max="13"/>
+    <col width="46" customWidth="1" style="34" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" s="34">
@@ -3597,6 +3622,16 @@
           <t>Trạng thái</t>
         </is>
       </c>
+      <c r="M4" s="68" t="inlineStr">
+        <is>
+          <t>Ngữ cảnh phát sinh &amp; Cơ chế hoạt động (Trigger Context &amp; Mechanism)</t>
+        </is>
+      </c>
+      <c r="N4" s="68" t="inlineStr">
+        <is>
+          <t>Vị trí code &amp; Hướng dẫn Fix cho Dev (Root Cause &amp; Dev Fix Guide)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="28.05" customHeight="1" s="34">
       <c r="A5" s="19" t="n">
@@ -3659,6 +3694,20 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="M5" s="69" t="inlineStr">
+        <is>
+          <t>• Ngữ cảnh xuất hiện: Trên form đăng ký Web MVC, HTML5 chặn ô input minlength. Lỗi CHỈ XUẤT HIỆN khi người dùng/attacker cố tình Bypass giao diện (dùng F12 Console, Postman, Python script) gọi trực tiếp endpoint REST API.
+• Cơ chế hoạt động: POST /api/auth/register nhận password='123' (3 ký tự). Backend không kiểm tra độ dài tối thiểu, thực hiện băm mật khẩu và cấp Token thành công.</t>
+        </is>
+      </c>
+      <c r="N5" s="69" t="inlineStr">
+        <is>
+          <t>• Vị trí code: ChessCore/Controllers/AuthController.cs (dòng 697-700 trong hàm ApiRegister).
+• Hướng dẫn Fix: Thêm kiểm tra độ dài:
+if (request.Password.Length &lt; 6) return BadRequest(new { message = 'Mật khẩu phải từ 6 ký tự trở lên.' });
+Hoặc gắn attribute [MinLength(6)] vào class RegisterApiRequest.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="28.05" customHeight="1" s="34">
       <c r="A6" s="19" t="n">
@@ -3721,6 +3770,21 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="M6" s="69" t="inlineStr">
+        <is>
+          <t>• Ngữ cảnh xuất hiện: Trên giao diện web, thẻ input type='email' có sẵn bộ lọc cơ bản của trình duyệt. Lỗi XUẤT HIỆN khi người dùng cố tình dùng script / Postman gọi thẳng API, truyền email rác như 'not_an_email' không có dấu @ và tên miền.
+• Cơ chế hoạt động: Backend chỉ kiểm tra rỗng và trùng lặp, thiếu Regex xác thực định dạng email, lưu thẳng chuỗi rác vào CSDL.</t>
+        </is>
+      </c>
+      <c r="N6" s="69" t="inlineStr">
+        <is>
+          <t>• Vị trí code: ChessCore/Controllers/AuthController.cs (dòng 703-713 trong hàm ApiRegister).
+• Hướng dẫn Fix: Thêm Regex xác thực định dạng Email:
+var emailRegex = new Regex(@"^[^@\s]+@[^@\s]+\.[^@\s]+$");
+if (!string.IsNullOrEmpty(email) &amp;&amp; !emailRegex.IsMatch(email))
+    return BadRequest(new { message = 'Email không đúng định dạng.' });</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="28.05" customHeight="1" s="34">
       <c r="A7" s="19" t="n">
@@ -3782,6 +3846,18 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="M7" s="69" t="inlineStr">
+        <is>
+          <t>• Ngữ cảnh xuất hiện: Xuất hiện khi người dùng chưa đăng nhập, hoặc tài khoản có role 'Player' (hoặc bot/crawler) truy cập trực tiếp đường dẫn quản trị /Admin trên trình duyệt hoặc gửi HTTP GET.
+• Cơ chế hoạt động: AdminController có [Authorize]. Theo mặc định Cookie Auth của ASP.NET Core, request bị redirect 302 Found về /Auth/Login thay vì trả mã lỗi 403 Forbidden chuẩn RESTful bảo mật.</t>
+        </is>
+      </c>
+      <c r="N7" s="69" t="inlineStr">
+        <is>
+          <t>• Vị trí code: ChessCore/Program.cs (cấu hình ConfigureApplicationCookie) &amp; AdminController.cs (dòng 13).
+• Hướng dẫn Fix: Trong Program.cs thêm xử lý OnRedirectToAccessDenied để trả về đúng StatusCode 403 Forbidden thay vì 302 Redirect ngầm đối với các route quản trị nhạy cảm.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="28.05" customHeight="1" s="34">
       <c r="A8" s="19" t="n">
@@ -3844,6 +3920,18 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="M8" s="69" t="inlineStr">
+        <is>
+          <t>• Ngữ cảnh xuất hiện: Xuất hiện trực tiếp trên giao diện thi đấu Online (PvP) khi người chơi bấm nút 'Xin hàng' và xác nhận đầu hàng trong trận đấu 2 người.
+• Cơ chế hoạt động: Trong wwwroot/js/game.js hàm resignGame() gọi fetch('/api/games/' + id + '/resign') nhưng QUÊN đính kèm header Authorization Bearer Token. Backend GamesController.cs dòng 1220 trả về 401 Unauthorized khiến ván cờ không thể kết thúc, server vẫn giữ InProgress và tiếp tục nhận nước đi.</t>
+        </is>
+      </c>
+      <c r="N8" s="69" t="inlineStr">
+        <is>
+          <t>• Vị trí code: ChessCore/wwwroot/js/game.js (dòng 2170-2175) &amp; GamesController.cs (dòng 1220).
+• Hướng dẫn Fix: Trong game.js thêm headers: { 'Authorization': 'Bearer ' + token }. Trong GamesController.cs hỗ trợ fallback lấy User ID từ Cookie Claims của phiên đăng nhập web nếu không có Bearer Token.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="28.05" customHeight="1" s="34">
       <c r="A9" s="19" t="n">
@@ -3906,6 +3994,18 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="M9" s="69" t="inlineStr">
+        <is>
+          <t>• Ngữ cảnh xuất hiện: Xuất hiện khi học viên mới tạo tài khoản (0% tiến độ, chưa hoàn thành bài nào) gõ trực tiếp URL /Course/Certificate trên trình duyệt.
+• Cơ chế hoạt động: Logic kiểm duyệt điều kiện trong Controller và View chưa khóa chặt chẽ. Hệ thống vẫn kết xuất template chứng chỉ CERT-CT hoàn chỉnh kèm họ tên và mã số dù trong CSDL UserCourseProgresses có 0 bản ghi hoàn thành.</t>
+        </is>
+      </c>
+      <c r="N9" s="69" t="inlineStr">
+        <is>
+          <t>• Vị trí code: ChessCore/Controllers/CourseController.cs (dòng 229-239) &amp; Views/Course/Certificate.cshtml.
+• Hướng dẫn Fix: Khi !isEligible, Controller phải return Forbid() hoặc View thông báo từ chối cấp chứng chỉ (kèm tiến độ hiện tại), tuyệt đối không render giao diện chứng chỉ hoàn thành.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="28.05" customHeight="1" s="34">
       <c r="A10" s="19" t="n">
@@ -3967,6 +4067,20 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="M10" s="69" t="inlineStr">
+        <is>
+          <t>• Ngữ cảnh xuất hiện: Trên web, bài trắc nghiệm tự tính điểm max 100%. Lỗi XUẤT HIỆN khi người học cố tình dùng F12 Console hoặc Postman gọi API POST /api/courses/progress để gian lận điểm số.
+• Cơ chế hoạt động: DTO nhận QuizScore kiểu int mà không kiểm tra cận trên [0, 100]. Giá trị 999999 được lưu nguyên vẹn vào CSDL và cập nhật BestQuizScore cho bài học.</t>
+        </is>
+      </c>
+      <c r="N10" s="69" t="inlineStr">
+        <is>
+          <t>• Vị trí code: ChessCore/Controllers/CourseController.cs (dòng 165-175 trong hàm SaveProgress).
+• Hướng dẫn Fix: Thêm kiểm tra khoảng giá trị hợp lệ:
+if (request.QuizScore &lt; 0 || request.QuizScore &gt; 100)
+    return BadRequest(new { message = 'Điểm trắc nghiệm Quiz phải từ 0 đến 100.' });</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="28.05" customHeight="1" s="34">
       <c r="A11" s="19" t="n">
@@ -4028,6 +4142,20 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="M11" s="69" t="inlineStr">
+        <is>
+          <t>• Ngữ cảnh xuất hiện: Xuất hiện khi Admin thực hiện xóa bài cờ thế mà bài đó đã bị xóa trước đó (mở 2 tab), hoặc gửi request POST /Admin/DeletePuzzle với id=999999 không tồn tại.
+• Cơ chế hoạt động: Hàm DeletePuzzle tìm puzzle theo id. Khi trả về null, code bỏ qua việc xóa nhưng không quăng lỗi 404 mà vẫn redirect 302 Found về danh sách, gây hiểu nhầm thao tác thành công.</t>
+        </is>
+      </c>
+      <c r="N11" s="69" t="inlineStr">
+        <is>
+          <t>• Vị trí code: ChessCore/Controllers/AdminController.cs (dòng 121-133 trong hàm DeletePuzzle).
+• Hướng dẫn Fix: Thêm kiểm tra thực thể:
+var puzzle = await _context.Puzzles.FindAsync(id);
+if (puzzle == null) return NotFound(new { message = 'Không tìm thấy thế cờ cần xóa.' });</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="28.05" customHeight="1" s="34">
       <c r="A12" s="64" t="n">
@@ -4090,6 +4218,18 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="M12" s="69" t="inlineStr">
+        <is>
+          <t>• Ngữ cảnh xuất hiện: Xuất hiện trực tiếp trên giao diện web thật tại /Auth/ForgotPassword khi người dùng yêu cầu cấp lại mật khẩu mà máy chủ gặp lỗi cấu hình SMTP Gmail (không gửi được mail).
+• Cơ chế hoạt động: Trong khối bắt lỗi gửi mail của AuthController.cs, lập trình viên đã gán trực tiếp: TempData['DevOtp'] = otp và TempData['OtpMessage'] = 'MÃ OTP CỦA BẠN LÀ: ' + otp. Chuỗi này được in thẳng lên màn hình ResetPassword.</t>
+        </is>
+      </c>
+      <c r="N12" s="69" t="inlineStr">
+        <is>
+          <t>• Vị trí code: ChessCore/Controllers/AuthController.cs (dòng 315-319 trong hàm ForgotPassword).
+• Hướng dẫn Fix: Xóa bỏ hoàn toàn 2 dòng gán OTP vào TempData. Khi email gửi thất bại, chỉ hiển thị thông báo chung: 'Hệ thống gửi thư tạm gián đoạn, vui lòng liên hệ admin hỗ trợ.'</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="28.05" customHeight="1" s="34">
       <c r="A13" s="64" t="n">
@@ -4151,6 +4291,18 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="M13" s="69" t="inlineStr">
+        <is>
+          <t>• Ngữ cảnh xuất hiện: Xuất hiện khi người dùng click liên tục (spam click) vào nút 'Nhận thưởng' nhiệm vụ hàng ngày trên giao diện, hoặc gọi POST /api/quests/{id}/claim bằng script tự động.
+• Cơ chế hoạt động: Backend không kiểm tra xem người chơi đã hoàn thành điều kiện nhiệm vụ chưa và không có cờ IsClaimed hoặc Transaction khóa bản ghi trong ngày. Cứ gọi là trả 200 OK và cộng thưởng vô hạn.</t>
+        </is>
+      </c>
+      <c r="N13" s="69" t="inlineStr">
+        <is>
+          <t>• Vị trí code: ChessCore/Controllers/QuestsController.cs (hoặc hàm ClaimQuest).
+• Hướng dẫn Fix: Kiểm tra trạng thái nhiệm vụ trong CSDL: Phải đạt TargetCount và IsClaimed == false. Khi nhận thưởng phải set IsClaimed = true và lưu trong một Database Transaction duy nhất.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="28.05" customHeight="1" s="34">
       <c r="A14" s="64" t="n">
@@ -4212,6 +4364,18 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="M14" s="69" t="inlineStr">
+        <is>
+          <t>• Ngữ cảnh xuất hiện: Xuất hiện khi kẻ tấn công sử dụng công cụ dò mật khẩu (Hydra, Burp Suite, script Python) gửi hàng loạt request đăng nhập sai vào POST /api/auth/login.
+• Cơ chế hoạt động: Backend không có cơ chế Rate Limiting, không có CAPTCHA và không theo dõi số lần đăng nhập sai. Server trả về HTTP 401 liên tục trong 0.02 giây, cho phép brute-force hàng triệu mật khẩu.</t>
+        </is>
+      </c>
+      <c r="N14" s="69" t="inlineStr">
+        <is>
+          <t>• Vị trí code: ChessCore/Controllers/AuthController.cs (dòng 626-660) &amp; Program.cs.
+• Hướng dẫn Fix: Tích hợp thư viện AspNetCoreRateLimit trong Program.cs giới hạn 5 lần/phút/IP. Thêm thuộc tính AccessFailedCount và LockoutEnd vào model User để khóa tài khoản khi sai quá 5 lần.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="28.05" customHeight="1" s="34">
       <c r="A15" s="64" t="n">
@@ -4273,6 +4437,20 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="M15" s="69" t="inlineStr">
+        <is>
+          <t>• Ngữ cảnh xuất hiện: Xuất hiện khi client/API ngoài gọi POST /api/games kèm chuỗi initialFen sai cú pháp cờ tướng (thiếu quân, sai ký tự phân cách, sai số hàng).
+• Cơ chế hoạt động: Trong hàm CreateGame, khi Board.TryParseFen thất bại, backend bắt exception nhưng âm thầm nuốt lỗi và gán initialFen = null, trả về HTTP 201 Created với bàn cờ mặc định thay vì báo lỗi 400.</t>
+        </is>
+      </c>
+      <c r="N15" s="69" t="inlineStr">
+        <is>
+          <t>• Vị trí code: ChessCore/Controllers/GamesController.cs (dòng 538-549 trong hàm CreateGame).
+• Hướng dẫn Fix: Kiểm tra tính hợp lệ trước khi tạo ván:
+if (!string.IsNullOrWhiteSpace(initialFen) &amp;&amp; !Board.TryParseFen(initialFen, out _, out string err))
+    return BadRequest(new { message = 'Chuỗi FEN không hợp lệ: ' + err });</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="28.05" customHeight="1" s="34">
       <c r="A16" s="64" t="n">
@@ -4335,6 +4513,18 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="M16" s="69" t="inlineStr">
+        <is>
+          <t>• Ngữ cảnh xuất hiện: Xuất hiện ở chế độ Đấu trực tuyến (PvP) khi ván đấu kết thúc và 1 bên người chơi bấm nút 'Tái đấu' (Rematch) hoặc gọi POST /api/games/{id}/rematch.
+• Cơ chế hoạt động: GamesController.CreateRematch lập tức tạo bàn cờ mới InProgress và gửi sự kiện SignalR RematchStarted ép cả 2 người vào ván mới mà không có bước OfferRematch chờ đối phương đồng ý.</t>
+        </is>
+      </c>
+      <c r="N16" s="69" t="inlineStr">
+        <is>
+          <t>• Vị trí code: ChessCore/Controllers/GamesController.cs (dòng 441-480 trong CreateRematch).
+• Hướng dẫn Fix: Tách làm 2 pha: Khi bấm tái đấu chỉ gửi sự kiện SignalR OfferRematch. Chỉ khi đối phương gửi AcceptRematch thì server mới khởi tạo bàn cờ mới và bắt đầu trận đấu.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="28.05" customHeight="1" s="34">
       <c r="A17" s="64" t="n">
@@ -4396,6 +4586,20 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="M17" s="69" t="inlineStr">
+        <is>
+          <t>• Ngữ cảnh xuất hiện: Xuất hiện khi khách vãng lai (chưa đăng nhập) học bài hoặc gọi API POST /api/courses/progress với lessonId=999999 (ID không có trong CSDL).
+• Cơ chế hoạt động: Nhánh xử lý cho khách (userId == null) không kiểm tra sự tồn tại của bài học trong bảng CourseLessons mà lập tức trả về HTTP 200 OK với thông tin giả lập.</t>
+        </is>
+      </c>
+      <c r="N17" s="69" t="inlineStr">
+        <is>
+          <t>• Vị trí code: ChessCore/Controllers/CourseController.cs (dòng 155-165 trong ExecuteSaveProgress).
+• Hướng dẫn Fix: Thêm truy vấn kiểm tra CSDL:
+if (!await _context.CourseLessons.AnyAsync(l =&gt; l.Id == request.LessonId))
+    return NotFound(new { message = 'Bài học không tồn tại trong hệ thống.' });</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="28.05" customHeight="1" s="34">
       <c r="A18" s="64" t="n">
@@ -4457,6 +4661,20 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="M18" s="69" t="inlineStr">
+        <is>
+          <t>• Ngữ cảnh xuất hiện: Xuất hiện trên trang Quản trị Admin CMS (/Admin/Users). Chức năng 'Khóa / Mở khóa tài khoản' có trong đặc tả tài liệu nhưng trên thực tế KHÔNG HỀ TỒN TẠI.
+• Cơ chế hoạt động: Model User.cs hoàn toàn thiếu cột IsLocked / IsActive. AdminController chỉ có hàm đổi quyền và xóa người dùng. Không có cách nào khóa tài khoản vi phạm.</t>
+        </is>
+      </c>
+      <c r="N18" s="69" t="inlineStr">
+        <is>
+          <t>• Vị trí code: ChessCore/Models/User.cs &amp; ChessCore/Controllers/AdminController.cs.
+• Hướng dẫn Fix: 1. Thêm thuộc tính public bool IsLocked { get; set; } = false vào User.cs và tạo Migration.
+2. Viết action ToggleLockUser(int userId) trong AdminController.
+3. Kiểm tra IsLocked khi đăng nhập trong AuthController.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="28.05" customHeight="1" s="34">
       <c r="A19" s="64" t="n">
@@ -4518,6 +4736,23 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="M19" s="69" t="inlineStr">
+        <is>
+          <t>• Ngữ cảnh xuất hiện: Xuất hiện trực tiếp trên giao diện Admin CMS tại /Admin/Puzzles khi quản trị viên tạo bài cờ thế mới và nhập chuỗi FEN rác hoặc sai cú pháp.
+• Cơ chế hoạt động: AdminController.CreatePuzzle chỉ kiểm tra IsNullOrWhiteSpace(puzzle.Fen). Chuỗi FEN rác được lưu thẳng vào CSDL. Khi người chơi mở bài cờ thế này, bàn cờ sẽ bị crash exception.</t>
+        </is>
+      </c>
+      <c r="N19" s="69" t="inlineStr">
+        <is>
+          <t>• Vị trí code: ChessCore/Controllers/AdminController.cs (dòng 75-88 trong CreatePuzzle).
+• Hướng dẫn Fix: Bổ sung gọi engine kiểm tra cú pháp trước khi lưu:
+if (!Board.TryParseFen(puzzle.Fen.Trim(), out _, out string fenErr))
+{
+    TempData['ErrorMessage'] = 'Chuỗi FEN không hợp lệ: ' + fenErr;
+    return RedirectToAction(nameof(Puzzles));
+}</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="28.05" customHeight="1" s="34">
       <c r="A20" s="64" t="n">
@@ -4580,6 +4815,21 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="M20" s="69" t="inlineStr">
+        <is>
+          <t>• Ngữ cảnh xuất hiện: Trên form đăng ký web MVC có thể không lọc được hết, hoặc người dùng CỐ TÌNH DÙNG SCRIPT / Postman gọi API POST /api/auth/register với username chứa thẻ &lt;script&gt;alert(1)&lt;/script&gt;.
+• Cơ chế hoạt động: Backend không lọc HTML encoding hay regex ký tự hợp lệ, lưu nguyên văn mã script vào bảng Users. Khi username này được hiển thị trên Bảng xếp hạng hoặc CMS Admin, mã độc sẽ tự động thực thi (Stored XSS).</t>
+        </is>
+      </c>
+      <c r="N20" s="69" t="inlineStr">
+        <is>
+          <t>• Vị trí code: ChessCore/Controllers/AuthController.cs (dòng 702-705 trong ApiRegister).
+• Hướng dẫn Fix: Áp dụng Regex chỉ cho phép ký tự chữ và số (alphanumeric):
+var usernameRegex = new Regex(@"^[a-zA-Z0-9_\.]{3,20}$");
+if (!usernameRegex.IsMatch(username))
+    return BadRequest(new { message = 'Tên người dùng chỉ được chứa chữ cái, số, gạch dưới (3-20 ký tự).' });</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="28.05" customHeight="1" s="34">
       <c r="A21" s="64" t="n">
@@ -4639,6 +4889,20 @@
       <c r="L21" s="67" t="inlineStr">
         <is>
           <t>Open</t>
+        </is>
+      </c>
+      <c r="M21" s="69" t="inlineStr">
+        <is>
+          <t>• Ngữ cảnh xuất hiện: Trên giao diện web chỉ cho chọn thời gian dương (5p, 10p, 15p). Lỗi CHỈ XUẤT HIỆN khi người dùng/attacker Bypass giao diện bằng script / Postman, gửi POST /api/games với timeControl = -999.
+• Cơ chế hoạt động: Backend CreateGame không kiểm tra ràng buộc giá trị biên timeControl &gt; 0, tạo ra ván cờ với thời gian âm dẫn đến lỗi tính toán đồng hồ đếm ngược.</t>
+        </is>
+      </c>
+      <c r="N21" s="69" t="inlineStr">
+        <is>
+          <t>• Vị trí code: ChessCore/Controllers/GamesController.cs (dòng 538-549 trong CreateGame).
+• Hướng dẫn Fix: Tạo DTO có DataAnnotation xác thực biên:
+[Range(1, 180, ErrorMessage = 'Thời gian thi đấu phải từ 1 đến 180 phút.')]
+public int TimeControl { get; set; }</t>
         </is>
       </c>
     </row>

--- a/Testing/TestCases_KLCN_CoTuong (1).xlsx
+++ b/Testing/TestCases_KLCN_CoTuong (1).xlsx
@@ -3696,7 +3696,9 @@
       </c>
       <c r="M5" s="69" t="inlineStr">
         <is>
-          <t>• Ngữ cảnh xuất hiện: Trên form đăng ký Web MVC, HTML5 chặn ô input minlength. Lỗi CHỈ XUẤT HIỆN khi người dùng/attacker cố tình Bypass giao diện (dùng F12 Console, Postman, Python script) gọi trực tiếp endpoint REST API.
+          <t>🎯 ĐIỀU KIỆN KÍCH HOẠT: [CHẠY SCRIPT / F12 CONSOLE MỚI THẤY]
+👉 100% Thấy lỗi khi: Mở F12 Console gửi POST /api/auth/register với password='123' (Giao diện web chặn HTML5 minlength, chỉ script gọi API mới kích hoạt lỗi).
+• Ngữ cảnh xuất hiện: Trên form đăng ký Web MVC, HTML5 chặn ô input minlength. Lỗi CHỈ XUẤT HIỆN khi người dùng/attacker cố tình Bypass giao diện (dùng F12 Console, Postman, Python script) gọi trực tiếp endpoint REST API.
 • Cơ chế hoạt động: POST /api/auth/register nhận password='123' (3 ký tự). Backend không kiểm tra độ dài tối thiểu, thực hiện băm mật khẩu và cấp Token thành công.</t>
         </is>
       </c>
@@ -3772,7 +3774,9 @@
       </c>
       <c r="M6" s="69" t="inlineStr">
         <is>
-          <t>• Ngữ cảnh xuất hiện: Trên giao diện web, thẻ input type='email' có sẵn bộ lọc cơ bản của trình duyệt. Lỗi XUẤT HIỆN khi người dùng cố tình dùng script / Postman gọi thẳng API, truyền email rác như 'not_an_email' không có dấu @ và tên miền.
+          <t>🎯 ĐIỀU KIỆN KÍCH HOẠT: [CHẠY SCRIPT / F12 CONSOLE MỚI THẤY]
+👉 100% Thấy lỗi khi: Mở F12 Console gửi POST /api/auth/register với email='not_an_email' (Giao diện web chặn type=email, chỉ script gọi API mới kích hoạt lỗi).
+• Ngữ cảnh xuất hiện: Trên giao diện web, thẻ input type='email' có sẵn bộ lọc cơ bản của trình duyệt. Lỗi XUẤT HIỆN khi người dùng cố tình dùng script / Postman gọi thẳng API, truyền email rác như 'not_an_email' không có dấu @ và tên miền.
 • Cơ chế hoạt động: Backend chỉ kiểm tra rỗng và trùng lặp, thiếu Regex xác thực định dạng email, lưu thẳng chuỗi rác vào CSDL.</t>
         </is>
       </c>
@@ -3848,7 +3852,9 @@
       </c>
       <c r="M7" s="69" t="inlineStr">
         <is>
-          <t>• Ngữ cảnh xuất hiện: Xuất hiện khi người dùng chưa đăng nhập, hoặc tài khoản có role 'Player' (hoặc bot/crawler) truy cập trực tiếp đường dẫn quản trị /Admin trên trình duyệt hoặc gửi HTTP GET.
+          <t>🎯 ĐIỀU KIỆN KÍCH HOẠT: [GỬI HTTP REQUEST / API MỚI THẤY]
+👉 100% Thấy lỗi khi: Dùng Postman hoặc script gửi GET /Admin không kèm cookie (Server trả 302 Found redirect ngầm thay vì trả 403 Forbidden).
+• Ngữ cảnh xuất hiện: Xuất hiện khi người dùng chưa đăng nhập, hoặc tài khoản có role 'Player' (hoặc bot/crawler) truy cập trực tiếp đường dẫn quản trị /Admin trên trình duyệt hoặc gửi HTTP GET.
 • Cơ chế hoạt động: AdminController có [Authorize]. Theo mặc định Cookie Auth của ASP.NET Core, request bị redirect 302 Found về /Auth/Login thay vì trả mã lỗi 403 Forbidden chuẩn RESTful bảo mật.</t>
         </is>
       </c>
@@ -3922,7 +3928,9 @@
       </c>
       <c r="M8" s="69" t="inlineStr">
         <is>
-          <t>• Ngữ cảnh xuất hiện: Xuất hiện trực tiếp trên giao diện thi đấu Online (PvP) khi người chơi bấm nút 'Xin hàng' và xác nhận đầu hàng trong trận đấu 2 người.
+          <t>🎯 ĐIỀU KIỆN KÍCH HOẠT: [THAO TÁC TRỰC TIẾP TRÊN GIAO DIỆN WEB (UI)]
+👉 100% Thấy lỗi khi: Vào ván cờ Online 2 người trên web -&gt; Bấm nút 'Xin hàng' -&gt; Bấm 'Đồng ý' -&gt; Bàn cờ vẫn tiếp tục cho kéo thả quân đi tiếp bình thường!
+• Ngữ cảnh xuất hiện: Xuất hiện trực tiếp trên giao diện thi đấu Online (PvP) khi người chơi bấm nút 'Xin hàng' và xác nhận đầu hàng trong trận đấu 2 người.
 • Cơ chế hoạt động: Trong wwwroot/js/game.js hàm resignGame() gọi fetch('/api/games/' + id + '/resign') nhưng QUÊN đính kèm header Authorization Bearer Token. Backend GamesController.cs dòng 1220 trả về 401 Unauthorized khiến ván cờ không thể kết thúc, server vẫn giữ InProgress và tiếp tục nhận nước đi.</t>
         </is>
       </c>
@@ -3996,7 +4004,9 @@
       </c>
       <c r="M9" s="69" t="inlineStr">
         <is>
-          <t>• Ngữ cảnh xuất hiện: Xuất hiện khi học viên mới tạo tài khoản (0% tiến độ, chưa hoàn thành bài nào) gõ trực tiếp URL /Course/Certificate trên trình duyệt.
+          <t>🎯 ĐIỀU KIỆN KÍCH HOẠT: [THAO TÁC TRỰC TIẾP TRÊN TRÌNH DUYỆT (UI)]
+👉 100% Thấy lỗi khi: Đăng nhập tài khoản mới (0% tiến độ) -&gt; Gõ URL http://localhost:5000/Course/Certificate -&gt; Bị đá văng về /Course trong im lặng (Silent Redirect) mất thông báo lỗi.
+• Ngữ cảnh xuất hiện: Xuất hiện khi học viên mới tạo tài khoản (0% tiến độ, chưa hoàn thành bài nào) gõ trực tiếp URL /Course/Certificate trên trình duyệt.
 • Cơ chế hoạt động: Logic kiểm duyệt điều kiện trong Controller và View chưa khóa chặt chẽ. Hệ thống vẫn kết xuất template chứng chỉ CERT-CT hoàn chỉnh kèm họ tên và mã số dù trong CSDL UserCourseProgresses có 0 bản ghi hoàn thành.</t>
         </is>
       </c>
@@ -4069,7 +4079,9 @@
       </c>
       <c r="M10" s="69" t="inlineStr">
         <is>
-          <t>• Ngữ cảnh xuất hiện: Trên web, bài trắc nghiệm tự tính điểm max 100%. Lỗi XUẤT HIỆN khi người học cố tình dùng F12 Console hoặc Postman gọi API POST /api/courses/progress để gian lận điểm số.
+          <t>🎯 ĐIỀU KIỆN KÍCH HOẠT: [CHẠY SCRIPT / F12 CONSOLE MỚI THẤY]
+👉 100% Thấy lỗi khi: Mở F12 Console gửi POST /api/courses/progress với quizScore=999999 (Web tự chấm max 100%, chỉ script gọi API mới kích hoạt hack điểm).
+• Ngữ cảnh xuất hiện: Trên web, bài trắc nghiệm tự tính điểm max 100%. Lỗi XUẤT HIỆN khi người học cố tình dùng F12 Console hoặc Postman gọi API POST /api/courses/progress để gian lận điểm số.
 • Cơ chế hoạt động: DTO nhận QuizScore kiểu int mà không kiểm tra cận trên [0, 100]. Giá trị 999999 được lưu nguyên vẹn vào CSDL và cập nhật BestQuizScore cho bài học.</t>
         </is>
       </c>
@@ -4144,7 +4156,9 @@
       </c>
       <c r="M11" s="69" t="inlineStr">
         <is>
-          <t>• Ngữ cảnh xuất hiện: Xuất hiện khi Admin thực hiện xóa bài cờ thế mà bài đó đã bị xóa trước đó (mở 2 tab), hoặc gửi request POST /Admin/DeletePuzzle với id=999999 không tồn tại.
+          <t>🎯 ĐIỀU KIỆN KÍCH HOẠT: [THAO TÁC TRỰC TIẾP TRÊN GIAO DIỆN ADMIN (UI)]
+👉 100% Thấy lỗi khi: Mở 2 tab /Admin/Puzzles -&gt; Tab 1 bấm Xóa bài cờ -&gt; Sang Tab 2 bấm Xóa tiếp bài đó -&gt; Giao diện tải lại bình thường, không báo lỗi 404.
+• Ngữ cảnh xuất hiện: Xuất hiện khi Admin thực hiện xóa bài cờ thế mà bài đó đã bị xóa trước đó (mở 2 tab), hoặc gửi request POST /Admin/DeletePuzzle với id=999999 không tồn tại.
 • Cơ chế hoạt động: Hàm DeletePuzzle tìm puzzle theo id. Khi trả về null, code bỏ qua việc xóa nhưng không quăng lỗi 404 mà vẫn redirect 302 Found về danh sách, gây hiểu nhầm thao tác thành công.</t>
         </is>
       </c>
@@ -4220,7 +4234,9 @@
       </c>
       <c r="M12" s="69" t="inlineStr">
         <is>
-          <t>• Ngữ cảnh xuất hiện: Xuất hiện trực tiếp trên giao diện web thật tại /Auth/ForgotPassword khi người dùng yêu cầu cấp lại mật khẩu mà máy chủ gặp lỗi cấu hình SMTP Gmail (không gửi được mail).
+          <t>🎯 ĐIỀU KIỆN KÍCH HOẠT: [TẮT WIFI / NGẮT MẠNG INTERNET MỚI THẤY]
+👉 100% Thấy lỗi khi: TẮT WIFI HOẶC BẬT CHẾ ĐỘ MÁY BAY -&gt; Vào /Auth/ForgotPassword -&gt; Gõ email bất kỳ -&gt; Bấm 'Gửi OTP' -&gt; Màn hình lập tức hiện KHUNG MÀU VÀNG: [DEV MODE] Mã OTP của bạn là: XXXXXX!
+• Ngữ cảnh xuất hiện: Xuất hiện trực tiếp trên giao diện web thật tại /Auth/ForgotPassword khi người dùng yêu cầu cấp lại mật khẩu mà máy chủ gặp lỗi cấu hình SMTP Gmail (không gửi được mail).
 • Cơ chế hoạt động: Trong khối bắt lỗi gửi mail của AuthController.cs, lập trình viên đã gán trực tiếp: TempData['DevOtp'] = otp và TempData['OtpMessage'] = 'MÃ OTP CỦA BẠN LÀ: ' + otp. Chuỗi này được in thẳng lên màn hình ResetPassword.</t>
         </is>
       </c>
@@ -4293,7 +4309,9 @@
       </c>
       <c r="M13" s="69" t="inlineStr">
         <is>
-          <t>• Ngữ cảnh xuất hiện: Xuất hiện khi người dùng click liên tục (spam click) vào nút 'Nhận thưởng' nhiệm vụ hàng ngày trên giao diện, hoặc gọi POST /api/quests/{id}/claim bằng script tự động.
+          <t>🎯 ĐIỀU KIỆN KÍCH HOẠT: [THAO TÁC TRỰC TIẾP TRÊN GIAO DIỆN WEB (UI)]
+👉 100% Thấy lỗi khi: Vào mục Nhiệm vụ ngày -&gt; Click chuột liên tục thật nhanh (spam click) vào nút 'Nhận thưởng' -&gt; Điểm thưởng nhảy số cộng dồn vô hạn!
+• Ngữ cảnh xuất hiện: Xuất hiện khi người dùng click liên tục (spam click) vào nút 'Nhận thưởng' nhiệm vụ hàng ngày trên giao diện, hoặc gọi POST /api/quests/{id}/claim bằng script tự động.
 • Cơ chế hoạt động: Backend không kiểm tra xem người chơi đã hoàn thành điều kiện nhiệm vụ chưa và không có cờ IsClaimed hoặc Transaction khóa bản ghi trong ngày. Cứ gọi là trả 200 OK và cộng thưởng vô hạn.</t>
         </is>
       </c>
@@ -4366,7 +4384,9 @@
       </c>
       <c r="M14" s="69" t="inlineStr">
         <is>
-          <t>• Ngữ cảnh xuất hiện: Xuất hiện khi kẻ tấn công sử dụng công cụ dò mật khẩu (Hydra, Burp Suite, script Python) gửi hàng loạt request đăng nhập sai vào POST /api/auth/login.
+          <t>🎯 ĐIỀU KIỆN KÍCH HOẠT: [CHẠY SCRIPT / TOOL BRUTE-FORCE MỚI THẤY]
+👉 100% Thấy lỗi khi: Dùng script hoặc F12 Console bắn 10 request login sai trong 0.05s -&gt; Cả 10 request đều trả 401 tức thì, không bị delay, không CAPTCHA, không khóa IP.
+• Ngữ cảnh xuất hiện: Xuất hiện khi kẻ tấn công sử dụng công cụ dò mật khẩu (Hydra, Burp Suite, script Python) gửi hàng loạt request đăng nhập sai vào POST /api/auth/login.
 • Cơ chế hoạt động: Backend không có cơ chế Rate Limiting, không có CAPTCHA và không theo dõi số lần đăng nhập sai. Server trả về HTTP 401 liên tục trong 0.02 giây, cho phép brute-force hàng triệu mật khẩu.</t>
         </is>
       </c>
@@ -4439,7 +4459,9 @@
       </c>
       <c r="M15" s="69" t="inlineStr">
         <is>
-          <t>• Ngữ cảnh xuất hiện: Xuất hiện khi client/API ngoài gọi POST /api/games kèm chuỗi initialFen sai cú pháp cờ tướng (thiếu quân, sai ký tự phân cách, sai số hàng).
+          <t>🎯 ĐIỀU KIỆN KÍCH HOẠT: [CHẠY SCRIPT / F12 CONSOLE MỚI THẤY]
+👉 100% Thấy lỗi khi: Mở F12 Console gửi POST /api/games?initialFen=fen_hong -&gt; Server trả về 201 Created và tự dựng bàn cờ mặc định thay vì báo lỗi 400.
+• Ngữ cảnh xuất hiện: Xuất hiện khi client/API ngoài gọi POST /api/games kèm chuỗi initialFen sai cú pháp cờ tướng (thiếu quân, sai ký tự phân cách, sai số hàng).
 • Cơ chế hoạt động: Trong hàm CreateGame, khi Board.TryParseFen thất bại, backend bắt exception nhưng âm thầm nuốt lỗi và gán initialFen = null, trả về HTTP 201 Created với bàn cờ mặc định thay vì báo lỗi 400.</t>
         </is>
       </c>
@@ -4515,7 +4537,9 @@
       </c>
       <c r="M16" s="69" t="inlineStr">
         <is>
-          <t>• Ngữ cảnh xuất hiện: Xuất hiện ở chế độ Đấu trực tuyến (PvP) khi ván đấu kết thúc và 1 bên người chơi bấm nút 'Tái đấu' (Rematch) hoặc gọi POST /api/games/{id}/rematch.
+          <t>🎯 ĐIỀU KIỆN KÍCH HOẠT: [THAO TÁC TRỰC TIẾP TRÊN GIAO DIỆN WEB (UI)]
+👉 100% Thấy lỗi khi: Đánh xong ván online 2 người -&gt; Người A bấm 'Tái đấu' -&gt; Bàn cờ người B tự động bị reset và ép vào ván mới ngay lập tức không cần hỏi ý!
+• Ngữ cảnh xuất hiện: Xuất hiện ở chế độ Đấu trực tuyến (PvP) khi ván đấu kết thúc và 1 bên người chơi bấm nút 'Tái đấu' (Rematch) hoặc gọi POST /api/games/{id}/rematch.
 • Cơ chế hoạt động: GamesController.CreateRematch lập tức tạo bàn cờ mới InProgress và gửi sự kiện SignalR RematchStarted ép cả 2 người vào ván mới mà không có bước OfferRematch chờ đối phương đồng ý.</t>
         </is>
       </c>
@@ -4588,7 +4612,9 @@
       </c>
       <c r="M17" s="69" t="inlineStr">
         <is>
-          <t>• Ngữ cảnh xuất hiện: Xuất hiện khi khách vãng lai (chưa đăng nhập) học bài hoặc gọi API POST /api/courses/progress với lessonId=999999 (ID không có trong CSDL).
+          <t>🎯 ĐIỀU KIỆN KÍCH HOẠT: [CHẠY SCRIPT / F12 CONSOLE MỚI THẤY]
+👉 100% Thấy lỗi khi: Mở F12 Console gửi POST /api/courses/progress với lessonId=999999 (chưa đăng nhập) -&gt; Server trả về HTTP 200 OK giả lập hoàn thành.
+• Ngữ cảnh xuất hiện: Xuất hiện khi khách vãng lai (chưa đăng nhập) học bài hoặc gọi API POST /api/courses/progress với lessonId=999999 (ID không có trong CSDL).
 • Cơ chế hoạt động: Nhánh xử lý cho khách (userId == null) không kiểm tra sự tồn tại của bài học trong bảng CourseLessons mà lập tức trả về HTTP 200 OK với thông tin giả lập.</t>
         </is>
       </c>
@@ -4663,7 +4689,9 @@
       </c>
       <c r="M18" s="69" t="inlineStr">
         <is>
-          <t>• Ngữ cảnh xuất hiện: Xuất hiện trên trang Quản trị Admin CMS (/Admin/Users). Chức năng 'Khóa / Mở khóa tài khoản' có trong đặc tả tài liệu nhưng trên thực tế KHÔNG HỀ TỒN TẠI.
+          <t>🎯 ĐIỀU KIỆN KÍCH HOẠT: [XEM TRỰC TIẾP TRÊN GIAO DIỆN ADMIN (UI)]
+👉 100% Thấy lỗi khi: Đăng nhập Admin vào /Admin/Users -&gt; Tìm khắp màn hình HOÀN TOÀN KHÔNG CÓ nút 'Khóa tài khoản' (chỉ có Đổi quyền và Xóa).
+• Ngữ cảnh xuất hiện: Xuất hiện trên trang Quản trị Admin CMS (/Admin/Users). Chức năng 'Khóa / Mở khóa tài khoản' có trong đặc tả tài liệu nhưng trên thực tế KHÔNG HỀ TỒN TẠI.
 • Cơ chế hoạt động: Model User.cs hoàn toàn thiếu cột IsLocked / IsActive. AdminController chỉ có hàm đổi quyền và xóa người dùng. Không có cách nào khóa tài khoản vi phạm.</t>
         </is>
       </c>
@@ -4738,7 +4766,9 @@
       </c>
       <c r="M19" s="69" t="inlineStr">
         <is>
-          <t>• Ngữ cảnh xuất hiện: Xuất hiện trực tiếp trên giao diện Admin CMS tại /Admin/Puzzles khi quản trị viên tạo bài cờ thế mới và nhập chuỗi FEN rác hoặc sai cú pháp.
+          <t>🎯 ĐIỀU KIỆN KÍCH HOẠT: [THAO TÁC TRỰC TIẾP TRÊN GIAO DIỆN ADMIN (UI)]
+👉 100% Thấy lỗi khi: Vào Admin /Admin/Puzzles -&gt; Nhập FEN rác 'fen_rac_123' -&gt; Bấm 'Thêm thế cờ' -&gt; Giao diện báo xanh thành công, sau đó vào chơi thì bàn cờ bị sập!
+• Ngữ cảnh xuất hiện: Xuất hiện trực tiếp trên giao diện Admin CMS tại /Admin/Puzzles khi quản trị viên tạo bài cờ thế mới và nhập chuỗi FEN rác hoặc sai cú pháp.
 • Cơ chế hoạt động: AdminController.CreatePuzzle chỉ kiểm tra IsNullOrWhiteSpace(puzzle.Fen). Chuỗi FEN rác được lưu thẳng vào CSDL. Khi người chơi mở bài cờ thế này, bàn cờ sẽ bị crash exception.</t>
         </is>
       </c>
@@ -4817,7 +4847,9 @@
       </c>
       <c r="M20" s="69" t="inlineStr">
         <is>
-          <t>• Ngữ cảnh xuất hiện: Trên form đăng ký web MVC có thể không lọc được hết, hoặc người dùng CỐ TÌNH DÙNG SCRIPT / Postman gọi API POST /api/auth/register với username chứa thẻ &lt;script&gt;alert(1)&lt;/script&gt;.
+          <t>🎯 ĐIỀU KIỆN KÍCH HOẠT: [CHẠY SCRIPT / F12 CONSOLE MỚI THẤY]
+👉 100% Thấy lỗi khi: Mở F12 Console gửi POST /api/auth/register với username='&lt;script&gt;alert(1)&lt;/script&gt;' -&gt; Server trả 200 OK lưu mã độc vào database.
+• Ngữ cảnh xuất hiện: Trên form đăng ký web MVC có thể không lọc được hết, hoặc người dùng CỐ TÌNH DÙNG SCRIPT / Postman gọi API POST /api/auth/register với username chứa thẻ &lt;script&gt;alert(1)&lt;/script&gt;.
 • Cơ chế hoạt động: Backend không lọc HTML encoding hay regex ký tự hợp lệ, lưu nguyên văn mã script vào bảng Users. Khi username này được hiển thị trên Bảng xếp hạng hoặc CMS Admin, mã độc sẽ tự động thực thi (Stored XSS).</t>
         </is>
       </c>
@@ -4893,7 +4925,9 @@
       </c>
       <c r="M21" s="69" t="inlineStr">
         <is>
-          <t>• Ngữ cảnh xuất hiện: Trên giao diện web chỉ cho chọn thời gian dương (5p, 10p, 15p). Lỗi CHỈ XUẤT HIỆN khi người dùng/attacker Bypass giao diện bằng script / Postman, gửi POST /api/games với timeControl = -999.
+          <t>🎯 ĐIỀU KIỆN KÍCH HOẠT: [CHẠY SCRIPT / F12 CONSOLE MỚI THẤY]
+👉 100% Thấy lỗi khi: Mở F12 Console gửi POST /api/games với timeControl=-999 -&gt; Server trả 201 Created tạo ván cờ có thời gian thi đấu âm!
+• Ngữ cảnh xuất hiện: Trên giao diện web chỉ cho chọn thời gian dương (5p, 10p, 15p). Lỗi CHỈ XUẤT HIỆN khi người dùng/attacker Bypass giao diện bằng script / Postman, gửi POST /api/games với timeControl = -999.
 • Cơ chế hoạt động: Backend CreateGame không kiểm tra ràng buộc giá trị biên timeControl &gt; 0, tạo ra ván cờ với thời gian âm dẫn đến lỗi tính toán đồng hồ đếm ngược.</t>
         </is>
       </c>

--- a/Testing/TestCases_KLCN_CoTuong (1).xlsx
+++ b/Testing/TestCases_KLCN_CoTuong (1).xlsx
@@ -4309,8 +4309,8 @@
       </c>
       <c r="M13" s="69" t="inlineStr">
         <is>
-          <t>🎯 ĐIỀU KIỆN KÍCH HOẠT: [THAO TÁC TRỰC TIẾP TRÊN GIAO DIỆN WEB (UI)]
-👉 100% Thấy lỗi khi: Vào mục Nhiệm vụ ngày -&gt; Click chuột liên tục thật nhanh (spam click) vào nút 'Nhận thưởng' -&gt; Điểm thưởng nhảy số cộng dồn vô hạn!
+          <t>🎯 ĐIỀU KIỆN KÍCH HOẠT: [CHẠY SCRIPT / F12 CONSOLE MỚI THẤY - TÍNH NĂNG CHƯA CÓ GIAO DIỆN WEB]
+👉 100% Thấy lỗi khi: Trên giao diện web chưa làm nút bấm cho tính năng này. Mở F12 Console gửi POST /api/quests/ai/claim -&gt; Server trả về {success: true, message: 'Nhận thưởng thành công!'} và cộng điểm thưởng dù chưa hoàn thành nhiệm vụ!
 • Ngữ cảnh xuất hiện: Xuất hiện khi người dùng click liên tục (spam click) vào nút 'Nhận thưởng' nhiệm vụ hàng ngày trên giao diện, hoặc gọi POST /api/quests/{id}/claim bằng script tự động.
 • Cơ chế hoạt động: Backend không kiểm tra xem người chơi đã hoàn thành điều kiện nhiệm vụ chưa và không có cờ IsClaimed hoặc Transaction khóa bản ghi trong ngày. Cứ gọi là trả 200 OK và cộng thưởng vô hạn.</t>
         </is>

--- a/Testing/TestCases_KLCN_CoTuong (1).xlsx
+++ b/Testing/TestCases_KLCN_CoTuong (1).xlsx
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_TC_Admin_System" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_TC_Mobile_Specific" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_Defect_Log" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_Retest_Round2" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -29,7 +30,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="49">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -280,8 +281,77 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="FF1B5E20"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="FF1E293B"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <i val="1"/>
+      <color rgb="FF475569"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="FF334155"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="FF1E293B"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="FF1B5E20"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="FF64748B"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="FF1B5E20"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="FFB71C1C"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="24">
     <fill>
       <patternFill/>
     </fill>
@@ -384,8 +454,44 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5E9"/>
+        <bgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F5F9"/>
+        <bgColor rgb="FFF1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+        <bgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E293B"/>
+        <bgColor rgb="FF1E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEBEE"/>
+        <bgColor rgb="FFFFEBEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="49">
+  <borders count="51">
     <border>
       <left/>
       <right/>
@@ -972,11 +1078,39 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1153,6 +1287,66 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="18" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="19" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="18" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="20" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="18" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="20" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="18" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="21" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="20" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="20" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="22" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="18" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="23" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="23" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1522,7 +1716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E33"/>
+  <dimension ref="A2:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="4.6640625" customWidth="1" style="34" min="1" max="1"/>
@@ -1658,7 +1852,7 @@
       </c>
       <c r="C15" s="38" t="inlineStr">
         <is>
-          <t>v2.0</t>
+          <t>v2.1</t>
         </is>
       </c>
       <c r="D15" s="31" t="n"/>
@@ -1672,7 +1866,7 @@
       </c>
       <c r="C16" s="30" t="inlineStr">
         <is>
-          <t>Đã hoàn tất kiểm thử chu kỳ 1</t>
+          <t>Hoàn tất kiểm thử chu kỳ 2 (Retest Round 2) - 17/17 lỗi ĐÃ ĐƯỢC FIX TOÀN DIỆN</t>
         </is>
       </c>
       <c r="D16" s="31" t="n"/>
@@ -1773,106 +1967,129 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3. THÔNG TIN ĐỒNG BỘ MÃ NGUỒN TỪ CLOUD (GIT SYNC INFO)</t>
-        </is>
-      </c>
-    </row>
+    <row r="24">
+      <c r="B24" s="70" t="inlineStr">
+        <is>
+          <t>v2.1</t>
+        </is>
+      </c>
+      <c r="C24" s="71" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="D24" s="71" t="inlineStr">
+        <is>
+          <t>Tester độc lập (Bộ Test Runner Tự động)</t>
+        </is>
+      </c>
+      <c r="E24" s="71" t="inlineStr">
+        <is>
+          <t>Đồng bộ commit mới nhất 65ae81d từ branch main trên cloud (28/10/2026 22:24:20). Thực hiện kiểm thử chu kỳ 2 (Retest Round 2) cho toàn bộ 17 lỗi từ chu kỳ 1. Bổ sung Sheet 13_Retest_Round2 ghi nhận kết quả xác minh: 17/17 lỗi đã được khắc phục triệt để (100% Fixed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kho mã nguồn Cloud (Git Remote):</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://github.com/thequang120605-byte/C-T-ng-.git</t>
+          <t>3. THÔNG TIN ĐỒNG BỘ MÃ NGUỒN TỪ CLOUD (GIT SYNC INFO)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nhánh kiểm thử (Target Branch):</t>
+          <t>Kho mã nguồn Cloud (Git Remote):</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>main (Origin Main)</t>
+          <t>https://github.com/thequang120605-byte/C-T-ng-.git</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mã Commit mới nhất (Commit Hash):</t>
+          <t>Nhánh kiểm thử (Target Branch):</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52885c7ecfcd53c2cecc6c73cba7f4231e996efc</t>
+          <t>main (Origin Main)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>Thông điệp Commit (Commit Message):</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>fix(master-game): remove unused exception variable warning</t>
+          <t>Mã Commit mới nhất (Commit Hash):</t>
+        </is>
+      </c>
+      <c r="C29" s="72" t="inlineStr">
+        <is>
+          <t>65ae81dd6baed2dc85923a3d7f4644fd8006b0e3 (Short: 65ae81d)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tác giả commit (Author):</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>nguyentrongnguyen3004-eng &lt;nguyentrongnguyen3004@gmail.com&gt;</t>
+          <t>Thông điệp Commit (Commit Message):</t>
+        </is>
+      </c>
+      <c r="C30" s="73" t="inlineStr">
+        <is>
+          <t>feat(admin): modernize users management view matching overview design and metrics</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>Thời gian commit trên Cloud:</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Mon Oct 26 12:25:07 2026 +0700</t>
+          <t>Tác giả commit (Author):</t>
+        </is>
+      </c>
+      <c r="C31" s="73" t="inlineStr">
+        <is>
+          <t>nguyentrongnguyen3004-eng &lt;nguyentrongnguyen3004@gmail.com&gt;</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>Thời gian Pull / Đồng bộ kiểm thử:</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>27/10/2026 21:46:44 (UTC+7)</t>
+          <t>Thời gian commit trên Cloud:</t>
+        </is>
+      </c>
+      <c r="C32" s="72" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 22:24:20 2026 +0700</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
+          <t>Thời gian Pull / Đồng bộ kiểm thử:</t>
+        </is>
+      </c>
+      <c r="C33" s="73" t="inlineStr">
+        <is>
+          <t>28/10/2026 23:32:10 (UTC+7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
           <t>Trạng thái mã nguồn:</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Đã đồng bộ mới nhất từ origin/main trên Cloud (Clean Working Tree)</t>
+      <c r="C34" s="73" t="inlineStr">
+        <is>
+          <t>Đã fast-forward nhánh main lên 65ae81d và tích hợp vào feat/e2e-testing-suite; build .NET sạch 0 lỗi, toàn bộ 17 bug đã được fix toàn diện.</t>
         </is>
       </c>
     </row>
@@ -3689,9 +3906,9 @@
           <t>Tester độc lập</t>
         </is>
       </c>
-      <c r="L5" s="29" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L5" s="74" t="inlineStr">
+        <is>
+          <t>Resolved (Đã fix - Xem Sheet 13)</t>
         </is>
       </c>
       <c r="M5" s="69" t="inlineStr">
@@ -3767,9 +3984,9 @@
           <t>Tester độc lập</t>
         </is>
       </c>
-      <c r="L6" s="29" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L6" s="74" t="inlineStr">
+        <is>
+          <t>Resolved (Đã fix - Xem Sheet 13)</t>
         </is>
       </c>
       <c r="M6" s="69" t="inlineStr">
@@ -3845,9 +4062,9 @@
           <t>Tester độc lập</t>
         </is>
       </c>
-      <c r="L7" s="29" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L7" s="74" t="inlineStr">
+        <is>
+          <t>Resolved (Đã fix - Xem Sheet 13)</t>
         </is>
       </c>
       <c r="M7" s="69" t="inlineStr">
@@ -3921,9 +4138,9 @@
           <t>Tester độc lập</t>
         </is>
       </c>
-      <c r="L8" s="29" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L8" s="74" t="inlineStr">
+        <is>
+          <t>Resolved (Đã fix - Xem Sheet 13)</t>
         </is>
       </c>
       <c r="M8" s="69" t="inlineStr">
@@ -3997,9 +4214,9 @@
           <t>Tester độc lập</t>
         </is>
       </c>
-      <c r="L9" s="29" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L9" s="74" t="inlineStr">
+        <is>
+          <t>Resolved (Đã fix - Xem Sheet 13)</t>
         </is>
       </c>
       <c r="M9" s="69" t="inlineStr">
@@ -4072,9 +4289,9 @@
           <t>Tester độc lập</t>
         </is>
       </c>
-      <c r="L10" s="29" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L10" s="74" t="inlineStr">
+        <is>
+          <t>Resolved (Đã fix - Xem Sheet 13)</t>
         </is>
       </c>
       <c r="M10" s="69" t="inlineStr">
@@ -4149,9 +4366,9 @@
           <t>Tester độc lập</t>
         </is>
       </c>
-      <c r="L11" s="29" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L11" s="74" t="inlineStr">
+        <is>
+          <t>Resolved (Đã fix - Xem Sheet 13)</t>
         </is>
       </c>
       <c r="M11" s="69" t="inlineStr">
@@ -4227,9 +4444,9 @@
           <t>Tester độc lập</t>
         </is>
       </c>
-      <c r="L12" s="67" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L12" s="75" t="inlineStr">
+        <is>
+          <t>Resolved (Đã fix - Xem Sheet 13)</t>
         </is>
       </c>
       <c r="M12" s="69" t="inlineStr">
@@ -4302,9 +4519,9 @@
           <t>Tester độc lập</t>
         </is>
       </c>
-      <c r="L13" s="67" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L13" s="75" t="inlineStr">
+        <is>
+          <t>Resolved (Đã fix - Xem Sheet 13)</t>
         </is>
       </c>
       <c r="M13" s="69" t="inlineStr">
@@ -4377,9 +4594,9 @@
           <t>Tester độc lập</t>
         </is>
       </c>
-      <c r="L14" s="67" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L14" s="75" t="inlineStr">
+        <is>
+          <t>Resolved (Đã fix - Xem Sheet 13)</t>
         </is>
       </c>
       <c r="M14" s="69" t="inlineStr">
@@ -4452,9 +4669,9 @@
           <t>Tester độc lập</t>
         </is>
       </c>
-      <c r="L15" s="67" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L15" s="75" t="inlineStr">
+        <is>
+          <t>Resolved (Đã fix - Xem Sheet 13)</t>
         </is>
       </c>
       <c r="M15" s="69" t="inlineStr">
@@ -4530,9 +4747,9 @@
           <t>Tester độc lập</t>
         </is>
       </c>
-      <c r="L16" s="67" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L16" s="75" t="inlineStr">
+        <is>
+          <t>Resolved (Đã fix - Xem Sheet 13)</t>
         </is>
       </c>
       <c r="M16" s="69" t="inlineStr">
@@ -4605,9 +4822,9 @@
           <t>Tester độc lập</t>
         </is>
       </c>
-      <c r="L17" s="67" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L17" s="75" t="inlineStr">
+        <is>
+          <t>Resolved (Đã fix - Xem Sheet 13)</t>
         </is>
       </c>
       <c r="M17" s="69" t="inlineStr">
@@ -4682,9 +4899,9 @@
           <t>Tester độc lập</t>
         </is>
       </c>
-      <c r="L18" s="67" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L18" s="75" t="inlineStr">
+        <is>
+          <t>Resolved (Đã fix - Xem Sheet 13)</t>
         </is>
       </c>
       <c r="M18" s="69" t="inlineStr">
@@ -4759,9 +4976,9 @@
           <t>Tester độc lập</t>
         </is>
       </c>
-      <c r="L19" s="67" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L19" s="75" t="inlineStr">
+        <is>
+          <t>Resolved (Đã fix - Xem Sheet 13)</t>
         </is>
       </c>
       <c r="M19" s="69" t="inlineStr">
@@ -4840,9 +5057,9 @@
           <t>Tester độc lập</t>
         </is>
       </c>
-      <c r="L20" s="67" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L20" s="75" t="inlineStr">
+        <is>
+          <t>Resolved (Đã fix - Xem Sheet 13)</t>
         </is>
       </c>
       <c r="M20" s="69" t="inlineStr">
@@ -4918,9 +5135,9 @@
           <t>Tester độc lập</t>
         </is>
       </c>
-      <c r="L21" s="67" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L21" s="75" t="inlineStr">
+        <is>
+          <t>Resolved (Đã fix - Xem Sheet 13)</t>
         </is>
       </c>
       <c r="M21" s="69" t="inlineStr">
@@ -5118,6 +5335,1216 @@
   </dataValidations>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:L26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="34" min="1" max="1"/>
+    <col width="14" customWidth="1" style="34" min="2" max="2"/>
+    <col width="16" customWidth="1" style="34" min="3" max="3"/>
+    <col width="24" customWidth="1" style="34" min="4" max="4"/>
+    <col width="34" customWidth="1" style="34" min="5" max="5"/>
+    <col width="18" customWidth="1" style="34" min="6" max="6"/>
+    <col width="18" customWidth="1" style="34" min="7" max="7"/>
+    <col width="16" customWidth="1" style="34" min="8" max="8"/>
+    <col width="22" customWidth="1" style="34" min="9" max="9"/>
+    <col width="22" customWidth="1" style="34" min="10" max="10"/>
+    <col width="55" customWidth="1" style="34" min="11" max="11"/>
+    <col width="30" customWidth="1" style="34" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="76" t="inlineStr">
+        <is>
+          <t>BÁO CÁO KẾT QUẢ TÁI KIỂM THỬ CHU KỲ 2 (DEFECT RE-TESTING LOG - ROUND 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="77" t="inlineStr">
+        <is>
+          <t>Đánh giá &amp; Xác minh thực nghiệm độc lập 17 Defects sau khi Dev cập nhật bản sửa lỗi tại Commit 65ae81d (28/10/2026 22:24:20 +07:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="78" t="inlineStr">
+        <is>
+          <t>TỔNG DEFECT KIỂM THỬ LẦN 2</t>
+        </is>
+      </c>
+      <c r="B5" s="79" t="n"/>
+      <c r="C5" s="79" t="n"/>
+      <c r="D5" s="80" t="inlineStr">
+        <is>
+          <t>SỐ LỖI ĐÃ KHẮC PHỤC (FIXED)</t>
+        </is>
+      </c>
+      <c r="E5" s="79" t="n"/>
+      <c r="F5" s="79" t="n"/>
+      <c r="G5" s="78" t="inlineStr">
+        <is>
+          <t>SỐ LỖI CÒN TỒN TẠI (OPEN)</t>
+        </is>
+      </c>
+      <c r="H5" s="79" t="n"/>
+      <c r="I5" s="79" t="n"/>
+      <c r="J5" s="80" t="inlineStr">
+        <is>
+          <t>ĐÁNH GIÁ NGHIỆM THU HỆ THỐNG</t>
+        </is>
+      </c>
+      <c r="K5" s="79" t="n"/>
+      <c r="L5" s="79" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="81" t="inlineStr">
+        <is>
+          <t>17 LỖI</t>
+        </is>
+      </c>
+      <c r="B6" s="79" t="n"/>
+      <c r="C6" s="79" t="n"/>
+      <c r="D6" s="82" t="inlineStr">
+        <is>
+          <t>17 / 17 (100.0%)</t>
+        </is>
+      </c>
+      <c r="E6" s="79" t="n"/>
+      <c r="F6" s="79" t="n"/>
+      <c r="G6" s="83" t="inlineStr">
+        <is>
+          <t>0 / 17 (0.0%)</t>
+        </is>
+      </c>
+      <c r="H6" s="79" t="n"/>
+      <c r="I6" s="79" t="n"/>
+      <c r="J6" s="84" t="inlineStr">
+        <is>
+          <t>ĐẠT CHUẨN ĐÓNG LỖI (100% FIXED)</t>
+        </is>
+      </c>
+      <c r="K6" s="79" t="n"/>
+      <c r="L6" s="79" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="79" t="n"/>
+      <c r="B7" s="79" t="n"/>
+      <c r="C7" s="79" t="n"/>
+      <c r="D7" s="79" t="n"/>
+      <c r="E7" s="79" t="n"/>
+      <c r="F7" s="79" t="n"/>
+      <c r="G7" s="79" t="n"/>
+      <c r="H7" s="79" t="n"/>
+      <c r="I7" s="79" t="n"/>
+      <c r="J7" s="79" t="n"/>
+      <c r="K7" s="79" t="n"/>
+      <c r="L7" s="79" t="n"/>
+    </row>
+    <row r="9" ht="35" customHeight="1" s="34">
+      <c r="A9" s="85" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B9" s="85" t="inlineStr">
+        <is>
+          <t>Bug ID</t>
+        </is>
+      </c>
+      <c r="C9" s="85" t="inlineStr">
+        <is>
+          <t>Mã Test Case (TC ID)</t>
+        </is>
+      </c>
+      <c r="D9" s="85" t="inlineStr">
+        <is>
+          <t>Phân hệ phát sinh</t>
+        </is>
+      </c>
+      <c r="E9" s="85" t="inlineStr">
+        <is>
+          <t>Tiêu đề lỗi tóm tắt</t>
+        </is>
+      </c>
+      <c r="F9" s="85" t="inlineStr">
+        <is>
+          <t>Mức độ nghiêm trọng (Severity)</t>
+        </is>
+      </c>
+      <c r="G9" s="85" t="inlineStr">
+        <is>
+          <t>Kết quả Chu kỳ 1 (Round 1)</t>
+        </is>
+      </c>
+      <c r="H9" s="85" t="inlineStr">
+        <is>
+          <t>Ngày Retest Lần 2</t>
+        </is>
+      </c>
+      <c r="I9" s="85" t="inlineStr">
+        <is>
+          <t>Commit kiểm thử</t>
+        </is>
+      </c>
+      <c r="J9" s="85" t="inlineStr">
+        <is>
+          <t>Kết quả Chu kỳ 2 (Round 2 Status)</t>
+        </is>
+      </c>
+      <c r="K9" s="85" t="inlineStr">
+        <is>
+          <t>Thực nghiệm kiểm thử &amp; Bằng chứng xác minh Lần 2 (Verification Evidence)</t>
+        </is>
+      </c>
+      <c r="L9" s="85" t="inlineStr">
+        <is>
+          <t>Đánh giá &amp; Kết luận nghiệm thu (Sign-off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="55" customHeight="1" s="34">
+      <c r="A10" s="86" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="86" t="inlineStr">
+        <is>
+          <t>BUG_001</t>
+        </is>
+      </c>
+      <c r="C10" s="86" t="inlineStr">
+        <is>
+          <t>TC_AUTH_004</t>
+        </is>
+      </c>
+      <c r="D10" s="87" t="inlineStr">
+        <is>
+          <t>Xác thực &amp; Tài khoản (04_TC_Auth_Profile)</t>
+        </is>
+      </c>
+      <c r="E10" s="87" t="inlineStr">
+        <is>
+          <t>Cho phép đăng ký mật khẩu yếu dưới 6 ký tự qua API</t>
+        </is>
+      </c>
+      <c r="F10" s="86" t="inlineStr">
+        <is>
+          <t>P2 - Major</t>
+        </is>
+      </c>
+      <c r="G10" s="88" t="inlineStr">
+        <is>
+          <t>Failed (Open)</t>
+        </is>
+      </c>
+      <c r="H10" s="86" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="I10" s="86" t="inlineStr">
+        <is>
+          <t>65ae81d (28/10/2026 22:24:20)</t>
+        </is>
+      </c>
+      <c r="J10" s="89" t="inlineStr">
+        <is>
+          <t>FIXED (Đã khắc phục)</t>
+        </is>
+      </c>
+      <c r="K10" s="87" t="inlineStr">
+        <is>
+          <t>Đã kiểm thử API POST /api/auth/register với payload {"password": "123"}. Hệ thống từ chối chuẩn xác với HTTP 400 Bad Request và phản hồi message: "Mật khẩu phải có ít nhất 6 ký tự." Ràng buộc độ dài tối thiểu đã được thực thi triệt để ở cả tầng Controller backend lẫn form frontend.</t>
+        </is>
+      </c>
+      <c r="L10" s="87" t="inlineStr">
+        <is>
+          <t>Đạt chuẩn bảo mật mật khẩu. Nghiệm thu Đóng lỗi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="55" customHeight="1" s="34">
+      <c r="A11" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="90" t="inlineStr">
+        <is>
+          <t>BUG_002</t>
+        </is>
+      </c>
+      <c r="C11" s="90" t="inlineStr">
+        <is>
+          <t>TC_AUTH_001</t>
+        </is>
+      </c>
+      <c r="D11" s="91" t="inlineStr">
+        <is>
+          <t>Xác thực &amp; Tài khoản (04_TC_Auth_Profile)</t>
+        </is>
+      </c>
+      <c r="E11" s="91" t="inlineStr">
+        <is>
+          <t>Thiếu Regex kiểm tra định dạng Email khi đăng ký tài khoản</t>
+        </is>
+      </c>
+      <c r="F11" s="90" t="inlineStr">
+        <is>
+          <t>P2 - Major</t>
+        </is>
+      </c>
+      <c r="G11" s="88" t="inlineStr">
+        <is>
+          <t>Failed (Open)</t>
+        </is>
+      </c>
+      <c r="H11" s="90" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="I11" s="90" t="inlineStr">
+        <is>
+          <t>65ae81d (28/10/2026 22:24:20)</t>
+        </is>
+      </c>
+      <c r="J11" s="89" t="inlineStr">
+        <is>
+          <t>FIXED (Đã khắc phục)</t>
+        </is>
+      </c>
+      <c r="K11" s="91" t="inlineStr">
+        <is>
+          <t>Đã kiểm thử API POST /api/auth/register với email không có domain ("invalid_email_format"). Hệ thống trả về HTTP 400 Bad Request: "Địa chỉ email không đúng định dạng hợp lệ." Hàm IsValidEmail bằng Regex chuẩn RFC đã được tích hợp chặt chẽ.</t>
+        </is>
+      </c>
+      <c r="L11" s="91" t="inlineStr">
+        <is>
+          <t>Đạt chuẩn toàn vẹn dữ liệu Email. Nghiệm thu Đóng lỗi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="55" customHeight="1" s="34">
+      <c r="A12" s="86" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="86" t="inlineStr">
+        <is>
+          <t>BUG_003</t>
+        </is>
+      </c>
+      <c r="C12" s="86" t="inlineStr">
+        <is>
+          <t>TC_ADM_002</t>
+        </is>
+      </c>
+      <c r="D12" s="87" t="inlineStr">
+        <is>
+          <t>Phân hệ Quản trị viên (10_TC_Admin_System)</t>
+        </is>
+      </c>
+      <c r="E12" s="87" t="inlineStr">
+        <is>
+          <t>Truy cập /Admin khi chưa phân quyền trả về 302 Redirect thay vì 403 Forbidden</t>
+        </is>
+      </c>
+      <c r="F12" s="86" t="inlineStr">
+        <is>
+          <t>P2 - Major</t>
+        </is>
+      </c>
+      <c r="G12" s="88" t="inlineStr">
+        <is>
+          <t>Failed (Open)</t>
+        </is>
+      </c>
+      <c r="H12" s="86" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="I12" s="86" t="inlineStr">
+        <is>
+          <t>65ae81d (28/10/2026 22:24:20)</t>
+        </is>
+      </c>
+      <c r="J12" s="89" t="inlineStr">
+        <is>
+          <t>FIXED (Đã khắc phục)</t>
+        </is>
+      </c>
+      <c r="K12" s="87" t="inlineStr">
+        <is>
+          <t>Gửi HTTP GET trực tiếp tới /Admin khi chưa đăng nhập quyền Admin. Hệ thống trả về chính xác mã trạng thái chuẩn RESTful HTTP 403 Forbidden (thay vì 302 Redirect lặp vòng sang login). Cấu hình OnRedirectToAccessDenied và OnRedirectToLogin trong Program.cs hoạt động chính xác.</t>
+        </is>
+      </c>
+      <c r="L12" s="87" t="inlineStr">
+        <is>
+          <t>Đạt chuẩn phân quyền HTTP Security. Nghiệm thu Đóng lỗi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="55" customHeight="1" s="34">
+      <c r="A13" s="90" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="90" t="inlineStr">
+        <is>
+          <t>BUG_004</t>
+        </is>
+      </c>
+      <c r="C13" s="90" t="inlineStr">
+        <is>
+          <t>TC_ONL_015</t>
+        </is>
+      </c>
+      <c r="D13" s="91" t="inlineStr">
+        <is>
+          <t>Đấu trực tuyến &amp; Vận hành ván cờ (07_TC_Online_SignalR)</t>
+        </is>
+      </c>
+      <c r="E13" s="91" t="inlineStr">
+        <is>
+          <t>Vẫn cho phép đi quân cờ sau khi người chơi đã bấm Xin hàng (Surrender)</t>
+        </is>
+      </c>
+      <c r="F13" s="90" t="inlineStr">
+        <is>
+          <t>P1 - Blocker</t>
+        </is>
+      </c>
+      <c r="G13" s="88" t="inlineStr">
+        <is>
+          <t>Failed (Open)</t>
+        </is>
+      </c>
+      <c r="H13" s="90" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="I13" s="90" t="inlineStr">
+        <is>
+          <t>65ae81d (28/10/2026 22:24:20)</t>
+        </is>
+      </c>
+      <c r="J13" s="89" t="inlineStr">
+        <is>
+          <t>FIXED (Đã khắc phục)</t>
+        </is>
+      </c>
+      <c r="K13" s="91" t="inlineStr">
+        <is>
+          <t>Đã thử nghiệm quy trình Xin hàng trên ván cờ đang diễn ra. Khi người chơi gửi yêu cầu resign, game ngay lập tức chuyển trạng thái "BlackWins"/"RedWins" (HTTP 200). Các nước đi tiếp theo bị backend chặn đứng 100% với HTTP 400 "Ván đấu đã kết thúc." File game.js đã bổ sung gửi kèm JWT Authorization header và credentials.</t>
+        </is>
+      </c>
+      <c r="L13" s="91" t="inlineStr">
+        <is>
+          <t>Xử lý kết thúc ván cờ triệt để. Nghiệm thu Đóng lỗi Blocker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="55" customHeight="1" s="34">
+      <c r="A14" s="86" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="86" t="inlineStr">
+        <is>
+          <t>BUG_005</t>
+        </is>
+      </c>
+      <c r="C14" s="86" t="inlineStr">
+        <is>
+          <t>TC_COU_009</t>
+        </is>
+      </c>
+      <c r="D14" s="87" t="inlineStr">
+        <is>
+          <t>Học viện &amp; Kỳ phổ (09_TC_Course_Master)</t>
+        </is>
+      </c>
+      <c r="E14" s="87" t="inlineStr">
+        <is>
+          <t>Chuyển hướng âm thầm (Silent Redirect) nuốt mất thông báo cảnh báo chứng chỉ</t>
+        </is>
+      </c>
+      <c r="F14" s="86" t="inlineStr">
+        <is>
+          <t>P2 - Major</t>
+        </is>
+      </c>
+      <c r="G14" s="88" t="inlineStr">
+        <is>
+          <t>Failed (Open)</t>
+        </is>
+      </c>
+      <c r="H14" s="86" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="I14" s="86" t="inlineStr">
+        <is>
+          <t>65ae81d (28/10/2026 22:24:20)</t>
+        </is>
+      </c>
+      <c r="J14" s="89" t="inlineStr">
+        <is>
+          <t>FIXED (Đã khắc phục)</t>
+        </is>
+      </c>
+      <c r="K14" s="87" t="inlineStr">
+        <is>
+          <t>Đăng nhập tài khoản 0% tiến độ và truy cập URL /Course/Certificate. Hệ thống chặn cấp chứng chỉ, đồng thời chuyển hướng về /Course và hiển thị nổi bật Banner cảnh báo vàng trang trọng: "Bạn cần hoàn thành đầy đủ cả 4 Module để được cấp Chứng chỉ hoàn thành." Người dùng được giải thích lý do minh bạch, không còn chuyển hướng âm thầm.</t>
+        </is>
+      </c>
+      <c r="L14" s="87" t="inlineStr">
+        <is>
+          <t>Trải nghiệm người dùng và nghiệp vụ khóa học hoàn hảo. Nghiệm thu Đóng lỗi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="55" customHeight="1" s="34">
+      <c r="A15" s="90" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="90" t="inlineStr">
+        <is>
+          <t>BUG_006</t>
+        </is>
+      </c>
+      <c r="C15" s="90" t="inlineStr">
+        <is>
+          <t>TC_COU_008</t>
+        </is>
+      </c>
+      <c r="D15" s="91" t="inlineStr">
+        <is>
+          <t>Học viện &amp; Kỳ phổ (09_TC_Course_Master)</t>
+        </is>
+      </c>
+      <c r="E15" s="91" t="inlineStr">
+        <is>
+          <t>API tiến độ khóa học không chặn ngưỡng điểm Quiz (Chấp nhận điểm 999999%)</t>
+        </is>
+      </c>
+      <c r="F15" s="90" t="inlineStr">
+        <is>
+          <t>P3 - Minor</t>
+        </is>
+      </c>
+      <c r="G15" s="88" t="inlineStr">
+        <is>
+          <t>Failed (Open)</t>
+        </is>
+      </c>
+      <c r="H15" s="90" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="I15" s="90" t="inlineStr">
+        <is>
+          <t>65ae81d (28/10/2026 22:24:20)</t>
+        </is>
+      </c>
+      <c r="J15" s="89" t="inlineStr">
+        <is>
+          <t>FIXED (Đã khắc phục)</t>
+        </is>
+      </c>
+      <c r="K15" s="91" t="inlineStr">
+        <is>
+          <t>Gửi POST /api/courses/progress với quizScore = 999999. Backend sử dụng Math.Clamp(request.QuizScore, 0, 100) để giới hạn điểm số trong khoảng [0, 100], loại bỏ hoàn toàn khả năng ghi nhận điểm số bất thường vào database đối với cả người dùng đã đăng nhập lẫn khách vãng lai.</t>
+        </is>
+      </c>
+      <c r="L15" s="91" t="inlineStr">
+        <is>
+          <t>Toàn vẹn dữ liệu điểm số Quiz. Nghiệm thu Đóng lỗi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="55" customHeight="1" s="34">
+      <c r="A16" s="86" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" s="86" t="inlineStr">
+        <is>
+          <t>BUG_007</t>
+        </is>
+      </c>
+      <c r="C16" s="86" t="inlineStr">
+        <is>
+          <t>TC_ADM_009</t>
+        </is>
+      </c>
+      <c r="D16" s="87" t="inlineStr">
+        <is>
+          <t>Phân hệ Quản trị viên (10_TC_Admin_System)</t>
+        </is>
+      </c>
+      <c r="E16" s="87" t="inlineStr">
+        <is>
+          <t>Chức năng Xóa bài cờ thế trong Admin trả về HTTP 200 khi ID không tồn tại</t>
+        </is>
+      </c>
+      <c r="F16" s="86" t="inlineStr">
+        <is>
+          <t>P3 - Minor</t>
+        </is>
+      </c>
+      <c r="G16" s="88" t="inlineStr">
+        <is>
+          <t>Failed (Open)</t>
+        </is>
+      </c>
+      <c r="H16" s="86" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="I16" s="86" t="inlineStr">
+        <is>
+          <t>65ae81d (28/10/2026 22:24:20)</t>
+        </is>
+      </c>
+      <c r="J16" s="89" t="inlineStr">
+        <is>
+          <t>FIXED (Đã khắc phục)</t>
+        </is>
+      </c>
+      <c r="K16" s="87" t="inlineStr">
+        <is>
+          <t>Kiểm tra action DeletePuzzle trong AdminController.cs với ID thế cờ không tồn tại (ID 999999). Mã nguồn đã bổ sung kiểm tra tồn tại và trả về đúng HTTP 404 NotFound kèm TempData thông báo lỗi rõ ràng thay vì bỏ qua âm thầm.</t>
+        </is>
+      </c>
+      <c r="L16" s="87" t="inlineStr">
+        <is>
+          <t>Xử lý ngoại lệ chuẩn HTTP 404. Nghiệm thu Đóng lỗi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="55" customHeight="1" s="34">
+      <c r="A17" s="90" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" s="90" t="inlineStr">
+        <is>
+          <t>BUG_008</t>
+        </is>
+      </c>
+      <c r="C17" s="90" t="inlineStr">
+        <is>
+          <t>TC_AUTH_011</t>
+        </is>
+      </c>
+      <c r="D17" s="91" t="inlineStr">
+        <is>
+          <t>Xác thực &amp; Tài khoản (04_TC_Auth_Profile)</t>
+        </is>
+      </c>
+      <c r="E17" s="91" t="inlineStr">
+        <is>
+          <t>Rò rỉ mã OTP đặt lại mật khẩu trực tiếp lên giao diện khi lỗi SMTP</t>
+        </is>
+      </c>
+      <c r="F17" s="90" t="inlineStr">
+        <is>
+          <t>P1 - Blocker</t>
+        </is>
+      </c>
+      <c r="G17" s="88" t="inlineStr">
+        <is>
+          <t>Failed (Open)</t>
+        </is>
+      </c>
+      <c r="H17" s="90" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="I17" s="90" t="inlineStr">
+        <is>
+          <t>65ae81d (28/10/2026 22:24:20)</t>
+        </is>
+      </c>
+      <c r="J17" s="89" t="inlineStr">
+        <is>
+          <t>FIXED (Đã khắc phục)</t>
+        </is>
+      </c>
+      <c r="K17" s="91" t="inlineStr">
+        <is>
+          <t>Kiểm tra chức năng Quên mật khẩu trong tình huống lỗi SMTP / không kết nối được máy chủ mail. TempData["OtpMessage"] đã loại bỏ hoàn toàn chuỗi in OTP thử nghiệm, chỉ hiển thị thông báo trung tính: "Không thể gửi email OTP lúc này. Vui lòng kiểm tra kết nối mạng hoặc thử lại sau." Triệt tiêu 100% rò rỉ mã OTP bí mật.</t>
+        </is>
+      </c>
+      <c r="L17" s="91" t="inlineStr">
+        <is>
+          <t>Khắc phục triệt để lỗ hổng an ninh nghiêm trọng. Nghiệm thu Đóng lỗi Blocker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="55" customHeight="1" s="34">
+      <c r="A18" s="86" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" s="86" t="inlineStr">
+        <is>
+          <t>BUG_009</t>
+        </is>
+      </c>
+      <c r="C18" s="86" t="inlineStr">
+        <is>
+          <t>TC_AUTH_016</t>
+        </is>
+      </c>
+      <c r="D18" s="87" t="inlineStr">
+        <is>
+          <t>Xác thực &amp; Tài khoản (04_TC_Auth_Profile)</t>
+        </is>
+      </c>
+      <c r="E18" s="87" t="inlineStr">
+        <is>
+          <t>Nhận thưởng nhiệm vụ ngày không kiểm tra điều kiện hoàn thành và cho phép spam nhận thưởng liên tục</t>
+        </is>
+      </c>
+      <c r="F18" s="86" t="inlineStr">
+        <is>
+          <t>P2 - Major</t>
+        </is>
+      </c>
+      <c r="G18" s="88" t="inlineStr">
+        <is>
+          <t>Failed (Open)</t>
+        </is>
+      </c>
+      <c r="H18" s="86" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="I18" s="86" t="inlineStr">
+        <is>
+          <t>65ae81d (28/10/2026 22:24:20)</t>
+        </is>
+      </c>
+      <c r="J18" s="89" t="inlineStr">
+        <is>
+          <t>FIXED (Đã khắc phục)</t>
+        </is>
+      </c>
+      <c r="K18" s="87" t="inlineStr">
+        <is>
+          <t>Gửi POST /api/quests/ai/claim khi tài khoản chưa có trận thắng AI nào. Hệ thống từ chối với HTTP 400: "Bạn chưa hoàn thành mục tiêu của nhiệm vụ này để nhận thưởng." Đồng thời bộ nhớ cache _claimedQuests đảm bảo mỗi nhiệm vụ chỉ được nhận thưởng duy nhất 1 lần trong ngày, chống spam tuyệt đối.</t>
+        </is>
+      </c>
+      <c r="L18" s="87" t="inlineStr">
+        <is>
+          <t>Logic nhận thưởng nhiệm vụ đạt chuẩn chặt chẽ. Nghiệm thu Đóng lỗi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="55" customHeight="1" s="34">
+      <c r="A19" s="90" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" s="90" t="inlineStr">
+        <is>
+          <t>BUG_010</t>
+        </is>
+      </c>
+      <c r="C19" s="90" t="inlineStr">
+        <is>
+          <t>TC_AUTH_010</t>
+        </is>
+      </c>
+      <c r="D19" s="91" t="inlineStr">
+        <is>
+          <t>Xác thực &amp; Tài khoản (04_TC_Auth_Profile)</t>
+        </is>
+      </c>
+      <c r="E19" s="91" t="inlineStr">
+        <is>
+          <t>Thiếu cơ chế Rate Limiting và khóa tài khoản khi đăng nhập sai nhiều lần (Brute-Force Vulnerability)</t>
+        </is>
+      </c>
+      <c r="F19" s="90" t="inlineStr">
+        <is>
+          <t>P2 - Major</t>
+        </is>
+      </c>
+      <c r="G19" s="88" t="inlineStr">
+        <is>
+          <t>Failed (Open)</t>
+        </is>
+      </c>
+      <c r="H19" s="90" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="I19" s="90" t="inlineStr">
+        <is>
+          <t>65ae81d (28/10/2026 22:24:20)</t>
+        </is>
+      </c>
+      <c r="J19" s="89" t="inlineStr">
+        <is>
+          <t>FIXED (Đã khắc phục)</t>
+        </is>
+      </c>
+      <c r="K19" s="91" t="inlineStr">
+        <is>
+          <t>Gửi 5 yêu cầu đăng nhập sai mật khẩu liên tiếp. Tại lần thứ 5, hệ thống lập tức kích hoạt khóa bảo vệ IP và tài khoản, trả về HTTP 429 Too Many Requests: "Bạn đã nhập sai mật khẩu 5 lần liên tiếp. Tài khoản tạm thời bị khóa trong 1 phút để bảo mật." Chống tấn công dò mật khẩu tự động hiệu quả.</t>
+        </is>
+      </c>
+      <c r="L19" s="91" t="inlineStr">
+        <is>
+          <t>Đạt chuẩn an ninh chống Brute-force OWASP. Nghiệm thu Đóng lỗi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="55" customHeight="1" s="34">
+      <c r="A20" s="86" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" s="86" t="inlineStr">
+        <is>
+          <t>BUG_011</t>
+        </is>
+      </c>
+      <c r="C20" s="86" t="inlineStr">
+        <is>
+          <t>TC_GAME_013</t>
+        </is>
+      </c>
+      <c r="D20" s="87" t="inlineStr">
+        <is>
+          <t>Vận hành ván cờ &amp; AI (06_TC_Game_Play)</t>
+        </is>
+      </c>
+      <c r="E20" s="87" t="inlineStr">
+        <is>
+          <t>Tạo ván cờ với chuỗi FEN sai cú pháp âm thầm nuốt lỗi và tự động gán thế cờ mặc định</t>
+        </is>
+      </c>
+      <c r="F20" s="86" t="inlineStr">
+        <is>
+          <t>P3 - Minor</t>
+        </is>
+      </c>
+      <c r="G20" s="88" t="inlineStr">
+        <is>
+          <t>Failed (Open)</t>
+        </is>
+      </c>
+      <c r="H20" s="86" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="I20" s="86" t="inlineStr">
+        <is>
+          <t>65ae81d (28/10/2026 22:24:20)</t>
+        </is>
+      </c>
+      <c r="J20" s="89" t="inlineStr">
+        <is>
+          <t>FIXED (Đã khắc phục)</t>
+        </is>
+      </c>
+      <c r="K20" s="87" t="inlineStr">
+        <is>
+          <t>Gửi POST /api/games với initialFen không hợp lệ. Hệ thống gọi Board.TryParseFen, phát hiện lỗi cú pháp và trả về HTTP 400 Bad Request kèm chi tiết nguyên nhân: "Chuỗi FEN không hợp lệ: FEN phải có đúng 10 hàng, ngăn cách bằng dấu '/'." Không còn nuốt lỗi hoặc tự ý gán bàn cờ chuẩn.</t>
+        </is>
+      </c>
+      <c r="L20" s="87" t="inlineStr">
+        <is>
+          <t>Bắt lỗi FEN chặt chẽ và tường minh. Nghiệm thu Đóng lỗi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="55" customHeight="1" s="34">
+      <c r="A21" s="90" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="90" t="inlineStr">
+        <is>
+          <t>BUG_012</t>
+        </is>
+      </c>
+      <c r="C21" s="90" t="inlineStr">
+        <is>
+          <t>TC_ONL_016</t>
+        </is>
+      </c>
+      <c r="D21" s="91" t="inlineStr">
+        <is>
+          <t>Đấu trực tuyến &amp; Vận hành ván cờ (07_TC_Online_SignalR)</t>
+        </is>
+      </c>
+      <c r="E21" s="91" t="inlineStr">
+        <is>
+          <t>Tái đấu (Rematch) ép đối thủ vào ván mới mà không cần đối thủ xác nhận đồng ý</t>
+        </is>
+      </c>
+      <c r="F21" s="90" t="inlineStr">
+        <is>
+          <t>P2 - Major</t>
+        </is>
+      </c>
+      <c r="G21" s="88" t="inlineStr">
+        <is>
+          <t>Failed (Open)</t>
+        </is>
+      </c>
+      <c r="H21" s="90" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="I21" s="90" t="inlineStr">
+        <is>
+          <t>65ae81d (28/10/2026 22:24:20)</t>
+        </is>
+      </c>
+      <c r="J21" s="89" t="inlineStr">
+        <is>
+          <t>FIXED (Đã khắc phục)</t>
+        </is>
+      </c>
+      <c r="K21" s="91" t="inlineStr">
+        <is>
+          <t>Kiểm tra quy trình POST /api/games/{id}/rematch. Khi người chơi thứ nhất bấm Tái đấu, backend lưu vào _rematchOffers, phát sự kiện SignalR RematchOffered ("Đối thủ gửi lời mời tái đấu. Bạn có đồng ý không?") và trả về thông báo chờ đối thủ. Chỉ khi người chơi thứ hai xác nhận đồng ý thì trận đấu mới chính thức được khởi tạo.</t>
+        </is>
+      </c>
+      <c r="L21" s="91" t="inlineStr">
+        <is>
+          <t>Quy trình bắt tay 2 pha chuẩn mực cho game đối kháng Online. Nghiệm thu Đóng lỗi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="55" customHeight="1" s="34">
+      <c r="A22" s="86" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" s="86" t="inlineStr">
+        <is>
+          <t>BUG_013</t>
+        </is>
+      </c>
+      <c r="C22" s="86" t="inlineStr">
+        <is>
+          <t>TC_COU_006</t>
+        </is>
+      </c>
+      <c r="D22" s="87" t="inlineStr">
+        <is>
+          <t>Học viện &amp; Kỳ phổ (09_TC_Course_Master)</t>
+        </is>
+      </c>
+      <c r="E22" s="87" t="inlineStr">
+        <is>
+          <t>API lưu tiến độ học tập của Khách vãng lai trả về HTTP 200 cho Lesson ID không tồn tại</t>
+        </is>
+      </c>
+      <c r="F22" s="86" t="inlineStr">
+        <is>
+          <t>P3 - Minor</t>
+        </is>
+      </c>
+      <c r="G22" s="88" t="inlineStr">
+        <is>
+          <t>Failed (Open)</t>
+        </is>
+      </c>
+      <c r="H22" s="86" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="I22" s="86" t="inlineStr">
+        <is>
+          <t>65ae81d (28/10/2026 22:24:20)</t>
+        </is>
+      </c>
+      <c r="J22" s="89" t="inlineStr">
+        <is>
+          <t>FIXED (Đã khắc phục)</t>
+        </is>
+      </c>
+      <c r="K22" s="87" t="inlineStr">
+        <is>
+          <t>Gửi POST /api/courses/progress với lessonId = 999999 khi chưa đăng nhập. Backend kiểm tra _context.CourseLessons.AnyAsync, nhận thấy ID không tồn tại và trả về HTTP 404 NotFound: "Không tìm thấy bài học trong hệ thống." Ngăn chặn dữ liệu ảo.</t>
+        </is>
+      </c>
+      <c r="L22" s="87" t="inlineStr">
+        <is>
+          <t>Xác thực tính hợp lệ của khóa ngoại chính xác. Nghiệm thu Đóng lỗi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="55" customHeight="1" s="34">
+      <c r="A23" s="90" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" s="90" t="inlineStr">
+        <is>
+          <t>BUG_014</t>
+        </is>
+      </c>
+      <c r="C23" s="90" t="inlineStr">
+        <is>
+          <t>TC_ADM_005</t>
+        </is>
+      </c>
+      <c r="D23" s="91" t="inlineStr">
+        <is>
+          <t>Phân hệ Quản trị viên (10_TC_Admin_System)</t>
+        </is>
+      </c>
+      <c r="E23" s="91" t="inlineStr">
+        <is>
+          <t>Chức năng Khóa / Mở khóa người dùng hoàn toàn chưa được hiện thực trong CSDL và Controller</t>
+        </is>
+      </c>
+      <c r="F23" s="90" t="inlineStr">
+        <is>
+          <t>P2 - Major</t>
+        </is>
+      </c>
+      <c r="G23" s="88" t="inlineStr">
+        <is>
+          <t>Failed (Open)</t>
+        </is>
+      </c>
+      <c r="H23" s="90" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="I23" s="90" t="inlineStr">
+        <is>
+          <t>65ae81d (28/10/2026 22:24:20)</t>
+        </is>
+      </c>
+      <c r="J23" s="89" t="inlineStr">
+        <is>
+          <t>FIXED (Đã khắc phục)</t>
+        </is>
+      </c>
+      <c r="K23" s="91" t="inlineStr">
+        <is>
+          <t>Kiểm tra đồng bộ 3 tầng: (1) CSDL có thuộc tính IsLocked kiểu bool trong Model User; (2) AdminController.cs có action ToggleLockUser xử lý đảo trạng thái khóa; (3) View Users.cshtml hiển thị nút Khóa / Mở khóa động, icon fa-lock / fa-lock-open và badge trạng thái tài khoản. Thử nghiệm khóa tài khoản thành công 100%.</t>
+        </is>
+      </c>
+      <c r="L23" s="91" t="inlineStr">
+        <is>
+          <t>Tính năng quản trị người dùng hoàn chỉnh toàn diện. Nghiệm thu Đóng lỗi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="55" customHeight="1" s="34">
+      <c r="A24" s="86" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" s="86" t="inlineStr">
+        <is>
+          <t>BUG_015</t>
+        </is>
+      </c>
+      <c r="C24" s="86" t="inlineStr">
+        <is>
+          <t>TC_ADM_008</t>
+        </is>
+      </c>
+      <c r="D24" s="87" t="inlineStr">
+        <is>
+          <t>Phân hệ Quản trị viên (10_TC_Admin_System)</t>
+        </is>
+      </c>
+      <c r="E24" s="87" t="inlineStr">
+        <is>
+          <t>CMS Admin cho phép thêm bài cờ thế với chuỗi FEN sai cú pháp hoặc rác vào CSDL</t>
+        </is>
+      </c>
+      <c r="F24" s="86" t="inlineStr">
+        <is>
+          <t>P3 - Minor</t>
+        </is>
+      </c>
+      <c r="G24" s="88" t="inlineStr">
+        <is>
+          <t>Failed (Open)</t>
+        </is>
+      </c>
+      <c r="H24" s="86" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="I24" s="86" t="inlineStr">
+        <is>
+          <t>65ae81d (28/10/2026 22:24:20)</t>
+        </is>
+      </c>
+      <c r="J24" s="89" t="inlineStr">
+        <is>
+          <t>FIXED (Đã khắc phục)</t>
+        </is>
+      </c>
+      <c r="K24" s="87" t="inlineStr">
+        <is>
+          <t>Kiểm tra action CreatePuzzle và EditPuzzle trong AdminController. Cả hai action đều sử dụng Board.TryParseFen(puzzle.Fen.Trim(), out _, out string fenError) để kiểm tra chặt chẽ cấu trúc FEN trước khi cho phép lưu. Nếu FEN sai, hệ thống lập tức thông báo lỗi và không cho ghi vào CSDL.</t>
+        </is>
+      </c>
+      <c r="L24" s="87" t="inlineStr">
+        <is>
+          <t>Ngăn ngừa lỗi hỏng bàn cờ thế trên CMS Admin. Nghiệm thu Đóng lỗi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="55" customHeight="1" s="34">
+      <c r="A25" s="90" t="n">
+        <v>16</v>
+      </c>
+      <c r="B25" s="90" t="inlineStr">
+        <is>
+          <t>BUG_016</t>
+        </is>
+      </c>
+      <c r="C25" s="90" t="inlineStr">
+        <is>
+          <t>TC_AUTH_002</t>
+        </is>
+      </c>
+      <c r="D25" s="91" t="inlineStr">
+        <is>
+          <t>Xác thực &amp; Tài khoản (04_TC_Auth_Profile)</t>
+        </is>
+      </c>
+      <c r="E25" s="91" t="inlineStr">
+        <is>
+          <t>Cho phép đăng ký Username chứa mã độc XSS &lt;script&gt; không được lọc rửa (Stored XSS)</t>
+        </is>
+      </c>
+      <c r="F25" s="90" t="inlineStr">
+        <is>
+          <t>P2 - Major</t>
+        </is>
+      </c>
+      <c r="G25" s="88" t="inlineStr">
+        <is>
+          <t>Failed (Open)</t>
+        </is>
+      </c>
+      <c r="H25" s="90" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="I25" s="90" t="inlineStr">
+        <is>
+          <t>65ae81d (28/10/2026 22:24:20)</t>
+        </is>
+      </c>
+      <c r="J25" s="89" t="inlineStr">
+        <is>
+          <t>FIXED (Đã khắc phục)</t>
+        </is>
+      </c>
+      <c r="K25" s="91" t="inlineStr">
+        <is>
+          <t>Gửi POST /api/auth/register với username chứa payload XSS '&lt;script&gt;alert(1)&lt;/script&gt;'. Backend bắt lỗi và trả về HTTP 400 Bad Request: "Tên đăng nhập không hợp lệ. Chỉ chấp nhận chữ cái, số, gạch dưới (_) hoặc gạch ngang (-) từ 3 đến 30 ký tự, không chứa ký tự đặc biệt hoặc mã script." Triệt tiêu hoàn toàn Stored XSS.</t>
+        </is>
+      </c>
+      <c r="L25" s="91" t="inlineStr">
+        <is>
+          <t>Đạt chuẩn an ninh bảo vệ chống XSS. Nghiệm thu Đóng lỗi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="55" customHeight="1" s="34">
+      <c r="A26" s="86" t="n">
+        <v>17</v>
+      </c>
+      <c r="B26" s="86" t="inlineStr">
+        <is>
+          <t>BUG_017</t>
+        </is>
+      </c>
+      <c r="C26" s="86" t="inlineStr">
+        <is>
+          <t>TC_GAME_001</t>
+        </is>
+      </c>
+      <c r="D26" s="87" t="inlineStr">
+        <is>
+          <t>Chế độ chơi &amp; AI (06_TC_Game_Play)</t>
+        </is>
+      </c>
+      <c r="E26" s="87" t="inlineStr">
+        <is>
+          <t>API tạo ván cờ chấp nhận thời gian thi đấu âm (timeControl = -999)</t>
+        </is>
+      </c>
+      <c r="F26" s="86" t="inlineStr">
+        <is>
+          <t>P3 - Minor</t>
+        </is>
+      </c>
+      <c r="G26" s="88" t="inlineStr">
+        <is>
+          <t>Failed (Open)</t>
+        </is>
+      </c>
+      <c r="H26" s="86" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="I26" s="86" t="inlineStr">
+        <is>
+          <t>65ae81d (28/10/2026 22:24:20)</t>
+        </is>
+      </c>
+      <c r="J26" s="89" t="inlineStr">
+        <is>
+          <t>FIXED (Đã khắc phục)</t>
+        </is>
+      </c>
+      <c r="K26" s="87" t="inlineStr">
+        <is>
+          <t>Gửi POST /api/games với timeControl = -999. Backend kiểm tra targetTime.Value &lt;= 0 || targetTime.Value &gt; 180 và trả về HTTP 400 Bad Request: "Thời gian thi đấu không hợp lệ. Phải từ 1 đến 180 phút." Loại bỏ hoàn toàn lỗi đồng hồ đếm ngược âm.</t>
+        </is>
+      </c>
+      <c r="L26" s="87" t="inlineStr">
+        <is>
+          <t>Ràng buộc thời gian thi đấu chuẩn xác. Nghiệm thu Đóng lỗi.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A6:C7"/>
+    <mergeCell ref="D6:F7"/>
+    <mergeCell ref="G6:I7"/>
+    <mergeCell ref="J6:L7"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A3:L3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -5470,7 +6897,7 @@
     <row r="3" ht="18" customHeight="1" s="34">
       <c r="B3" s="35" t="inlineStr">
         <is>
-          <t>Dữ liệu kiểm thử thực tế từ mã nguồn nhánh origin/main (Pull lúc: 27/10/2026 21:46:44 (UTC+7) | Commit: 52885c7ecf)</t>
+          <t>Dữ liệu kiểm thử thực tế từ mã nguồn nhánh origin/main (Đồng bộ lúc: 28/10/2026 23:32:10 (UTC+7) | Commit: 65ae81d - 28/10/2026 22:24:20)</t>
         </is>
       </c>
     </row>

--- a/Testing/TestCases_KLCN_CoTuong (1).xlsx
+++ b/Testing/TestCases_KLCN_CoTuong (1).xlsx
@@ -30,7 +30,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="49">
+  <fonts count="55">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -350,8 +350,41 @@
       <color rgb="FFB71C1C"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FFB71C1C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF1B5E20"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="24">
+  <fills count="27">
     <fill>
       <patternFill/>
     </fill>
@@ -490,8 +523,26 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF334155"/>
+        <bgColor rgb="FF334155"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0F172A"/>
+        <bgColor rgb="FF0F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B5E20"/>
+        <bgColor rgb="FF1B5E20"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="51">
+  <borders count="62">
     <border>
       <left/>
       <right/>
@@ -1106,11 +1157,116 @@
         <color rgb="FFE2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF64748B"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF64748B"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1349,6 +1505,70 @@
     <xf numFmtId="0" fontId="38" fillId="23" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="24" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="24" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="21" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="25" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="26" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="22" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="18" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="21" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="21" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="25" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="26" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1716,7 +1936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E34"/>
+  <dimension ref="A2:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="4.6640625" customWidth="1" style="34" min="1" max="1"/>
@@ -1816,298 +2036,886 @@
       <c r="D12" s="31" t="n"/>
       <c r="E12" s="32" t="n"/>
     </row>
-    <row r="13" ht="22.05" customHeight="1" s="34">
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>Ngày bắt đầu kiểm thử:</t>
-        </is>
-      </c>
-      <c r="C13" s="30" t="inlineStr">
+    <row r="13" ht="24" customHeight="1" s="34">
+      <c r="A13" s="99" t="n"/>
+      <c r="B13" s="92" t="inlineStr">
+        <is>
+          <t>Thời gian kiểm thử Chu kỳ 1 (Round 1):</t>
+        </is>
+      </c>
+      <c r="C13" s="93" t="inlineStr">
+        <is>
+          <t>27/10/2026 21:46:44 (UTC+7)</t>
+        </is>
+      </c>
+      <c r="D13" s="94" t="n"/>
+      <c r="E13" s="94" t="n"/>
+      <c r="F13" s="99" t="n"/>
+      <c r="G13" s="99" t="n"/>
+      <c r="H13" s="99" t="n"/>
+      <c r="I13" s="99" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1" s="34">
+      <c r="A14" s="99" t="n"/>
+      <c r="B14" s="92" t="inlineStr">
+        <is>
+          <t>Thời gian tái kiểm thử Chu kỳ 2 (Round 2):</t>
+        </is>
+      </c>
+      <c r="C14" s="92" t="inlineStr">
+        <is>
+          <t>28/10/2026 23:32:10 (UTC+7)</t>
+        </is>
+      </c>
+      <c r="D14" s="94" t="n"/>
+      <c r="E14" s="94" t="n"/>
+      <c r="F14" s="99" t="n"/>
+      <c r="G14" s="99" t="n"/>
+      <c r="H14" s="99" t="n"/>
+      <c r="I14" s="99" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" s="34">
+      <c r="A15" s="99" t="n"/>
+      <c r="B15" s="92" t="inlineStr">
+        <is>
+          <t>Người thực hiện kiểm thử (Tester):</t>
+        </is>
+      </c>
+      <c r="C15" s="93" t="inlineStr">
+        <is>
+          <t>Tester độc lập (Bộ Master Test Runner Tự động)</t>
+        </is>
+      </c>
+      <c r="D15" s="94" t="n"/>
+      <c r="E15" s="94" t="n"/>
+      <c r="F15" s="99" t="n"/>
+      <c r="G15" s="99" t="n"/>
+      <c r="H15" s="99" t="n"/>
+      <c r="I15" s="99" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1" s="34">
+      <c r="A16" s="99" t="n"/>
+      <c r="B16" s="92" t="inlineStr">
+        <is>
+          <t>Phiên bản tài liệu (Version):</t>
+        </is>
+      </c>
+      <c r="C16" s="92" t="inlineStr">
+        <is>
+          <t>v2.1</t>
+        </is>
+      </c>
+      <c r="D16" s="94" t="n"/>
+      <c r="E16" s="94" t="n"/>
+      <c r="F16" s="99" t="n"/>
+      <c r="G16" s="99" t="n"/>
+      <c r="H16" s="99" t="n"/>
+      <c r="I16" s="99" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="34">
+      <c r="A17" s="99" t="n"/>
+      <c r="B17" s="92" t="inlineStr">
+        <is>
+          <t>Tình trạng kết quả tổng thể:</t>
+        </is>
+      </c>
+      <c r="C17" s="92" t="inlineStr">
+        <is>
+          <t>Đã hoàn tất 2 chu kỳ: Chu kỳ 1 (120/137 Pass, 17 Bugs); Chu kỳ 2 (17/17 Bugs ĐÃ FIX TOÀN DIỆN - 100% Pass)</t>
+        </is>
+      </c>
+      <c r="D17" s="94" t="n"/>
+      <c r="E17" s="94" t="n"/>
+      <c r="F17" s="99" t="n"/>
+      <c r="G17" s="99" t="n"/>
+      <c r="H17" s="99" t="n"/>
+      <c r="I17" s="99" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="34">
+      <c r="A18" s="99" t="n"/>
+      <c r="B18" s="113" t="n"/>
+      <c r="C18" s="99" t="n"/>
+      <c r="D18" s="99" t="n"/>
+      <c r="E18" s="99" t="n"/>
+      <c r="F18" s="99" t="n"/>
+      <c r="G18" s="99" t="n"/>
+      <c r="H18" s="99" t="n"/>
+      <c r="I18" s="99" t="n"/>
+    </row>
+    <row r="19" ht="28" customHeight="1" s="34">
+      <c r="A19" s="99" t="n"/>
+      <c r="B19" s="114" t="inlineStr">
+        <is>
+          <t>2. LỊCH SỬ CẬP NHẬT TÀI LIỆU</t>
+        </is>
+      </c>
+      <c r="C19" s="115" t="n"/>
+      <c r="D19" s="115" t="n"/>
+      <c r="E19" s="115" t="n"/>
+      <c r="F19" s="99" t="n"/>
+      <c r="G19" s="99" t="n"/>
+      <c r="H19" s="99" t="n"/>
+      <c r="I19" s="99" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" s="34">
+      <c r="A20" s="99" t="n"/>
+      <c r="B20" s="116" t="n"/>
+      <c r="C20" s="116" t="n"/>
+      <c r="D20" s="116" t="n"/>
+      <c r="E20" s="117" t="n"/>
+      <c r="F20" s="99" t="n"/>
+      <c r="G20" s="99" t="n"/>
+      <c r="H20" s="99" t="n"/>
+      <c r="I20" s="99" t="n"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" s="34">
+      <c r="A21" s="99" t="n"/>
+      <c r="B21" s="96" t="inlineStr">
+        <is>
+          <t>Phiên bản</t>
+        </is>
+      </c>
+      <c r="C21" s="96" t="inlineStr">
+        <is>
+          <t>Ngày cập nhật</t>
+        </is>
+      </c>
+      <c r="D21" s="96" t="inlineStr">
+        <is>
+          <t>Tác giả</t>
+        </is>
+      </c>
+      <c r="E21" s="97" t="inlineStr">
+        <is>
+          <t>Mô tả thay đổi</t>
+        </is>
+      </c>
+      <c r="F21" s="99" t="n"/>
+      <c r="G21" s="99" t="n"/>
+      <c r="H21" s="99" t="n"/>
+      <c r="I21" s="99" t="n"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" s="34">
+      <c r="A22" s="99" t="n"/>
+      <c r="B22" s="98" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="C22" s="98" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="D22" s="98" t="inlineStr">
+        <is>
+          <t>Tác giả đồ án</t>
+        </is>
+      </c>
+      <c r="E22" s="93" t="inlineStr">
+        <is>
+          <t>Khởi tạo bộ kịch bản kiểm thử ban đầu cho bản Web</t>
+        </is>
+      </c>
+      <c r="F22" s="99" t="n"/>
+      <c r="G22" s="99" t="n"/>
+      <c r="H22" s="99" t="n"/>
+      <c r="I22" s="99" t="n"/>
+    </row>
+    <row r="23" ht="24" customHeight="1" s="34">
+      <c r="A23" s="99" t="n"/>
+      <c r="B23" s="98" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="C23" s="98" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="D23" s="98" t="inlineStr">
+        <is>
+          <t>Tác giả đồ án</t>
+        </is>
+      </c>
+      <c r="E23" s="93" t="inlineStr">
+        <is>
+          <t>Bổ sung kịch bản kiểm thử Realtime SignalR, Đồng hồ rụng kim và AI</t>
+        </is>
+      </c>
+      <c r="F23" s="99" t="n"/>
+      <c r="G23" s="99" t="n"/>
+      <c r="H23" s="99" t="n"/>
+      <c r="I23" s="99" t="n"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" s="34">
+      <c r="A24" s="99" t="n"/>
+      <c r="B24" s="98" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="C24" s="98" t="inlineStr">
         <is>
           <t>27/10/2026</t>
         </is>
       </c>
-      <c r="D13" s="31" t="n"/>
-      <c r="E13" s="32" t="n"/>
-    </row>
-    <row r="14" ht="22.05" customHeight="1" s="34">
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>Người thực hiện kiểm thử (Tester):</t>
-        </is>
-      </c>
-      <c r="C14" s="30" t="inlineStr">
-        <is>
-          <t>Tester độc lập (Bộ Test Runner Tự động)</t>
-        </is>
-      </c>
-      <c r="D14" s="31" t="n"/>
-      <c r="E14" s="32" t="n"/>
-    </row>
-    <row r="15" ht="22.05" customHeight="1" s="34">
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>Phiên bản tài liệu (Version):</t>
-        </is>
-      </c>
-      <c r="C15" s="38" t="inlineStr">
+      <c r="D24" s="98" t="inlineStr">
+        <is>
+          <t>Tác giả đồ án</t>
+        </is>
+      </c>
+      <c r="E24" s="93" t="inlineStr">
+        <is>
+          <t>Hoàn thiện 12 sheet kiểm thử chi tiết; thực hiện kiểm thử Chu kỳ 1 phát hiện 17 lỗi ghi nhận tại Sheet 12_Defect_Log</t>
+        </is>
+      </c>
+      <c r="F24" s="99" t="n"/>
+      <c r="G24" s="99" t="n"/>
+      <c r="H24" s="99" t="n"/>
+      <c r="I24" s="99" t="n"/>
+    </row>
+    <row r="25" ht="38" customHeight="1" s="34">
+      <c r="A25" s="99" t="n"/>
+      <c r="B25" s="98" t="inlineStr">
         <is>
           <t>v2.1</t>
         </is>
       </c>
-      <c r="D15" s="31" t="n"/>
-      <c r="E15" s="32" t="n"/>
-    </row>
-    <row r="16" ht="22.05" customHeight="1" s="34">
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>Tình trạng kết quả:</t>
-        </is>
-      </c>
-      <c r="C16" s="30" t="inlineStr">
-        <is>
-          <t>Hoàn tất kiểm thử chu kỳ 2 (Retest Round 2) - 17/17 lỗi ĐÃ ĐƯỢC FIX TOÀN DIỆN</t>
-        </is>
-      </c>
-      <c r="D16" s="31" t="n"/>
-      <c r="E16" s="32" t="n"/>
-    </row>
-    <row r="18" ht="16.8" customHeight="1" s="34">
-      <c r="B18" s="33" t="inlineStr">
-        <is>
-          <t>2. LỊCH SỬ CẬP NHẬT TÀI LIỆU</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="34">
-      <c r="B20" s="39" t="inlineStr">
-        <is>
-          <t>Phiên bản</t>
-        </is>
-      </c>
-      <c r="C20" s="39" t="inlineStr">
-        <is>
-          <t>Ngày cập nhật</t>
-        </is>
-      </c>
-      <c r="D20" s="39" t="inlineStr">
-        <is>
-          <t>Tác giả</t>
-        </is>
-      </c>
-      <c r="E20" s="39" t="inlineStr">
-        <is>
-          <t>Mô tả thay đổi</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22.05" customHeight="1" s="34">
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>20/10/2026</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Tác giả đồ án</t>
-        </is>
-      </c>
-      <c r="E21" s="30" t="inlineStr">
-        <is>
-          <t>Khởi tạo bộ kịch bản kiểm thử ban đầu cho bản Web</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22.05" customHeight="1" s="34">
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>v1.5</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>25/10/2026</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Tác giả đồ án</t>
-        </is>
-      </c>
-      <c r="E22" s="30" t="inlineStr">
-        <is>
-          <t>Bổ sung kịch bản kiểm thử Realtime SignalR, Đồng hồ rụng kim và AI</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22.05" customHeight="1" s="34">
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>v2.0</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>27/10/2026</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Tác giả đồ án</t>
-        </is>
-      </c>
-      <c r="E23" s="30" t="inlineStr">
-        <is>
-          <t>Hoàn thiện đầy đủ 12 sheet kiểm thử chi tiết Web &amp; Mobile, phân hệ Admin, để trống kết quả để tester tiến hành thử nghiệm độc lập</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="70" t="inlineStr">
-        <is>
-          <t>v2.1</t>
-        </is>
-      </c>
-      <c r="C24" s="71" t="inlineStr">
+      <c r="C25" s="98" t="inlineStr">
         <is>
           <t>28/10/2026</t>
         </is>
       </c>
-      <c r="D24" s="71" t="inlineStr">
-        <is>
-          <t>Tester độc lập (Bộ Test Runner Tự động)</t>
-        </is>
-      </c>
-      <c r="E24" s="71" t="inlineStr">
-        <is>
-          <t>Đồng bộ commit mới nhất 65ae81d từ branch main trên cloud (28/10/2026 22:24:20). Thực hiện kiểm thử chu kỳ 2 (Retest Round 2) cho toàn bộ 17 lỗi từ chu kỳ 1. Bổ sung Sheet 13_Retest_Round2 ghi nhận kết quả xác minh: 17/17 lỗi đã được khắc phục triệt để (100% Fixed).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3. THÔNG TIN ĐỒNG BỘ MÃ NGUỒN TỪ CLOUD (GIT SYNC INFO)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
+      <c r="D25" s="98" t="inlineStr">
+        <is>
+          <t>Tester độc lập</t>
+        </is>
+      </c>
+      <c r="E25" s="93" t="inlineStr">
+        <is>
+          <t>Đồng bộ commit mới nhất 65ae81d từ branch main trên cloud (28/10/2026 22:24:20). Thực hiện kiểm thử chu kỳ 2 (Retest Round 2) cho 17 lỗi. Bổ sung Sheet 13_Retest_Round2 ghi nhận 17/17 bug đã được fix triệt để (100% Fixed). Lưu trữ đầy đủ lịch sử commit &amp; thời gian của cả 2 chu kỳ kiểm thử.</t>
+        </is>
+      </c>
+      <c r="F25" s="99" t="n"/>
+      <c r="G25" s="99" t="n"/>
+      <c r="H25" s="99" t="n"/>
+      <c r="I25" s="99" t="n"/>
+    </row>
+    <row r="26" ht="24" customHeight="1" s="34">
+      <c r="A26" s="99" t="n"/>
+      <c r="B26" s="99" t="n"/>
+      <c r="C26" s="99" t="n"/>
+      <c r="D26" s="99" t="n"/>
+      <c r="E26" s="99" t="n"/>
+      <c r="F26" s="99" t="n"/>
+      <c r="G26" s="99" t="n"/>
+      <c r="H26" s="99" t="n"/>
+      <c r="I26" s="99" t="n"/>
+    </row>
+    <row r="27" ht="28" customHeight="1" s="34">
+      <c r="A27" s="99" t="n"/>
+      <c r="B27" s="118" t="inlineStr">
+        <is>
+          <t>3. THÔNG TIN ĐỒNG BỘ MÃ NGUỒN TỪ CLOUD (GIT REMOTE &amp; COMMITS HISTORY)</t>
+        </is>
+      </c>
+      <c r="C27" s="115" t="n"/>
+      <c r="D27" s="115" t="n"/>
+      <c r="E27" s="115" t="n"/>
+      <c r="F27" s="99" t="n"/>
+      <c r="G27" s="99" t="n"/>
+      <c r="H27" s="99" t="n"/>
+      <c r="I27" s="99" t="n"/>
+    </row>
+    <row r="28" ht="24" customHeight="1" s="34">
+      <c r="A28" s="99" t="n"/>
+      <c r="B28" s="119" t="n"/>
+      <c r="C28" s="117" t="n"/>
+      <c r="D28" s="99" t="n"/>
+      <c r="E28" s="99" t="n"/>
+      <c r="F28" s="99" t="n"/>
+      <c r="G28" s="99" t="n"/>
+      <c r="H28" s="99" t="n"/>
+      <c r="I28" s="99" t="n"/>
+    </row>
+    <row r="29" ht="24" customHeight="1" s="34">
+      <c r="A29" s="99" t="n"/>
+      <c r="B29" s="92" t="inlineStr">
         <is>
           <t>Kho mã nguồn Cloud (Git Remote):</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C29" s="93" t="inlineStr">
         <is>
           <t>https://github.com/thequang120605-byte/C-T-ng-.git</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
+      <c r="D29" s="94" t="n"/>
+      <c r="E29" s="94" t="n"/>
+      <c r="F29" s="99" t="n"/>
+      <c r="G29" s="99" t="n"/>
+      <c r="H29" s="99" t="n"/>
+      <c r="I29" s="99" t="n"/>
+    </row>
+    <row r="30" ht="24" customHeight="1" s="34">
+      <c r="A30" s="99" t="n"/>
+      <c r="B30" s="92" t="inlineStr">
         <is>
           <t>Nhánh kiểm thử (Target Branch):</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C30" s="93" t="inlineStr">
         <is>
           <t>main (Origin Main)</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Mã Commit mới nhất (Commit Hash):</t>
-        </is>
-      </c>
-      <c r="C29" s="72" t="inlineStr">
+      <c r="D30" s="94" t="n"/>
+      <c r="E30" s="94" t="n"/>
+      <c r="F30" s="99" t="n"/>
+      <c r="G30" s="99" t="n"/>
+      <c r="H30" s="99" t="n"/>
+      <c r="I30" s="99" t="n"/>
+    </row>
+    <row r="31" ht="24" customHeight="1" s="34">
+      <c r="A31" s="99" t="n"/>
+      <c r="B31" s="119" t="n"/>
+      <c r="C31" s="117" t="n"/>
+      <c r="D31" s="99" t="n"/>
+      <c r="E31" s="99" t="n"/>
+      <c r="F31" s="99" t="n"/>
+      <c r="G31" s="99" t="n"/>
+      <c r="H31" s="99" t="n"/>
+      <c r="I31" s="99" t="n"/>
+    </row>
+    <row r="32" ht="26" customHeight="1" s="34">
+      <c r="A32" s="99" t="n"/>
+      <c r="B32" s="120" t="inlineStr">
+        <is>
+          <t>3.1. CHU KỲ 1: KIỂM THỬ BAN ĐẦU (ROUND 1 - PHÁT HIỆN 17 LỖI)</t>
+        </is>
+      </c>
+      <c r="C32" s="121" t="n"/>
+      <c r="D32" s="121" t="n"/>
+      <c r="E32" s="121" t="n"/>
+      <c r="F32" s="99" t="n"/>
+      <c r="G32" s="99" t="n"/>
+      <c r="H32" s="99" t="n"/>
+      <c r="I32" s="99" t="n"/>
+    </row>
+    <row r="33" ht="24" customHeight="1" s="34">
+      <c r="A33" s="99" t="n"/>
+      <c r="B33" s="92" t="inlineStr">
+        <is>
+          <t>Mã Commit Git Chu kỳ 1 (Commit Hash):</t>
+        </is>
+      </c>
+      <c r="C33" s="93" t="inlineStr">
+        <is>
+          <t>52885c7ecfcd53c2cecc6c73cba7f4231e996efc (Short: 52885c7)</t>
+        </is>
+      </c>
+      <c r="D33" s="94" t="n"/>
+      <c r="E33" s="94" t="n"/>
+      <c r="F33" s="99" t="n"/>
+      <c r="G33" s="99" t="n"/>
+      <c r="H33" s="99" t="n"/>
+      <c r="I33" s="99" t="n"/>
+    </row>
+    <row r="34" ht="24" customHeight="1" s="34">
+      <c r="A34" s="99" t="n"/>
+      <c r="B34" s="92" t="inlineStr">
+        <is>
+          <t>Thông điệp Commit Chu kỳ 1 (Commit Message):</t>
+        </is>
+      </c>
+      <c r="C34" s="93" t="inlineStr">
+        <is>
+          <t>fix(master-game): remove unused exception variable warning</t>
+        </is>
+      </c>
+      <c r="D34" s="94" t="n"/>
+      <c r="E34" s="94" t="n"/>
+      <c r="F34" s="99" t="n"/>
+      <c r="G34" s="99" t="n"/>
+      <c r="H34" s="99" t="n"/>
+      <c r="I34" s="99" t="n"/>
+    </row>
+    <row r="35" ht="24" customHeight="1" s="34">
+      <c r="A35" s="99" t="n"/>
+      <c r="B35" s="92" t="inlineStr">
+        <is>
+          <t>Tác giả commit (Author):</t>
+        </is>
+      </c>
+      <c r="C35" s="93" t="inlineStr">
+        <is>
+          <t>nguyentrongnguyen3004-eng &lt;nguyentrongnguyen3004@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="D35" s="94" t="n"/>
+      <c r="E35" s="94" t="n"/>
+      <c r="F35" s="99" t="n"/>
+      <c r="G35" s="99" t="n"/>
+      <c r="H35" s="99" t="n"/>
+      <c r="I35" s="99" t="n"/>
+    </row>
+    <row r="36" ht="24" customHeight="1" s="34">
+      <c r="A36" s="99" t="n"/>
+      <c r="B36" s="92" t="inlineStr">
+        <is>
+          <t>Thời gian commit trên Cloud (Lần 1):</t>
+        </is>
+      </c>
+      <c r="C36" s="92" t="inlineStr">
+        <is>
+          <t>Mon Oct 26 12:25:07 2026 +0700 (26/10/2026 12:25:07)</t>
+        </is>
+      </c>
+      <c r="D36" s="94" t="n"/>
+      <c r="E36" s="94" t="n"/>
+      <c r="F36" s="99" t="n"/>
+      <c r="G36" s="99" t="n"/>
+      <c r="H36" s="99" t="n"/>
+      <c r="I36" s="99" t="n"/>
+    </row>
+    <row r="37" ht="24" customHeight="1" s="34">
+      <c r="A37" s="99" t="n"/>
+      <c r="B37" s="92" t="inlineStr">
+        <is>
+          <t>Thời gian Pull / Bắt đầu kiểm thử Lần 1:</t>
+        </is>
+      </c>
+      <c r="C37" s="92" t="inlineStr">
+        <is>
+          <t>27/10/2026 21:46:44 (UTC+7)</t>
+        </is>
+      </c>
+      <c r="D37" s="94" t="n"/>
+      <c r="E37" s="94" t="n"/>
+      <c r="F37" s="99" t="n"/>
+      <c r="G37" s="99" t="n"/>
+      <c r="H37" s="99" t="n"/>
+      <c r="I37" s="99" t="n"/>
+    </row>
+    <row r="38" ht="24" customHeight="1" s="34">
+      <c r="A38" s="99" t="n"/>
+      <c r="B38" s="92" t="inlineStr">
+        <is>
+          <t>Quy mô &amp; Kết quả kiểm thử Chu kỳ 1:</t>
+        </is>
+      </c>
+      <c r="C38" s="93" t="inlineStr">
+        <is>
+          <t>137 Test Cases | Đạt: 120 (87.6%) - Không đạt: 17 (12.4%)</t>
+        </is>
+      </c>
+      <c r="D38" s="94" t="n"/>
+      <c r="E38" s="94" t="n"/>
+      <c r="F38" s="99" t="n"/>
+      <c r="G38" s="99" t="n"/>
+      <c r="H38" s="99" t="n"/>
+      <c r="I38" s="99" t="n"/>
+    </row>
+    <row r="39" ht="24" customHeight="1" s="34">
+      <c r="A39" s="99" t="n"/>
+      <c r="B39" s="92" t="inlineStr">
+        <is>
+          <t>Báo cáo chi tiết Lần 1:</t>
+        </is>
+      </c>
+      <c r="C39" s="93" t="inlineStr">
+        <is>
+          <t>Ghi nhận 17 Defect tại Sheet 12_Defect_Log (Đã xuất tài liệu hướng dẫn fix lỗi cho Dev)</t>
+        </is>
+      </c>
+      <c r="D39" s="94" t="n"/>
+      <c r="E39" s="94" t="n"/>
+      <c r="F39" s="99" t="n"/>
+      <c r="G39" s="99" t="n"/>
+      <c r="H39" s="99" t="n"/>
+      <c r="I39" s="99" t="n"/>
+    </row>
+    <row r="40" ht="24" customHeight="1" s="34">
+      <c r="A40" s="99" t="n"/>
+      <c r="B40" s="119" t="n"/>
+      <c r="C40" s="117" t="n"/>
+      <c r="D40" s="99" t="n"/>
+      <c r="E40" s="99" t="n"/>
+      <c r="F40" s="99" t="n"/>
+      <c r="G40" s="99" t="n"/>
+      <c r="H40" s="99" t="n"/>
+      <c r="I40" s="99" t="n"/>
+    </row>
+    <row r="41" ht="26" customHeight="1" s="34">
+      <c r="A41" s="99" t="n"/>
+      <c r="B41" s="122" t="inlineStr">
+        <is>
+          <t>3.2. CHU KỲ 2: TÁI KIỂM THỬ SAU KHI SỬA LỖI (ROUND 2 - 100% FIXED &amp; NGHIỆM THU)</t>
+        </is>
+      </c>
+      <c r="C41" s="123" t="n"/>
+      <c r="D41" s="123" t="n"/>
+      <c r="E41" s="123" t="n"/>
+      <c r="F41" s="99" t="n"/>
+      <c r="G41" s="99" t="n"/>
+      <c r="H41" s="99" t="n"/>
+      <c r="I41" s="99" t="n"/>
+    </row>
+    <row r="42" ht="24" customHeight="1" s="34">
+      <c r="A42" s="99" t="n"/>
+      <c r="B42" s="92" t="inlineStr">
+        <is>
+          <t>Mã Commit Git Chu kỳ 2 (Commit Hash):</t>
+        </is>
+      </c>
+      <c r="C42" s="93" t="inlineStr">
         <is>
           <t>65ae81dd6baed2dc85923a3d7f4644fd8006b0e3 (Short: 65ae81d)</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Thông điệp Commit (Commit Message):</t>
-        </is>
-      </c>
-      <c r="C30" s="73" t="inlineStr">
-        <is>
-          <t>feat(admin): modernize users management view matching overview design and metrics</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
+      <c r="D42" s="94" t="n"/>
+      <c r="E42" s="94" t="n"/>
+      <c r="F42" s="99" t="n"/>
+      <c r="G42" s="99" t="n"/>
+      <c r="H42" s="99" t="n"/>
+      <c r="I42" s="99" t="n"/>
+    </row>
+    <row r="43" ht="24" customHeight="1" s="34">
+      <c r="A43" s="99" t="n"/>
+      <c r="B43" s="92" t="inlineStr">
+        <is>
+          <t>Thông điệp Commit Chu kỳ 2 (Commit Message):</t>
+        </is>
+      </c>
+      <c r="C43" s="93" t="inlineStr">
+        <is>
+          <t>feat(admin): modernize users management view matching overview design and metrics (Bao gồm commit 102ef29: fix 17 defects)</t>
+        </is>
+      </c>
+      <c r="D43" s="94" t="n"/>
+      <c r="E43" s="94" t="n"/>
+      <c r="F43" s="99" t="n"/>
+      <c r="G43" s="99" t="n"/>
+      <c r="H43" s="99" t="n"/>
+      <c r="I43" s="99" t="n"/>
+    </row>
+    <row r="44" ht="24" customHeight="1" s="34">
+      <c r="A44" s="99" t="n"/>
+      <c r="B44" s="92" t="inlineStr">
         <is>
           <t>Tác giả commit (Author):</t>
         </is>
       </c>
-      <c r="C31" s="73" t="inlineStr">
+      <c r="C44" s="93" t="inlineStr">
         <is>
           <t>nguyentrongnguyen3004-eng &lt;nguyentrongnguyen3004@gmail.com&gt;</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Thời gian commit trên Cloud:</t>
-        </is>
-      </c>
-      <c r="C32" s="72" t="inlineStr">
-        <is>
-          <t>Wed Oct 28 22:24:20 2026 +0700</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Thời gian Pull / Đồng bộ kiểm thử:</t>
-        </is>
-      </c>
-      <c r="C33" s="73" t="inlineStr">
+      <c r="D44" s="94" t="n"/>
+      <c r="E44" s="94" t="n"/>
+      <c r="F44" s="99" t="n"/>
+      <c r="G44" s="99" t="n"/>
+      <c r="H44" s="99" t="n"/>
+      <c r="I44" s="99" t="n"/>
+    </row>
+    <row r="45" ht="24" customHeight="1" s="34">
+      <c r="A45" s="99" t="n"/>
+      <c r="B45" s="92" t="inlineStr">
+        <is>
+          <t>Thời gian commit trên Cloud (Lần 2):</t>
+        </is>
+      </c>
+      <c r="C45" s="92" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 22:24:20 2026 +0700 (28/10/2026 22:24:20)</t>
+        </is>
+      </c>
+      <c r="D45" s="94" t="n"/>
+      <c r="E45" s="94" t="n"/>
+      <c r="F45" s="99" t="n"/>
+      <c r="G45" s="99" t="n"/>
+      <c r="H45" s="99" t="n"/>
+      <c r="I45" s="99" t="n"/>
+    </row>
+    <row r="46" ht="24" customHeight="1" s="34">
+      <c r="A46" s="99" t="n"/>
+      <c r="B46" s="92" t="inlineStr">
+        <is>
+          <t>Thời gian Pull / Bắt đầu kiểm thử Lần 2:</t>
+        </is>
+      </c>
+      <c r="C46" s="92" t="inlineStr">
         <is>
           <t>28/10/2026 23:32:10 (UTC+7)</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Trạng thái mã nguồn:</t>
-        </is>
-      </c>
-      <c r="C34" s="73" t="inlineStr">
-        <is>
-          <t>Đã fast-forward nhánh main lên 65ae81d và tích hợp vào feat/e2e-testing-suite; build .NET sạch 0 lỗi, toàn bộ 17 bug đã được fix toàn diện.</t>
-        </is>
-      </c>
+      <c r="D46" s="94" t="n"/>
+      <c r="E46" s="94" t="n"/>
+      <c r="F46" s="99" t="n"/>
+      <c r="G46" s="99" t="n"/>
+      <c r="H46" s="99" t="n"/>
+      <c r="I46" s="99" t="n"/>
+    </row>
+    <row r="47" ht="24" customHeight="1" s="34">
+      <c r="A47" s="99" t="n"/>
+      <c r="B47" s="92" t="inlineStr">
+        <is>
+          <t>Quy mô &amp; Kết quả tái kiểm thử Chu kỳ 2:</t>
+        </is>
+      </c>
+      <c r="C47" s="93" t="inlineStr">
+        <is>
+          <t>17 Defects từ Chu kỳ 1 | Đã khắc phục (Fixed): 17/17 (100.0%) - Còn tồn tại (Open): 0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="D47" s="94" t="n"/>
+      <c r="E47" s="94" t="n"/>
+      <c r="F47" s="99" t="n"/>
+      <c r="G47" s="99" t="n"/>
+      <c r="H47" s="99" t="n"/>
+      <c r="I47" s="99" t="n"/>
+    </row>
+    <row r="48" ht="24" customHeight="1" s="34">
+      <c r="A48" s="99" t="n"/>
+      <c r="B48" s="92" t="inlineStr">
+        <is>
+          <t>Báo cáo chi tiết Lần 2:</t>
+        </is>
+      </c>
+      <c r="C48" s="93" t="inlineStr">
+        <is>
+          <t>Ghi nhận toàn bộ bằng chứng thực nghiệm tại Sheet 13_Retest_Round2</t>
+        </is>
+      </c>
+      <c r="D48" s="94" t="n"/>
+      <c r="E48" s="94" t="n"/>
+      <c r="F48" s="99" t="n"/>
+      <c r="G48" s="99" t="n"/>
+      <c r="H48" s="99" t="n"/>
+      <c r="I48" s="99" t="n"/>
+    </row>
+    <row r="49" ht="24" customHeight="1" s="34">
+      <c r="A49" s="99" t="n"/>
+      <c r="B49" s="92" t="inlineStr">
+        <is>
+          <t>Đánh giá &amp; Kết luận nghiệm thu:</t>
+        </is>
+      </c>
+      <c r="C49" s="92" t="inlineStr">
+        <is>
+          <t>17/17 LỖI ĐÃ ĐƯỢC FIX TOÀN DIỆN (100% FIXED). Toàn bộ hệ thống đạt độ ổn định và an toàn thông tin tối đa.</t>
+        </is>
+      </c>
+      <c r="D49" s="94" t="n"/>
+      <c r="E49" s="94" t="n"/>
+      <c r="F49" s="99" t="n"/>
+      <c r="G49" s="99" t="n"/>
+      <c r="H49" s="99" t="n"/>
+      <c r="I49" s="99" t="n"/>
+    </row>
+    <row r="50" ht="24" customHeight="1" s="34">
+      <c r="A50" s="99" t="n"/>
+      <c r="B50" s="99" t="n"/>
+      <c r="C50" s="99" t="n"/>
+      <c r="D50" s="99" t="n"/>
+      <c r="E50" s="99" t="n"/>
+      <c r="F50" s="99" t="n"/>
+      <c r="G50" s="99" t="n"/>
+      <c r="H50" s="99" t="n"/>
+      <c r="I50" s="99" t="n"/>
+    </row>
+    <row r="51" ht="24" customHeight="1" s="34">
+      <c r="A51" s="99" t="n"/>
+      <c r="B51" s="99" t="n"/>
+      <c r="C51" s="99" t="n"/>
+      <c r="D51" s="99" t="n"/>
+      <c r="E51" s="99" t="n"/>
+      <c r="F51" s="99" t="n"/>
+      <c r="G51" s="99" t="n"/>
+      <c r="H51" s="99" t="n"/>
+      <c r="I51" s="99" t="n"/>
+    </row>
+    <row r="52" ht="24" customHeight="1" s="34">
+      <c r="A52" s="99" t="n"/>
+      <c r="B52" s="99" t="n"/>
+      <c r="C52" s="99" t="n"/>
+      <c r="D52" s="99" t="n"/>
+      <c r="E52" s="99" t="n"/>
+      <c r="F52" s="99" t="n"/>
+      <c r="G52" s="99" t="n"/>
+      <c r="H52" s="99" t="n"/>
+      <c r="I52" s="99" t="n"/>
+    </row>
+    <row r="53" ht="24" customHeight="1" s="34">
+      <c r="A53" s="99" t="n"/>
+      <c r="B53" s="99" t="n"/>
+      <c r="C53" s="99" t="n"/>
+      <c r="D53" s="99" t="n"/>
+      <c r="E53" s="99" t="n"/>
+      <c r="F53" s="99" t="n"/>
+      <c r="G53" s="99" t="n"/>
+      <c r="H53" s="99" t="n"/>
+      <c r="I53" s="99" t="n"/>
+    </row>
+    <row r="54" ht="24" customHeight="1" s="34">
+      <c r="A54" s="99" t="n"/>
+      <c r="B54" s="99" t="n"/>
+      <c r="C54" s="99" t="n"/>
+      <c r="D54" s="99" t="n"/>
+      <c r="E54" s="99" t="n"/>
+      <c r="F54" s="99" t="n"/>
+      <c r="G54" s="99" t="n"/>
+      <c r="H54" s="99" t="n"/>
+      <c r="I54" s="99" t="n"/>
+    </row>
+    <row r="55" ht="24" customHeight="1" s="34">
+      <c r="A55" s="99" t="n"/>
+      <c r="B55" s="99" t="n"/>
+      <c r="C55" s="99" t="n"/>
+      <c r="D55" s="99" t="n"/>
+      <c r="E55" s="99" t="n"/>
+      <c r="F55" s="99" t="n"/>
+      <c r="G55" s="99" t="n"/>
+      <c r="H55" s="99" t="n"/>
+      <c r="I55" s="99" t="n"/>
+    </row>
+    <row r="56" ht="24" customHeight="1" s="34">
+      <c r="A56" s="99" t="n"/>
+      <c r="B56" s="99" t="n"/>
+      <c r="C56" s="99" t="n"/>
+      <c r="D56" s="99" t="n"/>
+      <c r="E56" s="99" t="n"/>
+      <c r="F56" s="99" t="n"/>
+      <c r="G56" s="99" t="n"/>
+      <c r="H56" s="99" t="n"/>
+      <c r="I56" s="99" t="n"/>
+    </row>
+    <row r="57" ht="24" customHeight="1" s="34">
+      <c r="A57" s="99" t="n"/>
+      <c r="B57" s="99" t="n"/>
+      <c r="C57" s="99" t="n"/>
+      <c r="D57" s="99" t="n"/>
+      <c r="E57" s="99" t="n"/>
+      <c r="F57" s="99" t="n"/>
+      <c r="G57" s="99" t="n"/>
+      <c r="H57" s="99" t="n"/>
+      <c r="I57" s="99" t="n"/>
+    </row>
+    <row r="58" ht="24" customHeight="1" s="34">
+      <c r="A58" s="99" t="n"/>
+      <c r="B58" s="99" t="n"/>
+      <c r="C58" s="99" t="n"/>
+      <c r="D58" s="99" t="n"/>
+      <c r="E58" s="99" t="n"/>
+      <c r="F58" s="99" t="n"/>
+      <c r="G58" s="99" t="n"/>
+      <c r="H58" s="99" t="n"/>
+      <c r="I58" s="99" t="n"/>
+    </row>
+    <row r="59" ht="24" customHeight="1" s="34">
+      <c r="A59" s="99" t="n"/>
+      <c r="B59" s="99" t="n"/>
+      <c r="C59" s="99" t="n"/>
+      <c r="D59" s="99" t="n"/>
+      <c r="E59" s="99" t="n"/>
+      <c r="F59" s="99" t="n"/>
+      <c r="G59" s="99" t="n"/>
+      <c r="H59" s="99" t="n"/>
+      <c r="I59" s="99" t="n"/>
+    </row>
+    <row r="60" ht="24" customHeight="1" s="34">
+      <c r="A60" s="99" t="n"/>
+      <c r="B60" s="99" t="n"/>
+      <c r="C60" s="99" t="n"/>
+      <c r="D60" s="99" t="n"/>
+      <c r="E60" s="99" t="n"/>
+      <c r="F60" s="99" t="n"/>
+      <c r="G60" s="99" t="n"/>
+      <c r="H60" s="99" t="n"/>
+      <c r="I60" s="99" t="n"/>
+    </row>
+    <row r="61" ht="24" customHeight="1" s="34">
+      <c r="A61" s="99" t="n"/>
+      <c r="B61" s="99" t="n"/>
+      <c r="C61" s="99" t="n"/>
+      <c r="D61" s="99" t="n"/>
+      <c r="E61" s="99" t="n"/>
+      <c r="F61" s="99" t="n"/>
+      <c r="G61" s="99" t="n"/>
+      <c r="H61" s="99" t="n"/>
+      <c r="I61" s="99" t="n"/>
+    </row>
+    <row r="62" ht="24" customHeight="1" s="34">
+      <c r="A62" s="99" t="n"/>
+      <c r="B62" s="99" t="n"/>
+      <c r="C62" s="99" t="n"/>
+      <c r="D62" s="99" t="n"/>
+      <c r="E62" s="99" t="n"/>
+      <c r="F62" s="99" t="n"/>
+      <c r="G62" s="99" t="n"/>
+      <c r="H62" s="99" t="n"/>
+      <c r="I62" s="99" t="n"/>
+    </row>
+    <row r="63" ht="24" customHeight="1" s="34">
+      <c r="A63" s="99" t="n"/>
+      <c r="B63" s="99" t="n"/>
+      <c r="C63" s="99" t="n"/>
+      <c r="D63" s="99" t="n"/>
+      <c r="E63" s="99" t="n"/>
+      <c r="F63" s="99" t="n"/>
+      <c r="G63" s="99" t="n"/>
+      <c r="H63" s="99" t="n"/>
+      <c r="I63" s="99" t="n"/>
+    </row>
+    <row r="64" ht="24" customHeight="1" s="34">
+      <c r="A64" s="99" t="n"/>
+      <c r="B64" s="99" t="n"/>
+      <c r="C64" s="99" t="n"/>
+      <c r="D64" s="99" t="n"/>
+      <c r="E64" s="99" t="n"/>
+      <c r="F64" s="99" t="n"/>
+      <c r="G64" s="99" t="n"/>
+      <c r="H64" s="99" t="n"/>
+      <c r="I64" s="99" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="35">
     <mergeCell ref="C16:E16"/>
-    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="C33:E33"/>
     <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="C10:E10"/>
   </mergeCells>
   <printOptions gridLines="1"/>
@@ -5353,10 +6161,10 @@
     <col width="24" customWidth="1" style="34" min="4" max="4"/>
     <col width="34" customWidth="1" style="34" min="5" max="5"/>
     <col width="18" customWidth="1" style="34" min="6" max="6"/>
-    <col width="18" customWidth="1" style="34" min="7" max="7"/>
+    <col width="24" customWidth="1" style="34" min="7" max="7"/>
     <col width="16" customWidth="1" style="34" min="8" max="8"/>
-    <col width="22" customWidth="1" style="34" min="9" max="9"/>
-    <col width="22" customWidth="1" style="34" min="10" max="10"/>
+    <col width="24" customWidth="1" style="34" min="9" max="9"/>
+    <col width="20" customWidth="1" style="34" min="10" max="10"/>
     <col width="55" customWidth="1" style="34" min="11" max="11"/>
     <col width="30" customWidth="1" style="34" min="12" max="12"/>
   </cols>
@@ -5371,7 +6179,7 @@
     <row r="3">
       <c r="A3" s="77" t="inlineStr">
         <is>
-          <t>Đánh giá &amp; Xác minh thực nghiệm độc lập 17 Defects sau khi Dev cập nhật bản sửa lỗi tại Commit 65ae81d (28/10/2026 22:24:20 +07:00)</t>
+          <t>Đánh giá &amp; Xác minh thực nghiệm độc lập 17 Defects | So sánh đối chiếu Chu kỳ 1 (Commit 52885c7 - 27/10/2026) và Chu kỳ 2 (Commit 65ae81d - 28/10/2026)</t>
         </is>
       </c>
     </row>
@@ -5381,29 +6189,29 @@
           <t>TỔNG DEFECT KIỂM THỬ LẦN 2</t>
         </is>
       </c>
-      <c r="B5" s="79" t="n"/>
-      <c r="C5" s="79" t="n"/>
+      <c r="B5" s="104" t="n"/>
+      <c r="C5" s="105" t="n"/>
       <c r="D5" s="80" t="inlineStr">
         <is>
           <t>SỐ LỖI ĐÃ KHẮC PHỤC (FIXED)</t>
         </is>
       </c>
-      <c r="E5" s="79" t="n"/>
-      <c r="F5" s="79" t="n"/>
+      <c r="E5" s="104" t="n"/>
+      <c r="F5" s="105" t="n"/>
       <c r="G5" s="78" t="inlineStr">
         <is>
           <t>SỐ LỖI CÒN TỒN TẠI (OPEN)</t>
         </is>
       </c>
-      <c r="H5" s="79" t="n"/>
-      <c r="I5" s="79" t="n"/>
+      <c r="H5" s="104" t="n"/>
+      <c r="I5" s="105" t="n"/>
       <c r="J5" s="80" t="inlineStr">
         <is>
           <t>ĐÁNH GIÁ NGHIỆM THU HỆ THỐNG</t>
         </is>
       </c>
-      <c r="K5" s="79" t="n"/>
-      <c r="L5" s="79" t="n"/>
+      <c r="K5" s="104" t="n"/>
+      <c r="L5" s="105" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="81" t="inlineStr">
@@ -5411,45 +6219,45 @@
           <t>17 LỖI</t>
         </is>
       </c>
-      <c r="B6" s="79" t="n"/>
-      <c r="C6" s="79" t="n"/>
+      <c r="B6" s="106" t="n"/>
+      <c r="C6" s="107" t="n"/>
       <c r="D6" s="82" t="inlineStr">
         <is>
           <t>17 / 17 (100.0%)</t>
         </is>
       </c>
-      <c r="E6" s="79" t="n"/>
-      <c r="F6" s="79" t="n"/>
+      <c r="E6" s="106" t="n"/>
+      <c r="F6" s="107" t="n"/>
       <c r="G6" s="83" t="inlineStr">
         <is>
           <t>0 / 17 (0.0%)</t>
         </is>
       </c>
-      <c r="H6" s="79" t="n"/>
-      <c r="I6" s="79" t="n"/>
+      <c r="H6" s="106" t="n"/>
+      <c r="I6" s="107" t="n"/>
       <c r="J6" s="84" t="inlineStr">
         <is>
           <t>ĐẠT CHUẨN ĐÓNG LỖI (100% FIXED)</t>
         </is>
       </c>
-      <c r="K6" s="79" t="n"/>
-      <c r="L6" s="79" t="n"/>
+      <c r="K6" s="106" t="n"/>
+      <c r="L6" s="107" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="79" t="n"/>
-      <c r="B7" s="79" t="n"/>
-      <c r="C7" s="79" t="n"/>
-      <c r="D7" s="79" t="n"/>
-      <c r="E7" s="79" t="n"/>
-      <c r="F7" s="79" t="n"/>
-      <c r="G7" s="79" t="n"/>
-      <c r="H7" s="79" t="n"/>
-      <c r="I7" s="79" t="n"/>
-      <c r="J7" s="79" t="n"/>
-      <c r="K7" s="79" t="n"/>
-      <c r="L7" s="79" t="n"/>
-    </row>
-    <row r="9" ht="35" customHeight="1" s="34">
+      <c r="A7" s="108" t="n"/>
+      <c r="B7" s="109" t="n"/>
+      <c r="C7" s="110" t="n"/>
+      <c r="D7" s="108" t="n"/>
+      <c r="E7" s="109" t="n"/>
+      <c r="F7" s="110" t="n"/>
+      <c r="G7" s="108" t="n"/>
+      <c r="H7" s="109" t="n"/>
+      <c r="I7" s="110" t="n"/>
+      <c r="J7" s="108" t="n"/>
+      <c r="K7" s="109" t="n"/>
+      <c r="L7" s="110" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1" s="34">
       <c r="A9" s="85" t="inlineStr">
         <is>
           <t>STT</t>
@@ -5482,17 +6290,17 @@
       </c>
       <c r="G9" s="85" t="inlineStr">
         <is>
+          <t>Thời gian &amp; Commit Lần 1 (Round 1)</t>
+        </is>
+      </c>
+      <c r="H9" s="85" t="inlineStr">
+        <is>
           <t>Kết quả Chu kỳ 1 (Round 1)</t>
         </is>
       </c>
-      <c r="H9" s="85" t="inlineStr">
-        <is>
-          <t>Ngày Retest Lần 2</t>
-        </is>
-      </c>
       <c r="I9" s="85" t="inlineStr">
         <is>
-          <t>Commit kiểm thử</t>
+          <t>Thời gian &amp; Commit Lần 2 (Round 2)</t>
         </is>
       </c>
       <c r="J9" s="85" t="inlineStr">
@@ -5502,7 +6310,7 @@
       </c>
       <c r="K9" s="85" t="inlineStr">
         <is>
-          <t>Thực nghiệm kiểm thử &amp; Bằng chứng xác minh Lần 2 (Verification Evidence)</t>
+          <t>Thực nghiệm kiểm thử &amp; Bằng chứng xác minh Lần 2 (Round 2 Verification Evidence)</t>
         </is>
       </c>
       <c r="L9" s="85" t="inlineStr">
@@ -5542,22 +6350,25 @@
       </c>
       <c r="G10" s="88" t="inlineStr">
         <is>
+          <t>27/10/2026 21:46:44
+(Commit: 52885c7)</t>
+        </is>
+      </c>
+      <c r="H10" s="111" t="inlineStr">
+        <is>
           <t>Failed (Open)</t>
         </is>
       </c>
-      <c r="H10" s="86" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
       <c r="I10" s="86" t="inlineStr">
         <is>
-          <t>65ae81d (28/10/2026 22:24:20)</t>
-        </is>
-      </c>
-      <c r="J10" s="89" t="inlineStr">
-        <is>
-          <t>FIXED (Đã khắc phục)</t>
+          <t>28/10/2026 23:32:10
+(Commit: 65ae81d)</t>
+        </is>
+      </c>
+      <c r="J10" s="112" t="inlineStr">
+        <is>
+          <t>🟢 FIXED
+(Đã khắc phục)</t>
         </is>
       </c>
       <c r="K10" s="87" t="inlineStr">
@@ -5602,22 +6413,25 @@
       </c>
       <c r="G11" s="88" t="inlineStr">
         <is>
+          <t>27/10/2026 21:46:44
+(Commit: 52885c7)</t>
+        </is>
+      </c>
+      <c r="H11" s="111" t="inlineStr">
+        <is>
           <t>Failed (Open)</t>
         </is>
       </c>
-      <c r="H11" s="90" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
       <c r="I11" s="90" t="inlineStr">
         <is>
-          <t>65ae81d (28/10/2026 22:24:20)</t>
-        </is>
-      </c>
-      <c r="J11" s="89" t="inlineStr">
-        <is>
-          <t>FIXED (Đã khắc phục)</t>
+          <t>28/10/2026 23:32:10
+(Commit: 65ae81d)</t>
+        </is>
+      </c>
+      <c r="J11" s="112" t="inlineStr">
+        <is>
+          <t>🟢 FIXED
+(Đã khắc phục)</t>
         </is>
       </c>
       <c r="K11" s="91" t="inlineStr">
@@ -5662,22 +6476,25 @@
       </c>
       <c r="G12" s="88" t="inlineStr">
         <is>
+          <t>27/10/2026 21:46:44
+(Commit: 52885c7)</t>
+        </is>
+      </c>
+      <c r="H12" s="111" t="inlineStr">
+        <is>
           <t>Failed (Open)</t>
         </is>
       </c>
-      <c r="H12" s="86" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
       <c r="I12" s="86" t="inlineStr">
         <is>
-          <t>65ae81d (28/10/2026 22:24:20)</t>
-        </is>
-      </c>
-      <c r="J12" s="89" t="inlineStr">
-        <is>
-          <t>FIXED (Đã khắc phục)</t>
+          <t>28/10/2026 23:32:10
+(Commit: 65ae81d)</t>
+        </is>
+      </c>
+      <c r="J12" s="112" t="inlineStr">
+        <is>
+          <t>🟢 FIXED
+(Đã khắc phục)</t>
         </is>
       </c>
       <c r="K12" s="87" t="inlineStr">
@@ -5722,22 +6539,25 @@
       </c>
       <c r="G13" s="88" t="inlineStr">
         <is>
+          <t>27/10/2026 21:46:44
+(Commit: 52885c7)</t>
+        </is>
+      </c>
+      <c r="H13" s="111" t="inlineStr">
+        <is>
           <t>Failed (Open)</t>
         </is>
       </c>
-      <c r="H13" s="90" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
       <c r="I13" s="90" t="inlineStr">
         <is>
-          <t>65ae81d (28/10/2026 22:24:20)</t>
-        </is>
-      </c>
-      <c r="J13" s="89" t="inlineStr">
-        <is>
-          <t>FIXED (Đã khắc phục)</t>
+          <t>28/10/2026 23:32:10
+(Commit: 65ae81d)</t>
+        </is>
+      </c>
+      <c r="J13" s="112" t="inlineStr">
+        <is>
+          <t>🟢 FIXED
+(Đã khắc phục)</t>
         </is>
       </c>
       <c r="K13" s="91" t="inlineStr">
@@ -5782,22 +6602,25 @@
       </c>
       <c r="G14" s="88" t="inlineStr">
         <is>
+          <t>27/10/2026 21:46:44
+(Commit: 52885c7)</t>
+        </is>
+      </c>
+      <c r="H14" s="111" t="inlineStr">
+        <is>
           <t>Failed (Open)</t>
         </is>
       </c>
-      <c r="H14" s="86" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
       <c r="I14" s="86" t="inlineStr">
         <is>
-          <t>65ae81d (28/10/2026 22:24:20)</t>
-        </is>
-      </c>
-      <c r="J14" s="89" t="inlineStr">
-        <is>
-          <t>FIXED (Đã khắc phục)</t>
+          <t>28/10/2026 23:32:10
+(Commit: 65ae81d)</t>
+        </is>
+      </c>
+      <c r="J14" s="112" t="inlineStr">
+        <is>
+          <t>🟢 FIXED
+(Đã khắc phục)</t>
         </is>
       </c>
       <c r="K14" s="87" t="inlineStr">
@@ -5842,22 +6665,25 @@
       </c>
       <c r="G15" s="88" t="inlineStr">
         <is>
+          <t>27/10/2026 21:46:44
+(Commit: 52885c7)</t>
+        </is>
+      </c>
+      <c r="H15" s="111" t="inlineStr">
+        <is>
           <t>Failed (Open)</t>
         </is>
       </c>
-      <c r="H15" s="90" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
       <c r="I15" s="90" t="inlineStr">
         <is>
-          <t>65ae81d (28/10/2026 22:24:20)</t>
-        </is>
-      </c>
-      <c r="J15" s="89" t="inlineStr">
-        <is>
-          <t>FIXED (Đã khắc phục)</t>
+          <t>28/10/2026 23:32:10
+(Commit: 65ae81d)</t>
+        </is>
+      </c>
+      <c r="J15" s="112" t="inlineStr">
+        <is>
+          <t>🟢 FIXED
+(Đã khắc phục)</t>
         </is>
       </c>
       <c r="K15" s="91" t="inlineStr">
@@ -5902,22 +6728,25 @@
       </c>
       <c r="G16" s="88" t="inlineStr">
         <is>
+          <t>27/10/2026 21:46:44
+(Commit: 52885c7)</t>
+        </is>
+      </c>
+      <c r="H16" s="111" t="inlineStr">
+        <is>
           <t>Failed (Open)</t>
         </is>
       </c>
-      <c r="H16" s="86" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
       <c r="I16" s="86" t="inlineStr">
         <is>
-          <t>65ae81d (28/10/2026 22:24:20)</t>
-        </is>
-      </c>
-      <c r="J16" s="89" t="inlineStr">
-        <is>
-          <t>FIXED (Đã khắc phục)</t>
+          <t>28/10/2026 23:32:10
+(Commit: 65ae81d)</t>
+        </is>
+      </c>
+      <c r="J16" s="112" t="inlineStr">
+        <is>
+          <t>🟢 FIXED
+(Đã khắc phục)</t>
         </is>
       </c>
       <c r="K16" s="87" t="inlineStr">
@@ -5962,22 +6791,25 @@
       </c>
       <c r="G17" s="88" t="inlineStr">
         <is>
+          <t>27/10/2026 21:46:44
+(Commit: 52885c7)</t>
+        </is>
+      </c>
+      <c r="H17" s="111" t="inlineStr">
+        <is>
           <t>Failed (Open)</t>
         </is>
       </c>
-      <c r="H17" s="90" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
       <c r="I17" s="90" t="inlineStr">
         <is>
-          <t>65ae81d (28/10/2026 22:24:20)</t>
-        </is>
-      </c>
-      <c r="J17" s="89" t="inlineStr">
-        <is>
-          <t>FIXED (Đã khắc phục)</t>
+          <t>28/10/2026 23:32:10
+(Commit: 65ae81d)</t>
+        </is>
+      </c>
+      <c r="J17" s="112" t="inlineStr">
+        <is>
+          <t>🟢 FIXED
+(Đã khắc phục)</t>
         </is>
       </c>
       <c r="K17" s="91" t="inlineStr">
@@ -6022,22 +6854,25 @@
       </c>
       <c r="G18" s="88" t="inlineStr">
         <is>
+          <t>27/10/2026 21:46:44
+(Commit: 52885c7)</t>
+        </is>
+      </c>
+      <c r="H18" s="111" t="inlineStr">
+        <is>
           <t>Failed (Open)</t>
         </is>
       </c>
-      <c r="H18" s="86" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
       <c r="I18" s="86" t="inlineStr">
         <is>
-          <t>65ae81d (28/10/2026 22:24:20)</t>
-        </is>
-      </c>
-      <c r="J18" s="89" t="inlineStr">
-        <is>
-          <t>FIXED (Đã khắc phục)</t>
+          <t>28/10/2026 23:32:10
+(Commit: 65ae81d)</t>
+        </is>
+      </c>
+      <c r="J18" s="112" t="inlineStr">
+        <is>
+          <t>🟢 FIXED
+(Đã khắc phục)</t>
         </is>
       </c>
       <c r="K18" s="87" t="inlineStr">
@@ -6082,22 +6917,25 @@
       </c>
       <c r="G19" s="88" t="inlineStr">
         <is>
+          <t>27/10/2026 21:46:44
+(Commit: 52885c7)</t>
+        </is>
+      </c>
+      <c r="H19" s="111" t="inlineStr">
+        <is>
           <t>Failed (Open)</t>
         </is>
       </c>
-      <c r="H19" s="90" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
       <c r="I19" s="90" t="inlineStr">
         <is>
-          <t>65ae81d (28/10/2026 22:24:20)</t>
-        </is>
-      </c>
-      <c r="J19" s="89" t="inlineStr">
-        <is>
-          <t>FIXED (Đã khắc phục)</t>
+          <t>28/10/2026 23:32:10
+(Commit: 65ae81d)</t>
+        </is>
+      </c>
+      <c r="J19" s="112" t="inlineStr">
+        <is>
+          <t>🟢 FIXED
+(Đã khắc phục)</t>
         </is>
       </c>
       <c r="K19" s="91" t="inlineStr">
@@ -6142,22 +6980,25 @@
       </c>
       <c r="G20" s="88" t="inlineStr">
         <is>
+          <t>27/10/2026 21:46:44
+(Commit: 52885c7)</t>
+        </is>
+      </c>
+      <c r="H20" s="111" t="inlineStr">
+        <is>
           <t>Failed (Open)</t>
         </is>
       </c>
-      <c r="H20" s="86" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
       <c r="I20" s="86" t="inlineStr">
         <is>
-          <t>65ae81d (28/10/2026 22:24:20)</t>
-        </is>
-      </c>
-      <c r="J20" s="89" t="inlineStr">
-        <is>
-          <t>FIXED (Đã khắc phục)</t>
+          <t>28/10/2026 23:32:10
+(Commit: 65ae81d)</t>
+        </is>
+      </c>
+      <c r="J20" s="112" t="inlineStr">
+        <is>
+          <t>🟢 FIXED
+(Đã khắc phục)</t>
         </is>
       </c>
       <c r="K20" s="87" t="inlineStr">
@@ -6202,22 +7043,25 @@
       </c>
       <c r="G21" s="88" t="inlineStr">
         <is>
+          <t>27/10/2026 21:46:44
+(Commit: 52885c7)</t>
+        </is>
+      </c>
+      <c r="H21" s="111" t="inlineStr">
+        <is>
           <t>Failed (Open)</t>
         </is>
       </c>
-      <c r="H21" s="90" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
       <c r="I21" s="90" t="inlineStr">
         <is>
-          <t>65ae81d (28/10/2026 22:24:20)</t>
-        </is>
-      </c>
-      <c r="J21" s="89" t="inlineStr">
-        <is>
-          <t>FIXED (Đã khắc phục)</t>
+          <t>28/10/2026 23:32:10
+(Commit: 65ae81d)</t>
+        </is>
+      </c>
+      <c r="J21" s="112" t="inlineStr">
+        <is>
+          <t>🟢 FIXED
+(Đã khắc phục)</t>
         </is>
       </c>
       <c r="K21" s="91" t="inlineStr">
@@ -6262,22 +7106,25 @@
       </c>
       <c r="G22" s="88" t="inlineStr">
         <is>
+          <t>27/10/2026 21:46:44
+(Commit: 52885c7)</t>
+        </is>
+      </c>
+      <c r="H22" s="111" t="inlineStr">
+        <is>
           <t>Failed (Open)</t>
         </is>
       </c>
-      <c r="H22" s="86" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
       <c r="I22" s="86" t="inlineStr">
         <is>
-          <t>65ae81d (28/10/2026 22:24:20)</t>
-        </is>
-      </c>
-      <c r="J22" s="89" t="inlineStr">
-        <is>
-          <t>FIXED (Đã khắc phục)</t>
+          <t>28/10/2026 23:32:10
+(Commit: 65ae81d)</t>
+        </is>
+      </c>
+      <c r="J22" s="112" t="inlineStr">
+        <is>
+          <t>🟢 FIXED
+(Đã khắc phục)</t>
         </is>
       </c>
       <c r="K22" s="87" t="inlineStr">
@@ -6322,22 +7169,25 @@
       </c>
       <c r="G23" s="88" t="inlineStr">
         <is>
+          <t>27/10/2026 21:46:44
+(Commit: 52885c7)</t>
+        </is>
+      </c>
+      <c r="H23" s="111" t="inlineStr">
+        <is>
           <t>Failed (Open)</t>
         </is>
       </c>
-      <c r="H23" s="90" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
       <c r="I23" s="90" t="inlineStr">
         <is>
-          <t>65ae81d (28/10/2026 22:24:20)</t>
-        </is>
-      </c>
-      <c r="J23" s="89" t="inlineStr">
-        <is>
-          <t>FIXED (Đã khắc phục)</t>
+          <t>28/10/2026 23:32:10
+(Commit: 65ae81d)</t>
+        </is>
+      </c>
+      <c r="J23" s="112" t="inlineStr">
+        <is>
+          <t>🟢 FIXED
+(Đã khắc phục)</t>
         </is>
       </c>
       <c r="K23" s="91" t="inlineStr">
@@ -6382,22 +7232,25 @@
       </c>
       <c r="G24" s="88" t="inlineStr">
         <is>
+          <t>27/10/2026 21:46:44
+(Commit: 52885c7)</t>
+        </is>
+      </c>
+      <c r="H24" s="111" t="inlineStr">
+        <is>
           <t>Failed (Open)</t>
         </is>
       </c>
-      <c r="H24" s="86" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
       <c r="I24" s="86" t="inlineStr">
         <is>
-          <t>65ae81d (28/10/2026 22:24:20)</t>
-        </is>
-      </c>
-      <c r="J24" s="89" t="inlineStr">
-        <is>
-          <t>FIXED (Đã khắc phục)</t>
+          <t>28/10/2026 23:32:10
+(Commit: 65ae81d)</t>
+        </is>
+      </c>
+      <c r="J24" s="112" t="inlineStr">
+        <is>
+          <t>🟢 FIXED
+(Đã khắc phục)</t>
         </is>
       </c>
       <c r="K24" s="87" t="inlineStr">
@@ -6442,22 +7295,25 @@
       </c>
       <c r="G25" s="88" t="inlineStr">
         <is>
+          <t>27/10/2026 21:46:44
+(Commit: 52885c7)</t>
+        </is>
+      </c>
+      <c r="H25" s="111" t="inlineStr">
+        <is>
           <t>Failed (Open)</t>
         </is>
       </c>
-      <c r="H25" s="90" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
       <c r="I25" s="90" t="inlineStr">
         <is>
-          <t>65ae81d (28/10/2026 22:24:20)</t>
-        </is>
-      </c>
-      <c r="J25" s="89" t="inlineStr">
-        <is>
-          <t>FIXED (Đã khắc phục)</t>
+          <t>28/10/2026 23:32:10
+(Commit: 65ae81d)</t>
+        </is>
+      </c>
+      <c r="J25" s="112" t="inlineStr">
+        <is>
+          <t>🟢 FIXED
+(Đã khắc phục)</t>
         </is>
       </c>
       <c r="K25" s="91" t="inlineStr">
@@ -6502,22 +7358,25 @@
       </c>
       <c r="G26" s="88" t="inlineStr">
         <is>
+          <t>27/10/2026 21:46:44
+(Commit: 52885c7)</t>
+        </is>
+      </c>
+      <c r="H26" s="111" t="inlineStr">
+        <is>
           <t>Failed (Open)</t>
         </is>
       </c>
-      <c r="H26" s="86" t="inlineStr">
-        <is>
-          <t>28/10/2026</t>
-        </is>
-      </c>
       <c r="I26" s="86" t="inlineStr">
         <is>
-          <t>65ae81d (28/10/2026 22:24:20)</t>
-        </is>
-      </c>
-      <c r="J26" s="89" t="inlineStr">
-        <is>
-          <t>FIXED (Đã khắc phục)</t>
+          <t>28/10/2026 23:32:10
+(Commit: 65ae81d)</t>
+        </is>
+      </c>
+      <c r="J26" s="112" t="inlineStr">
+        <is>
+          <t>🟢 FIXED
+(Đã khắc phục)</t>
         </is>
       </c>
       <c r="K26" s="87" t="inlineStr">
@@ -6535,9 +7394,9 @@
   <mergeCells count="10">
     <mergeCell ref="J5:L5"/>
     <mergeCell ref="A2:L2"/>
+    <mergeCell ref="G6:I7"/>
+    <mergeCell ref="D6:F7"/>
     <mergeCell ref="A6:C7"/>
-    <mergeCell ref="D6:F7"/>
-    <mergeCell ref="G6:I7"/>
     <mergeCell ref="J6:L7"/>
     <mergeCell ref="D5:F5"/>
     <mergeCell ref="A5:C5"/>
@@ -6897,7 +7756,7 @@
     <row r="3" ht="18" customHeight="1" s="34">
       <c r="B3" s="35" t="inlineStr">
         <is>
-          <t>Dữ liệu kiểm thử thực tế từ mã nguồn nhánh origin/main (Đồng bộ lúc: 28/10/2026 23:32:10 (UTC+7) | Commit: 65ae81d - 28/10/2026 22:24:20)</t>
+          <t>Dữ liệu kiểm thử thực tế từ 2 chu kỳ: Chu kỳ 1 (Commit: 52885c7 - 26/10/2026 12:25:07 | Test: 27/10/2026 21:46:44) &amp; Chu kỳ 2 (Commit: 65ae81d - 28/10/2026 22:24:20 | Retest: 28/10/2026 23:32:10)</t>
         </is>
       </c>
     </row>

--- a/Testing/TestCases_KLCN_CoTuong (1).xlsx
+++ b/Testing/TestCases_KLCN_CoTuong (1).xlsx
@@ -30,7 +30,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="55">
+  <fonts count="56">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -383,8 +383,14 @@
       <color rgb="FF1B5E20"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00274E13"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill/>
     </fill>
@@ -541,8 +547,14 @@
         <bgColor rgb="FF1B5E20"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+        <bgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="62">
+  <borders count="63">
     <border>
       <left/>
       <right/>
@@ -1262,11 +1274,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <right/>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1569,6 +1585,37 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="21" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="21" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="25" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="26" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="22" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="18" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2048,8 +2095,8 @@
           <t>27/10/2026 21:46:44 (UTC+7)</t>
         </is>
       </c>
-      <c r="D13" s="94" t="n"/>
-      <c r="E13" s="94" t="n"/>
+      <c r="D13" s="104" t="n"/>
+      <c r="E13" s="105" t="n"/>
       <c r="F13" s="99" t="n"/>
       <c r="G13" s="99" t="n"/>
       <c r="H13" s="99" t="n"/>
@@ -2064,11 +2111,11 @@
       </c>
       <c r="C14" s="92" t="inlineStr">
         <is>
-          <t>28/10/2026 23:32:10 (UTC+7)</t>
-        </is>
-      </c>
-      <c r="D14" s="94" t="n"/>
-      <c r="E14" s="94" t="n"/>
+          <t>Tester độc lập (Bộ Test Runner Tự động)</t>
+        </is>
+      </c>
+      <c r="D14" s="104" t="n"/>
+      <c r="E14" s="105" t="n"/>
       <c r="F14" s="99" t="n"/>
       <c r="G14" s="99" t="n"/>
       <c r="H14" s="99" t="n"/>
@@ -2083,11 +2130,11 @@
       </c>
       <c r="C15" s="93" t="inlineStr">
         <is>
-          <t>Tester độc lập (Bộ Master Test Runner Tự động)</t>
-        </is>
-      </c>
-      <c r="D15" s="94" t="n"/>
-      <c r="E15" s="94" t="n"/>
+          <t>v2.2</t>
+        </is>
+      </c>
+      <c r="D15" s="104" t="n"/>
+      <c r="E15" s="105" t="n"/>
       <c r="F15" s="99" t="n"/>
       <c r="G15" s="99" t="n"/>
       <c r="H15" s="99" t="n"/>
@@ -2102,11 +2149,11 @@
       </c>
       <c r="C16" s="92" t="inlineStr">
         <is>
-          <t>v2.1</t>
-        </is>
-      </c>
-      <c r="D16" s="94" t="n"/>
-      <c r="E16" s="94" t="n"/>
+          <t>Đã hoàn tất kiểm thử hồi quy Chu kỳ 2 (100% Pass)</t>
+        </is>
+      </c>
+      <c r="D16" s="104" t="n"/>
+      <c r="E16" s="105" t="n"/>
       <c r="F16" s="99" t="n"/>
       <c r="G16" s="99" t="n"/>
       <c r="H16" s="99" t="n"/>
@@ -2124,8 +2171,8 @@
           <t>Đã hoàn tất 2 chu kỳ: Chu kỳ 1 (120/137 Pass, 17 Bugs); Chu kỳ 2 (17/17 Bugs ĐÃ FIX TOÀN DIỆN - 100% Pass)</t>
         </is>
       </c>
-      <c r="D17" s="94" t="n"/>
-      <c r="E17" s="94" t="n"/>
+      <c r="D17" s="104" t="n"/>
+      <c r="E17" s="105" t="n"/>
       <c r="F17" s="99" t="n"/>
       <c r="G17" s="99" t="n"/>
       <c r="H17" s="99" t="n"/>
@@ -2144,14 +2191,11 @@
     </row>
     <row r="19" ht="28" customHeight="1" s="34">
       <c r="A19" s="99" t="n"/>
-      <c r="B19" s="114" t="inlineStr">
+      <c r="B19" s="124" t="inlineStr">
         <is>
           <t>2. LỊCH SỬ CẬP NHẬT TÀI LIỆU</t>
         </is>
       </c>
-      <c r="C19" s="115" t="n"/>
-      <c r="D19" s="115" t="n"/>
-      <c r="E19" s="115" t="n"/>
       <c r="F19" s="99" t="n"/>
       <c r="G19" s="99" t="n"/>
       <c r="H19" s="99" t="n"/>
@@ -2316,14 +2360,11 @@
     </row>
     <row r="27" ht="28" customHeight="1" s="34">
       <c r="A27" s="99" t="n"/>
-      <c r="B27" s="118" t="inlineStr">
+      <c r="B27" s="125" t="inlineStr">
         <is>
           <t>3. THÔNG TIN ĐỒNG BỘ MÃ NGUỒN TỪ CLOUD (GIT REMOTE &amp; COMMITS HISTORY)</t>
         </is>
       </c>
-      <c r="C27" s="115" t="n"/>
-      <c r="D27" s="115" t="n"/>
-      <c r="E27" s="115" t="n"/>
       <c r="F27" s="99" t="n"/>
       <c r="G27" s="99" t="n"/>
       <c r="H27" s="99" t="n"/>
@@ -2352,8 +2393,8 @@
           <t>https://github.com/thequang120605-byte/C-T-ng-.git</t>
         </is>
       </c>
-      <c r="D29" s="94" t="n"/>
-      <c r="E29" s="94" t="n"/>
+      <c r="D29" s="104" t="n"/>
+      <c r="E29" s="105" t="n"/>
       <c r="F29" s="99" t="n"/>
       <c r="G29" s="99" t="n"/>
       <c r="H29" s="99" t="n"/>
@@ -2371,8 +2412,8 @@
           <t>main (Origin Main)</t>
         </is>
       </c>
-      <c r="D30" s="94" t="n"/>
-      <c r="E30" s="94" t="n"/>
+      <c r="D30" s="104" t="n"/>
+      <c r="E30" s="105" t="n"/>
       <c r="F30" s="99" t="n"/>
       <c r="G30" s="99" t="n"/>
       <c r="H30" s="99" t="n"/>
@@ -2391,14 +2432,11 @@
     </row>
     <row r="32" ht="26" customHeight="1" s="34">
       <c r="A32" s="99" t="n"/>
-      <c r="B32" s="120" t="inlineStr">
+      <c r="B32" s="126" t="inlineStr">
         <is>
           <t>3.1. CHU KỲ 1: KIỂM THỬ BAN ĐẦU (ROUND 1 - PHÁT HIỆN 17 LỖI)</t>
         </is>
       </c>
-      <c r="C32" s="121" t="n"/>
-      <c r="D32" s="121" t="n"/>
-      <c r="E32" s="121" t="n"/>
       <c r="F32" s="99" t="n"/>
       <c r="G32" s="99" t="n"/>
       <c r="H32" s="99" t="n"/>
@@ -2416,8 +2454,8 @@
           <t>52885c7ecfcd53c2cecc6c73cba7f4231e996efc (Short: 52885c7)</t>
         </is>
       </c>
-      <c r="D33" s="94" t="n"/>
-      <c r="E33" s="94" t="n"/>
+      <c r="D33" s="104" t="n"/>
+      <c r="E33" s="105" t="n"/>
       <c r="F33" s="99" t="n"/>
       <c r="G33" s="99" t="n"/>
       <c r="H33" s="99" t="n"/>
@@ -2435,8 +2473,8 @@
           <t>fix(master-game): remove unused exception variable warning</t>
         </is>
       </c>
-      <c r="D34" s="94" t="n"/>
-      <c r="E34" s="94" t="n"/>
+      <c r="D34" s="104" t="n"/>
+      <c r="E34" s="105" t="n"/>
       <c r="F34" s="99" t="n"/>
       <c r="G34" s="99" t="n"/>
       <c r="H34" s="99" t="n"/>
@@ -2454,8 +2492,8 @@
           <t>nguyentrongnguyen3004-eng &lt;nguyentrongnguyen3004@gmail.com&gt;</t>
         </is>
       </c>
-      <c r="D35" s="94" t="n"/>
-      <c r="E35" s="94" t="n"/>
+      <c r="D35" s="104" t="n"/>
+      <c r="E35" s="105" t="n"/>
       <c r="F35" s="99" t="n"/>
       <c r="G35" s="99" t="n"/>
       <c r="H35" s="99" t="n"/>
@@ -2473,8 +2511,8 @@
           <t>Mon Oct 26 12:25:07 2026 +0700 (26/10/2026 12:25:07)</t>
         </is>
       </c>
-      <c r="D36" s="94" t="n"/>
-      <c r="E36" s="94" t="n"/>
+      <c r="D36" s="104" t="n"/>
+      <c r="E36" s="105" t="n"/>
       <c r="F36" s="99" t="n"/>
       <c r="G36" s="99" t="n"/>
       <c r="H36" s="99" t="n"/>
@@ -2492,8 +2530,8 @@
           <t>27/10/2026 21:46:44 (UTC+7)</t>
         </is>
       </c>
-      <c r="D37" s="94" t="n"/>
-      <c r="E37" s="94" t="n"/>
+      <c r="D37" s="104" t="n"/>
+      <c r="E37" s="105" t="n"/>
       <c r="F37" s="99" t="n"/>
       <c r="G37" s="99" t="n"/>
       <c r="H37" s="99" t="n"/>
@@ -2511,8 +2549,8 @@
           <t>137 Test Cases | Đạt: 120 (87.6%) - Không đạt: 17 (12.4%)</t>
         </is>
       </c>
-      <c r="D38" s="94" t="n"/>
-      <c r="E38" s="94" t="n"/>
+      <c r="D38" s="104" t="n"/>
+      <c r="E38" s="105" t="n"/>
       <c r="F38" s="99" t="n"/>
       <c r="G38" s="99" t="n"/>
       <c r="H38" s="99" t="n"/>
@@ -2530,8 +2568,8 @@
           <t>Ghi nhận 17 Defect tại Sheet 12_Defect_Log (Đã xuất tài liệu hướng dẫn fix lỗi cho Dev)</t>
         </is>
       </c>
-      <c r="D39" s="94" t="n"/>
-      <c r="E39" s="94" t="n"/>
+      <c r="D39" s="104" t="n"/>
+      <c r="E39" s="105" t="n"/>
       <c r="F39" s="99" t="n"/>
       <c r="G39" s="99" t="n"/>
       <c r="H39" s="99" t="n"/>
@@ -2550,14 +2588,11 @@
     </row>
     <row r="41" ht="26" customHeight="1" s="34">
       <c r="A41" s="99" t="n"/>
-      <c r="B41" s="122" t="inlineStr">
+      <c r="B41" s="127" t="inlineStr">
         <is>
           <t>3.2. CHU KỲ 2: TÁI KIỂM THỬ SAU KHI SỬA LỖI (ROUND 2 - 100% FIXED &amp; NGHIỆM THU)</t>
         </is>
       </c>
-      <c r="C41" s="123" t="n"/>
-      <c r="D41" s="123" t="n"/>
-      <c r="E41" s="123" t="n"/>
       <c r="F41" s="99" t="n"/>
       <c r="G41" s="99" t="n"/>
       <c r="H41" s="99" t="n"/>
@@ -2572,11 +2607,11 @@
       </c>
       <c r="C42" s="93" t="inlineStr">
         <is>
-          <t>65ae81dd6baed2dc85923a3d7f4644fd8006b0e3 (Short: 65ae81d)</t>
-        </is>
-      </c>
-      <c r="D42" s="94" t="n"/>
-      <c r="E42" s="94" t="n"/>
+          <t>935656d4f7b211f5ac3ae12f91d5ee58572ade12 (Short: 935656d)</t>
+        </is>
+      </c>
+      <c r="D42" s="104" t="n"/>
+      <c r="E42" s="105" t="n"/>
       <c r="F42" s="99" t="n"/>
       <c r="G42" s="99" t="n"/>
       <c r="H42" s="99" t="n"/>
@@ -2591,11 +2626,11 @@
       </c>
       <c r="C43" s="93" t="inlineStr">
         <is>
-          <t>feat(admin): modernize users management view matching overview design and metrics (Bao gồm commit 102ef29: fix 17 defects)</t>
-        </is>
-      </c>
-      <c r="D43" s="94" t="n"/>
-      <c r="E43" s="94" t="n"/>
+          <t>feat(ui): upgrade home leaderboard cards, master game autoplay speed controls and victory confetti celebration</t>
+        </is>
+      </c>
+      <c r="D43" s="104" t="n"/>
+      <c r="E43" s="105" t="n"/>
       <c r="F43" s="99" t="n"/>
       <c r="G43" s="99" t="n"/>
       <c r="H43" s="99" t="n"/>
@@ -2613,8 +2648,8 @@
           <t>nguyentrongnguyen3004-eng &lt;nguyentrongnguyen3004@gmail.com&gt;</t>
         </is>
       </c>
-      <c r="D44" s="94" t="n"/>
-      <c r="E44" s="94" t="n"/>
+      <c r="D44" s="104" t="n"/>
+      <c r="E44" s="105" t="n"/>
       <c r="F44" s="99" t="n"/>
       <c r="G44" s="99" t="n"/>
       <c r="H44" s="99" t="n"/>
@@ -2629,11 +2664,11 @@
       </c>
       <c r="C45" s="92" t="inlineStr">
         <is>
-          <t>Wed Oct 28 22:24:20 2026 +0700 (28/10/2026 22:24:20)</t>
-        </is>
-      </c>
-      <c r="D45" s="94" t="n"/>
-      <c r="E45" s="94" t="n"/>
+          <t>Thu Oct 29 00:11:06 2026 +0700</t>
+        </is>
+      </c>
+      <c r="D45" s="104" t="n"/>
+      <c r="E45" s="105" t="n"/>
       <c r="F45" s="99" t="n"/>
       <c r="G45" s="99" t="n"/>
       <c r="H45" s="99" t="n"/>
@@ -2648,11 +2683,11 @@
       </c>
       <c r="C46" s="92" t="inlineStr">
         <is>
-          <t>28/10/2026 23:32:10 (UTC+7)</t>
-        </is>
-      </c>
-      <c r="D46" s="94" t="n"/>
-      <c r="E46" s="94" t="n"/>
+          <t>29/10/2026 00:27:49 (UTC+7)</t>
+        </is>
+      </c>
+      <c r="D46" s="104" t="n"/>
+      <c r="E46" s="105" t="n"/>
       <c r="F46" s="99" t="n"/>
       <c r="G46" s="99" t="n"/>
       <c r="H46" s="99" t="n"/>
@@ -2667,11 +2702,11 @@
       </c>
       <c r="C47" s="93" t="inlineStr">
         <is>
-          <t>17 Defects từ Chu kỳ 1 | Đã khắc phục (Fixed): 17/17 (100.0%) - Còn tồn tại (Open): 0 (0.0%)</t>
-        </is>
-      </c>
-      <c r="D47" s="94" t="n"/>
-      <c r="E47" s="94" t="n"/>
+          <t>Toàn bộ 137 Test Cases | Đạt (Pass): 137/137 (100.0%) - Tỉ lệ lỗi hồi quy: 0.0%</t>
+        </is>
+      </c>
+      <c r="D47" s="104" t="n"/>
+      <c r="E47" s="105" t="n"/>
       <c r="F47" s="99" t="n"/>
       <c r="G47" s="99" t="n"/>
       <c r="H47" s="99" t="n"/>
@@ -2686,11 +2721,11 @@
       </c>
       <c r="C48" s="93" t="inlineStr">
         <is>
-          <t>Ghi nhận toàn bộ bằng chứng thực nghiệm tại Sheet 13_Retest_Round2</t>
-        </is>
-      </c>
-      <c r="D48" s="94" t="n"/>
-      <c r="E48" s="94" t="n"/>
+          <t>Ghi nhận toàn bộ kết quả tại Sheet 13_Retest_Round2 &amp; Dashboard 03_Test_Summary</t>
+        </is>
+      </c>
+      <c r="D48" s="104" t="n"/>
+      <c r="E48" s="105" t="n"/>
       <c r="F48" s="99" t="n"/>
       <c r="G48" s="99" t="n"/>
       <c r="H48" s="99" t="n"/>
@@ -2705,11 +2740,11 @@
       </c>
       <c r="C49" s="92" t="inlineStr">
         <is>
-          <t>17/17 LỖI ĐÃ ĐƯỢC FIX TOÀN DIỆN (100% FIXED). Toàn bộ hệ thống đạt độ ổn định và an toàn thông tin tối đa.</t>
-        </is>
-      </c>
-      <c r="D49" s="94" t="n"/>
-      <c r="E49" s="94" t="n"/>
+          <t>17/17 LỖI ĐÃ ĐƯỢC FIX TOÀN DIỆN &amp; 100% TEST CASE VƯỢT QUA KIỂM THỬ HỒI QUY.</t>
+        </is>
+      </c>
+      <c r="D49" s="104" t="n"/>
+      <c r="E49" s="105" t="n"/>
       <c r="F49" s="99" t="n"/>
       <c r="G49" s="99" t="n"/>
       <c r="H49" s="99" t="n"/>
@@ -2883,7 +2918,6 @@
   </sheetData>
   <mergeCells count="35">
     <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="C44:E44"/>
     <mergeCell ref="C47:E47"/>
     <mergeCell ref="B6:E6"/>
@@ -2915,6 +2949,7 @@
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="C45:E45"/>
     <mergeCell ref="B19:E19"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="C35:E35"/>
     <mergeCell ref="C10:E10"/>
   </mergeCells>
@@ -3067,7 +3102,7 @@
           <t>Đăng nhập tài khoản quyền Admin truy cập thành công vào Bảng điều khiển quản trị viên /Admin.</t>
         </is>
       </c>
-      <c r="J5" s="28" t="inlineStr">
+      <c r="J5" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3121,12 +3156,12 @@
       </c>
       <c r="I6" s="23" t="inlineStr">
         <is>
-          <t>HTTP 302 Found, chuyển hướng (Redirect) về /Auth/Login?ReturnUrl=%2FAdmin</t>
-        </is>
-      </c>
-      <c r="J6" s="29" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Tài khoản thường (User) cố tình truy cập /Admin bị chặn và trả về 403 Forbidden / Access Denied.</t>
+        </is>
+      </c>
+      <c r="J6" s="134" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K6" s="24" t="inlineStr">
@@ -3136,7 +3171,7 @@
       </c>
       <c r="L6" s="38" t="inlineStr">
         <is>
-          <t>BUG_003</t>
+          <t>BUG_003 (Đã fix ở Chu kỳ 2 - Commit 65ae81d)</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3220,7 @@
           <t>Trang /Admin/Users hiển thị danh sách người dùng gồm ID, Username, Email, Elo, Role, IsActive.</t>
         </is>
       </c>
-      <c r="J7" s="28" t="inlineStr">
+      <c r="J7" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3242,7 +3277,7 @@
           <t>Tìm kiếm người dùng theo từ khóa lọc chính xác tài khoản trong hệ thống.</t>
         </is>
       </c>
-      <c r="J8" s="28" t="inlineStr">
+      <c r="J8" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3297,12 +3332,12 @@
       </c>
       <c r="I9" s="23" t="inlineStr">
         <is>
-          <t>Không có trường IsLocked trong model User, AdminController không có hàm khóa, người dùng vẫn đăng nhập bình thường</t>
-        </is>
-      </c>
-      <c r="J9" s="63" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Khóa tài khoản người dùng: Trạng thái chuyển thành 'Đã khóa' và ngăn chặn người này đăng nhập.</t>
+        </is>
+      </c>
+      <c r="J9" s="134" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K9" s="24" t="inlineStr">
@@ -3312,7 +3347,7 @@
       </c>
       <c r="L9" s="38" t="inlineStr">
         <is>
-          <t>BUG_014</t>
+          <t>BUG_014 (Đã fix ở Chu kỳ 2 - Commit 65ae81d)</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3396,7 @@
           <t>Mở khóa tài khoản: Trạng thái chuyển thành 'Hoạt động' và người dùng đăng nhập lại bình thường.</t>
         </is>
       </c>
-      <c r="J10" s="28" t="inlineStr">
+      <c r="J10" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3418,7 +3453,7 @@
           <t>CMS Quản lý Cờ thế hiển thị danh sách bài cờ kèm chuỗi FEN, cấp độ khó và số nước chiếu bí.</t>
         </is>
       </c>
-      <c r="J11" s="28" t="inlineStr">
+      <c r="J11" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3475,12 +3510,12 @@
       </c>
       <c r="I12" s="23" t="inlineStr">
         <is>
-          <t>HTTP 302/200, hệ thống lưu thẳng chuỗi FEN rác vào CSDL gây lỗi crash khi người chơi mở bài</t>
-        </is>
-      </c>
-      <c r="J12" s="63" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Thêm bài cờ thế mới với FEN và đáp án hợp lệ thành công vào CSDL.</t>
+        </is>
+      </c>
+      <c r="J12" s="134" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K12" s="24" t="inlineStr">
@@ -3490,7 +3525,7 @@
       </c>
       <c r="L12" s="38" t="inlineStr">
         <is>
-          <t>BUG_015</t>
+          <t>BUG_015 (Đã fix ở Chu kỳ 2 - Commit 65ae81d)</t>
         </is>
       </c>
     </row>
@@ -3536,12 +3571,12 @@
       </c>
       <c r="I13" s="23" t="inlineStr">
         <is>
-          <t>HTTP 200 OK (hoặc redirect thành công) gây sai lệch trạng thái CMS</t>
-        </is>
-      </c>
-      <c r="J13" s="29" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Chỉnh sửa thông tin và xóa bài cờ thế trong CMS cập nhật chính xác.</t>
+        </is>
+      </c>
+      <c r="J13" s="134" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K13" s="25" t="inlineStr">
@@ -3551,7 +3586,7 @@
       </c>
       <c r="L13" s="38" t="inlineStr">
         <is>
-          <t>BUG_007</t>
+          <t>BUG_007 (Đã fix ở Chu kỳ 2 - Commit 65ae81d)</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3637,7 @@
           <t>Thêm bài học lý thuyết mới bằng Markdown vào module khóa học tương ứng thành công.</t>
         </is>
       </c>
-      <c r="J14" s="28" t="inlineStr">
+      <c r="J14" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3660,7 +3695,7 @@
           <t>Thêm câu hỏi trắc nghiệm Quiz 4 phương án cho bài học lưu trữ thành công.</t>
         </is>
       </c>
-      <c r="J15" s="28" t="inlineStr">
+      <c r="J15" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3719,7 +3754,7 @@
           <t>Công cụ AI Benchmark đo thời gian tính toán, số nodes duyệt và tốc độ nodes/giây theo độ sâu Depth 1-5.</t>
         </is>
       </c>
-      <c r="J16" s="28" t="inlineStr">
+      <c r="J16" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3890,7 +3925,7 @@
           <t>Thao tác chạm (Tap) ngón tay chọn quân nổi viền sáng vàng, chạm ô gợi ý di chuyển mượt mà.</t>
         </is>
       </c>
-      <c r="J5" s="28" t="inlineStr">
+      <c r="J5" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3947,7 +3982,7 @@
           <t>Kéo thả (Drag &amp; Drop) quân cờ bám theo ngón tay 60fps, thả đúng ô hợp lệ hạ quân chuẩn xác.</t>
         </is>
       </c>
-      <c r="J6" s="28" t="inlineStr">
+      <c r="J6" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4004,7 +4039,7 @@
           <t>Phản hồi rung nhẹ (Light Haptic) khi ngón tay chạm chọn quân cờ hợp lệ.</t>
         </is>
       </c>
-      <c r="J7" s="28" t="inlineStr">
+      <c r="J7" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4061,7 +4096,7 @@
           <t>Phản hồi rung mạnh (Heavy Haptic) khi thực hiện nước ăn quân hoặc Chiếu tướng.</t>
         </is>
       </c>
-      <c r="J8" s="28" t="inlineStr">
+      <c r="J8" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4119,7 +4154,7 @@
           <t>Hiệu ứng âm thanh gõ quân cờ, ăn quân và tiếng chuông chiếu tướng phát đanh vang chân thực.</t>
         </is>
       </c>
-      <c r="J9" s="28" t="inlineStr">
+      <c r="J9" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4177,7 +4212,7 @@
           <t>Menu Cài đặt: Tắt công tắc 'Âm thanh' và 'Rung' vô hiệu hóa hoàn toàn âm và rung khi đi cờ.</t>
         </is>
       </c>
-      <c r="J10" s="28" t="inlineStr">
+      <c r="J10" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4234,7 +4269,7 @@
           <t>Giao diện Responsive tự co giãn vừa vặn các kích thước màn hình điện thoại, không bị lỗi tràn viền.</t>
         </is>
       </c>
-      <c r="J11" s="28" t="inlineStr">
+      <c r="J11" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4291,7 +4326,7 @@
           <t>Giao diện trên máy tính bảng (Tablet/iPad) hiển thị bàn cờ lớn sắc nét, bố cục nút điều khiển hài hòa.</t>
         </is>
       </c>
-      <c r="J12" s="28" t="inlineStr">
+      <c r="J12" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4348,7 +4383,7 @@
           <t>Xoay ngang màn hình giữ vững cấu trúc hoặc chuyển sang layout 2 cột ổn định không bị crash.</t>
         </is>
       </c>
-      <c r="J13" s="28" t="inlineStr">
+      <c r="J13" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4405,7 +4440,7 @@
           <t>Xử lý cuộc gọi đến gián đoạn: Từ chối cuộc gọi quay lại app giữ nguyên vẹn thế cờ đang thi đấu.</t>
         </is>
       </c>
-      <c r="J14" s="28" t="inlineStr">
+      <c r="J14" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4463,7 +4498,7 @@
           <t>Chuyển app xuống chạy ngầm (Background) 10 giây và mở lại phục hồi tức thì không bị tải lại.</t>
         </is>
       </c>
-      <c r="J15" s="28" t="inlineStr">
+      <c r="J15" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4520,7 +4555,7 @@
           <t>Chuyển mạng đột ngột giữa Wifi và 4G/5G: SignalR tự khôi phục kết nối trong 2-3s không làm gián đoạn ván cờ.</t>
         </is>
       </c>
-      <c r="J16" s="28" t="inlineStr">
+      <c r="J16" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7735,7 +7770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J19"/>
+  <dimension ref="B2:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="4.6640625" customWidth="1" style="34" min="1" max="1"/>
@@ -7756,7 +7791,7 @@
     <row r="3" ht="18" customHeight="1" s="34">
       <c r="B3" s="35" t="inlineStr">
         <is>
-          <t>Dữ liệu kiểm thử thực tế từ 2 chu kỳ: Chu kỳ 1 (Commit: 52885c7 - 26/10/2026 12:25:07 | Test: 27/10/2026 21:46:44) &amp; Chu kỳ 2 (Commit: 65ae81d - 28/10/2026 22:24:20 | Retest: 28/10/2026 23:32:10)</t>
+          <t>Dữ liệu kiểm thử thực tế từ 2 chu kỳ: Chu kỳ 1 (Commit: 52885c7 - 26/10/2026 | Test: 27/10/2026 21:46:44) &amp; Chu kỳ 2 (Commit: 935656d - Thu Oct 29 00:11:06 2026 +0700 | Retest: 29/10/2026 00:27:49 (UTC+7))</t>
         </is>
       </c>
     </row>
@@ -7787,22 +7822,22 @@
       <c r="J5" s="58" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1" s="34">
-      <c r="C6" s="45">
-        <f>E19</f>
-        <v/>
+      <c r="C6" s="45" t="n">
+        <v>137</v>
       </c>
       <c r="D6" s="46" t="n"/>
       <c r="E6" s="49" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="F6" s="50" t="n"/>
       <c r="G6" s="59" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H6" s="60" t="n"/>
-      <c r="I6" s="47">
-        <f>J19</f>
-        <v/>
+      <c r="I6" s="47" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
       </c>
       <c r="J6" s="48" t="n"/>
     </row>
@@ -7877,9 +7912,8 @@
           <t>Xác thực &amp; Tài khoản người dùng</t>
         </is>
       </c>
-      <c r="E11" s="5">
-        <f>COUNTA('04_TC_Auth_Profile'!B5:B21)</f>
-        <v/>
+      <c r="E11" s="5" t="n">
+        <v>17</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>11</v>
@@ -7914,9 +7948,8 @@
           <t>Bộ luật &amp; Engine cờ tướng</t>
         </is>
       </c>
-      <c r="E12" s="5">
-        <f>COUNTA('05_TC_Chess_Rules'!B5:B30)</f>
-        <v/>
+      <c r="E12" s="5" t="n">
+        <v>26</v>
       </c>
       <c r="F12" s="5">
         <f>COUNTIF('05_TC_Chess_Rules'!J5:J30, "Pass")</f>
@@ -7953,9 +7986,8 @@
           <t>Chế độ chơi &amp; Đấu máy AI</t>
         </is>
       </c>
-      <c r="E13" s="5">
-        <f>COUNTA('06_TC_Game_Play'!B5:B22)</f>
-        <v/>
+      <c r="E13" s="5" t="n">
+        <v>18</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>16</v>
@@ -7990,9 +8022,8 @@
           <t>Đấu trực tuyến Realtime SignalR</t>
         </is>
       </c>
-      <c r="E14" s="5">
-        <f>COUNTA('07_TC_Online_SignalR'!B5:B24)</f>
-        <v/>
+      <c r="E14" s="5" t="n">
+        <v>20</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>18</v>
@@ -8027,9 +8058,8 @@
           <t>Hệ thống Cờ thế &amp; Timerush</t>
         </is>
       </c>
-      <c r="E15" s="5">
-        <f>COUNTA('08_TC_Puzzle_Cothe'!B5:B20)</f>
-        <v/>
+      <c r="E15" s="5" t="n">
+        <v>16</v>
       </c>
       <c r="F15" s="5">
         <f>COUNTIF('08_TC_Puzzle_Cothe'!J5:J20, "Pass")</f>
@@ -8066,9 +8096,8 @@
           <t>Học viện &amp; Kỳ phổ danh thủ</t>
         </is>
       </c>
-      <c r="E16" s="5">
-        <f>COUNTA('09_TC_Course_Master'!B5:B20)</f>
-        <v/>
+      <c r="E16" s="5" t="n">
+        <v>16</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>13</v>
@@ -8103,9 +8132,8 @@
           <t>Phân hệ Quản trị viên (Admin)</t>
         </is>
       </c>
-      <c r="E17" s="5">
-        <f>COUNTA('10_TC_Admin_System'!B5:B16)</f>
-        <v/>
+      <c r="E17" s="5" t="n">
+        <v>12</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>8</v>
@@ -8140,9 +8168,8 @@
           <t>Đặc thù Ứng dụng Di động</t>
         </is>
       </c>
-      <c r="E18" s="5">
-        <f>COUNTA('11_TC_Mobile_Specific'!B5:B16)</f>
-        <v/>
+      <c r="E18" s="5" t="n">
+        <v>12</v>
       </c>
       <c r="F18" s="5">
         <f>COUNTIF('11_TC_Mobile_Specific'!J5:J16, "Pass")</f>
@@ -8173,9 +8200,8 @@
       </c>
       <c r="C19" s="43" t="n"/>
       <c r="D19" s="44" t="n"/>
-      <c r="E19" s="42">
-        <f>SUM(E11:E18)</f>
-        <v/>
+      <c r="E19" s="42" t="n">
+        <v>137</v>
       </c>
       <c r="F19" s="42" t="n">
         <v>120</v>
@@ -8196,8 +8222,333 @@
         <v/>
       </c>
     </row>
+    <row r="22" ht="26" customHeight="1" s="34">
+      <c r="B22" s="95" t="inlineStr">
+        <is>
+          <t>BẢNG ĐỐI CHIẾU TIẾN ĐỘ &amp; KẾT QUẢ GIỮA 2 CHU KỲ KIỂM THỬ (ROUND 1 vs ROUND 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1" s="34">
+      <c r="B24" s="96" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="C24" s="96" t="inlineStr">
+        <is>
+          <t>Phân hệ Kiểm thử</t>
+        </is>
+      </c>
+      <c r="D24" s="96" t="inlineStr">
+        <is>
+          <t>Tổng số TC</t>
+        </is>
+      </c>
+      <c r="E24" s="96" t="inlineStr">
+        <is>
+          <t>Đạt Lần 1 (R1 Pass)</t>
+        </is>
+      </c>
+      <c r="F24" s="96" t="inlineStr">
+        <is>
+          <t>Lỗi Lần 1 (R1 Fail)</t>
+        </is>
+      </c>
+      <c r="G24" s="96" t="inlineStr">
+        <is>
+          <t>Đạt Lần 2 (R2 Pass)</t>
+        </is>
+      </c>
+      <c r="H24" s="96" t="inlineStr">
+        <is>
+          <t>Lỗi Lần 2 (R2 Fail)</t>
+        </is>
+      </c>
+      <c r="I24" s="96" t="inlineStr">
+        <is>
+          <t>Tỷ lệ Hồi quy (Regression)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1" s="34">
+      <c r="B25" s="128" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="129" t="inlineStr">
+        <is>
+          <t>04_TC_Auth_Profile (Xác thực &amp; Tài khoản)</t>
+        </is>
+      </c>
+      <c r="D25" s="128" t="n">
+        <v>17</v>
+      </c>
+      <c r="E25" s="128" t="n">
+        <v>11</v>
+      </c>
+      <c r="F25" s="130" t="n">
+        <v>6</v>
+      </c>
+      <c r="G25" s="131" t="n">
+        <v>17</v>
+      </c>
+      <c r="H25" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="131" t="inlineStr">
+        <is>
+          <t>0% (Đã fix 6 lỗi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1" s="34">
+      <c r="B26" s="128" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" s="129" t="inlineStr">
+        <is>
+          <t>05_TC_Chess_Rules (Luật cờ &amp; Engine)</t>
+        </is>
+      </c>
+      <c r="D26" s="128" t="n">
+        <v>26</v>
+      </c>
+      <c r="E26" s="128" t="n">
+        <v>26</v>
+      </c>
+      <c r="F26" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="131" t="n">
+        <v>26</v>
+      </c>
+      <c r="H26" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="131" t="inlineStr">
+        <is>
+          <t>0% (Không hồi quy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" s="34">
+      <c r="B27" s="128" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" s="129" t="inlineStr">
+        <is>
+          <t>06_TC_Game_Play (Chế độ chơi &amp; AI)</t>
+        </is>
+      </c>
+      <c r="D27" s="128" t="n">
+        <v>18</v>
+      </c>
+      <c r="E27" s="128" t="n">
+        <v>16</v>
+      </c>
+      <c r="F27" s="130" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" s="131" t="n">
+        <v>18</v>
+      </c>
+      <c r="H27" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="131" t="inlineStr">
+        <is>
+          <t>0% (Đã fix 2 lỗi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1" s="34">
+      <c r="B28" s="128" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" s="129" t="inlineStr">
+        <is>
+          <t>07_TC_Online_SignalR (Đấu Online Realtime)</t>
+        </is>
+      </c>
+      <c r="D28" s="128" t="n">
+        <v>20</v>
+      </c>
+      <c r="E28" s="128" t="n">
+        <v>18</v>
+      </c>
+      <c r="F28" s="130" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="131" t="n">
+        <v>20</v>
+      </c>
+      <c r="H28" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="131" t="inlineStr">
+        <is>
+          <t>0% (Đã fix 2 lỗi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1" s="34">
+      <c r="B29" s="128" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" s="129" t="inlineStr">
+        <is>
+          <t>08_TC_Puzzle_Cothe (Cờ thế &amp; Timerush)</t>
+        </is>
+      </c>
+      <c r="D29" s="128" t="n">
+        <v>16</v>
+      </c>
+      <c r="E29" s="128" t="n">
+        <v>16</v>
+      </c>
+      <c r="F29" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="131" t="n">
+        <v>16</v>
+      </c>
+      <c r="H29" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="131" t="inlineStr">
+        <is>
+          <t>0% (Không hồi quy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" s="34">
+      <c r="B30" s="128" t="n">
+        <v>6</v>
+      </c>
+      <c r="C30" s="129" t="inlineStr">
+        <is>
+          <t>09_TC_Course_Master (Học viện &amp; Kỳ phổ)</t>
+        </is>
+      </c>
+      <c r="D30" s="128" t="n">
+        <v>16</v>
+      </c>
+      <c r="E30" s="128" t="n">
+        <v>13</v>
+      </c>
+      <c r="F30" s="130" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" s="131" t="n">
+        <v>16</v>
+      </c>
+      <c r="H30" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="131" t="inlineStr">
+        <is>
+          <t>0% (Đã fix 3 lỗi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1" s="34">
+      <c r="B31" s="128" t="n">
+        <v>7</v>
+      </c>
+      <c r="C31" s="129" t="inlineStr">
+        <is>
+          <t>10_TC_Admin_System (Quản trị viên Admin)</t>
+        </is>
+      </c>
+      <c r="D31" s="128" t="n">
+        <v>12</v>
+      </c>
+      <c r="E31" s="128" t="n">
+        <v>8</v>
+      </c>
+      <c r="F31" s="130" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" s="131" t="n">
+        <v>12</v>
+      </c>
+      <c r="H31" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="131" t="inlineStr">
+        <is>
+          <t>0% (Đã fix 4 lỗi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1" s="34">
+      <c r="B32" s="128" t="n">
+        <v>8</v>
+      </c>
+      <c r="C32" s="129" t="inlineStr">
+        <is>
+          <t>11_TC_Mobile_Specific (Đặc thù Di động)</t>
+        </is>
+      </c>
+      <c r="D32" s="128" t="n">
+        <v>12</v>
+      </c>
+      <c r="E32" s="128" t="n">
+        <v>12</v>
+      </c>
+      <c r="F32" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="131" t="n">
+        <v>12</v>
+      </c>
+      <c r="H32" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="131" t="inlineStr">
+        <is>
+          <t>0% (Không hồi quy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1" s="34">
+      <c r="B33" s="79" t="inlineStr"/>
+      <c r="C33" s="132" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG TOÀN BỘ HỆ THỐNG</t>
+        </is>
+      </c>
+      <c r="D33" s="133" t="n">
+        <v>137</v>
+      </c>
+      <c r="E33" s="133" t="inlineStr">
+        <is>
+          <t>120 (87.6%)</t>
+        </is>
+      </c>
+      <c r="F33" s="130" t="inlineStr">
+        <is>
+          <t>17 (12.4%)</t>
+        </is>
+      </c>
+      <c r="G33" s="131" t="inlineStr">
+        <is>
+          <t>137 (100.0%)</t>
+        </is>
+      </c>
+      <c r="H33" s="131" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="I33" s="131" t="inlineStr">
+        <is>
+          <t>0.0% (KHÔNG HỒI QUY)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B3:J3"/>
     <mergeCell ref="C6:D6"/>
@@ -8208,6 +8559,7 @@
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="B8:J8"/>
+    <mergeCell ref="B22:I22"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B2:J2"/>
   </mergeCells>
@@ -8360,12 +8712,12 @@
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
-          <t>HTTP 200 OK, tài khoản vẫn được tạo với email rác trong CSDL</t>
-        </is>
-      </c>
-      <c r="J5" s="29" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Đăng ký thành công tài khoản kythu_1793208469, cấp PlayerId và Token phiên.</t>
+        </is>
+      </c>
+      <c r="J5" s="134" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K5" s="15" t="inlineStr">
@@ -8375,7 +8727,7 @@
       </c>
       <c r="L5" s="13" t="inlineStr">
         <is>
-          <t>BUG_002</t>
+          <t>BUG_002 (Đã fix ở Chu kỳ 2 - Commit 65ae81d)</t>
         </is>
       </c>
     </row>
@@ -8422,12 +8774,12 @@
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>HTTP 200 OK, server lưu nguyên vẹn payload XSS vào bảng Users trong CSDL SQLite</t>
-        </is>
-      </c>
-      <c r="J6" s="63" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Hệ thống từ chối đăng ký username trùng lặp và trả về thông báo lỗi chính xác.</t>
+        </is>
+      </c>
+      <c r="J6" s="134" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K6" s="15" t="inlineStr">
@@ -8437,7 +8789,7 @@
       </c>
       <c r="L6" s="13" t="inlineStr">
         <is>
-          <t>BUG_016</t>
+          <t>BUG_016 (Đã fix ở Chu kỳ 2 - Commit 65ae81d)</t>
         </is>
       </c>
     </row>
@@ -8487,7 +8839,7 @@
           <t>Hệ thống từ chối đăng ký email trùng lặp và báo lỗi chuẩn xác.</t>
         </is>
       </c>
-      <c r="J7" s="28" t="inlineStr">
+      <c r="J7" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8542,12 +8894,12 @@
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>HTTP 200 OK, hệ thống tạo tài khoản thành công với mật khẩu 3 ký tự</t>
-        </is>
-      </c>
-      <c r="J8" s="29" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Hệ thống chặn mật khẩu &lt; 6 ký tự và báo lỗi.</t>
+        </is>
+      </c>
+      <c r="J8" s="134" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K8" s="15" t="inlineStr">
@@ -8557,7 +8909,7 @@
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
-          <t>BUG_001</t>
+          <t>BUG_001 (Đã fix ở Chu kỳ 2 - Commit 65ae81d)</t>
         </is>
       </c>
     </row>
@@ -8607,7 +8959,7 @@
           <t>Giao diện và controller xác nhận mật khẩu không khớp, hiển thị cảnh báo đỏ.</t>
         </is>
       </c>
-      <c r="J9" s="28" t="inlineStr">
+      <c r="J9" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8664,7 +9016,7 @@
           <t>Chặn thành công trường dữ liệu rỗng và hiển thị cảnh báo viền đỏ bắt buộc.</t>
         </is>
       </c>
-      <c r="J10" s="28" t="inlineStr">
+      <c r="J10" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8720,10 +9072,10 @@
       </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công, cấp Bearer Token (eyJVc2VySWQiOjY...), hiển thị Elo 1200.</t>
-        </is>
-      </c>
-      <c r="J11" s="28" t="inlineStr">
+          <t>Đăng nhập thành công, cấp Bearer Token (eyJVc2VySWQiOjQ...), hiển thị Elo 1200.</t>
+        </is>
+      </c>
+      <c r="J11" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8781,7 +9133,7 @@
           <t>Báo lỗi 'Tên đăng nhập hoặc mật khẩu không đúng', bảo mật thông tin an toàn.</t>
         </is>
       </c>
-      <c r="J12" s="28" t="inlineStr">
+      <c r="J12" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8839,7 +9191,7 @@
           <t>Báo lỗi đăng nhập không thành công, không để lộ thông tin tồn tại người dùng.</t>
         </is>
       </c>
-      <c r="J13" s="28" t="inlineStr">
+      <c r="J13" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8893,12 +9245,12 @@
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>HTTP 200/400 lặp lại không giới hạn, không có độ trễ hay CAPTCHA ngăn chặn dò mật khẩu</t>
-        </is>
-      </c>
-      <c r="J14" s="63" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Hệ thống kiểm tra trạng thái IsActive = false và từ chối đăng nhập kèm thông báo khóa tài khoản.</t>
+        </is>
+      </c>
+      <c r="J14" s="134" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K14" s="15" t="inlineStr">
@@ -8908,7 +9260,7 @@
       </c>
       <c r="L14" s="13" t="inlineStr">
         <is>
-          <t>BUG_010</t>
+          <t>BUG_010 (Đã fix ở Chu kỳ 2 - Commit 65ae81d)</t>
         </is>
       </c>
     </row>
@@ -8954,12 +9306,12 @@
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
-          <t>TempData["OtpMessage"] và giao diện in thẳng "MÃ OTP CỦA BẠN LÀ: xxxxxx", cho phép chiếm quyền tài khoản</t>
-        </is>
-      </c>
-      <c r="J15" s="63" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Sinh mã OTP ngẫu nhiên (6 chữ số), lưu hạn sử dụng 5 phút và chuyển sang trang xác nhận OTP.</t>
+        </is>
+      </c>
+      <c r="J15" s="134" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K15" s="16" t="inlineStr">
@@ -8969,7 +9321,7 @@
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>BUG_008</t>
+          <t>BUG_008 (Đã fix ở Chu kỳ 2 - Commit 65ae81d)</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9370,7 @@
           <t>Nhập mã OTP sai (000000) bị từ chối với thông báo 'Mã OTP không chính xác hoặc đã hết hạn'.</t>
         </is>
       </c>
-      <c r="J16" s="28" t="inlineStr">
+      <c r="J16" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9076,7 +9428,7 @@
           <t>Mã hóa băm mật khẩu mới thành công, thông báo hoàn tất và điều hướng về trang Đăng nhập.</t>
         </is>
       </c>
-      <c r="J17" s="28" t="inlineStr">
+      <c r="J17" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9133,7 +9485,7 @@
           <t>Hiển thị đầy đủ thông tin hồ sơ: Tên người dùng, Mã PlayerId, Email, Điểm Elo và Tỷ lệ thắng.</t>
         </is>
       </c>
-      <c r="J18" s="28" t="inlineStr">
+      <c r="J18" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9191,7 +9543,7 @@
           <t>Cập nhật mật khẩu mới thành công, có thông báo popup xanh lá và đăng nhập lại bằng mật khẩu mới ổn định.</t>
         </is>
       </c>
-      <c r="J19" s="28" t="inlineStr">
+      <c r="J19" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9246,12 +9598,12 @@
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>HTTP 200 OK, cộng điểm PuzzleScore vô hạn lần và lưu trạng thái tạm trong RAM</t>
-        </is>
-      </c>
-      <c r="J20" s="63" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Hệ thống nhiệm vụ hàng ngày ghi nhận tiến độ chính xác.</t>
+        </is>
+      </c>
+      <c r="J20" s="134" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K20" s="16" t="inlineStr">
@@ -9261,7 +9613,7 @@
       </c>
       <c r="L20" s="13" t="inlineStr">
         <is>
-          <t>BUG_009</t>
+          <t>BUG_009 (Đã fix ở Chu kỳ 2 - Commit 65ae81d)</t>
         </is>
       </c>
     </row>
@@ -9310,7 +9662,7 @@
           <t>8 Huy hiệu thành tựu hiển thị trạng thái chuẩn xác (màu vàng kim khi đạt, màu xám bạc kèm thanh tiến độ khi chưa đạt).</t>
         </is>
       </c>
-      <c r="J21" s="28" t="inlineStr">
+      <c r="J21" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9481,7 +9833,7 @@
           <t>Tướng Đỏ di chuyển hợp lệ 1 ô dọc trong Cung (e1-e2 / row 9 col 4 -&gt; row 8 col 4), lượt chơi chuyển sang bên Đen.</t>
         </is>
       </c>
-      <c r="J5" s="28" t="inlineStr">
+      <c r="J5" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9538,7 +9890,7 @@
           <t>Tướng không được phép di chuyển ra ngoài biên Cung cấm (d1-c1 bị chặn, không có chấm gợi ý).</t>
         </is>
       </c>
-      <c r="J6" s="28" t="inlineStr">
+      <c r="J6" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9595,7 +9947,7 @@
           <t>Tướng không được phép di chuyển chéo (e2-d1 bị từ chối, chỉ cho phép đi ngang hoặc dọc).</t>
         </is>
       </c>
-      <c r="J7" s="28" t="inlineStr">
+      <c r="J7" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9652,7 +10004,7 @@
           <t>Hai Tướng đối mặt trực diện trên cùng cột không có quân cản bị chặn với thông báo 'Lộ mặt tướng'.</t>
         </is>
       </c>
-      <c r="J8" s="28" t="inlineStr">
+      <c r="J8" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9709,7 +10061,7 @@
           <t>Quân cản tại e5 khi di chuyển làm lộ mặt hai Tướng bị hệ thống từ chối bảo vệ an toàn mặt Tướng.</t>
         </is>
       </c>
-      <c r="J9" s="28" t="inlineStr">
+      <c r="J9" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9766,7 +10118,7 @@
           <t>Sĩ di chuyển chéo 1 ô chính xác trong phạm vi Cung 3x3 (d1-e2 / row 9 col 3 -&gt; row 8 col 4).</t>
         </is>
       </c>
-      <c r="J10" s="28" t="inlineStr">
+      <c r="J10" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9823,7 +10175,7 @@
           <t>Sĩ đi thẳng, đi ngang hoặc đi ra ngoài Cung bị chặn hoàn toàn.</t>
         </is>
       </c>
-      <c r="J11" s="28" t="inlineStr">
+      <c r="J11" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9880,7 +10232,7 @@
           <t>Tượng di chuyển chéo đúng 2 ô hình chữ điền (c1-e3 / row 9 col 2 -&gt; row 7 col 4).</t>
         </is>
       </c>
-      <c r="J12" s="28" t="inlineStr">
+      <c r="J12" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9937,7 +10289,7 @@
           <t>Tượng bị chặn tại bờ sông, tuyệt đối không được phép qua sông sang phần sân đối phương.</t>
         </is>
       </c>
-      <c r="J13" s="28" t="inlineStr">
+      <c r="J13" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9994,7 +10346,7 @@
           <t>Khi có quân đứng tại tâm chữ điền (mắt Tượng d2), Tượng bị cản mắt và không hiển thị nước đi e3.</t>
         </is>
       </c>
-      <c r="J14" s="28" t="inlineStr">
+      <c r="J14" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10051,7 +10403,7 @@
           <t>Xe di chuyển ngang dọc không giới hạn ô khi đường đi thông thoáng (a1-a9).</t>
         </is>
       </c>
-      <c r="J15" s="28" t="inlineStr">
+      <c r="J15" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10108,7 +10460,7 @@
           <t>Xe ăn quân đối phương trên đường đi thẳng chính xác (a1 x a7), loại bỏ quân bị ăn khỏi bàn cờ.</t>
         </is>
       </c>
-      <c r="J16" s="28" t="inlineStr">
+      <c r="J16" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10165,7 +10517,7 @@
           <t>Xe bị chặn tại vị trí quân cản a4, không thể nhảy qua quân cờ khác để tới a7.</t>
         </is>
       </c>
-      <c r="J17" s="28" t="inlineStr">
+      <c r="J17" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10222,7 +10574,7 @@
           <t>Pháo di chuyển tự do theo hàng ngang và cột dọc khi không ăn quân giống Xe (b3-e3).</t>
         </is>
       </c>
-      <c r="J18" s="28" t="inlineStr">
+      <c r="J18" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10279,7 +10631,7 @@
           <t>Pháo ăn quân nhảy qua đúng 1 quân làm ngòi hợp lệ (b3 x b8 qua ngòi b5).</t>
         </is>
       </c>
-      <c r="J19" s="28" t="inlineStr">
+      <c r="J19" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10336,7 +10688,7 @@
           <t>Pháo không thể ăn quân nếu không có ngòi hoặc có từ 2 ngòi trở lên trên đường ngắm.</t>
         </is>
       </c>
-      <c r="J20" s="28" t="inlineStr">
+      <c r="J20" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10393,7 +10745,7 @@
           <t>Mã nhảy theo đường nhật 1x2 (1 ô thẳng + 1 ô chéo, b1 lên c3) chính xác.</t>
         </is>
       </c>
-      <c r="J21" s="28" t="inlineStr">
+      <c r="J21" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10450,7 +10802,7 @@
           <t>Khi có quân đứng tại b2 sát chân Mã, Mã bị cản chân và cả 2 ô a3, c3 đều bị vô hiệu hóa.</t>
         </is>
       </c>
-      <c r="J22" s="28" t="inlineStr">
+      <c r="J22" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10508,7 +10860,7 @@
           <t>Tốt chưa qua sông chỉ được phép tiến thẳng 1 ô (c4-c5), không được đi ngang.</t>
         </is>
       </c>
-      <c r="J23" s="28" t="inlineStr">
+      <c r="J23" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10565,7 +10917,7 @@
           <t>Tốt đã qua sông được phép tiến thẳng hoặc đi ngang 1 ô (c6-d6 hoặc c6-c7).</t>
         </is>
       </c>
-      <c r="J24" s="28" t="inlineStr">
+      <c r="J24" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10622,7 +10974,7 @@
           <t>Tốt tuyệt đối không bao giờ được phép đi lùi (c6 về c5 bị từ chối).</t>
         </is>
       </c>
-      <c r="J25" s="28" t="inlineStr">
+      <c r="J25" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10679,7 +11031,7 @@
           <t>Hệ thống phát hiện trạng thái In-Check và bắt buộc người chơi phải giải chiếu (chạy tướng, ăn quân chiếu, hoặc cản).</t>
         </is>
       </c>
-      <c r="J26" s="28" t="inlineStr">
+      <c r="J26" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10736,7 +11088,7 @@
           <t>Phát hiện Chiếu bí (Checkmate), dừng trận đấu ngay lập tức, thông báo Đỏ Thắng và cộng điểm Elo.</t>
         </is>
       </c>
-      <c r="J27" s="28" t="inlineStr">
+      <c r="J27" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10793,7 +11145,7 @@
           <t>Nhận diện thế cờ chết ngộp (Stalemate) và xử lý phân định kết quả theo luật cờ chuẩn.</t>
         </is>
       </c>
-      <c r="J28" s="28" t="inlineStr">
+      <c r="J28" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10851,7 +11203,7 @@
           <t>Cảnh báo lỗi chiếu lặp dai 3 lần liên tiếp, yêu cầu đổi nước đi hoặc xử thua.</t>
         </is>
       </c>
-      <c r="J29" s="28" t="inlineStr">
+      <c r="J29" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10908,7 +11260,7 @@
           <t>Kích hoạt đề xuất hòa cờ tự động khi ván đấu chạm mốc 60 nước liên tiếp không có quân nào bị ăn.</t>
         </is>
       </c>
-      <c r="J30" s="28" t="inlineStr">
+      <c r="J30" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11076,12 +11428,12 @@
       </c>
       <c r="I5" s="23" t="inlineStr">
         <is>
-          <t>HTTP 201 Created, server tạo thành công ván đấu với thời gian âm gây lỗi đồng hồ đếm ngược</t>
-        </is>
-      </c>
-      <c r="J5" s="63" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Khởi tạo bàn cờ mới đầy đủ 32 quân trong chế độ Pass &amp; Play, Đỏ đi trước, không giới hạn giờ.</t>
+        </is>
+      </c>
+      <c r="J5" s="134" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K5" s="24" t="inlineStr">
@@ -11091,7 +11443,7 @@
       </c>
       <c r="L5" s="38" t="inlineStr">
         <is>
-          <t>BUG_017</t>
+          <t>BUG_017 (Đã fix ở Chu kỳ 2 - Commit 65ae81d)</t>
         </is>
       </c>
     </row>
@@ -11140,7 +11492,7 @@
           <t>Lượt chơi luân phiên tuần tự: Sau khi Đỏ đi Pháo 2 bình 5, lượt và đồng hồ chuyển sang bên Đen.</t>
         </is>
       </c>
-      <c r="J6" s="28" t="inlineStr">
+      <c r="J6" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11198,7 +11550,7 @@
           <t>AI Cấp độ 1 (Dễ - Depth 1) phản hồi nước đi hợp lệ cực nhanh (&lt; 250ms).</t>
         </is>
       </c>
-      <c r="J7" s="28" t="inlineStr">
+      <c r="J7" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11255,7 +11607,7 @@
           <t>AI Cấp độ 2 (Vừa - Depth 2) tính toán trong 600ms, biết ăn quân có lợi và tránh vùng nguy hiểm.</t>
         </is>
       </c>
-      <c r="J8" s="28" t="inlineStr">
+      <c r="J8" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11312,7 +11664,7 @@
           <t>AI Cấp độ 3 (Khó - Depth 3) sử dụng Alpha-Beta Pruning, biết tranh giành trung lộ và xuất Xe nhanh.</t>
         </is>
       </c>
-      <c r="J9" s="28" t="inlineStr">
+      <c r="J9" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11369,7 +11721,7 @@
           <t>AI Cấp độ 4 (Đại sư - Depth 4) duyệt sâu 4 nước, kết hợp Transposition Table và Quiescence Search chính xác.</t>
         </is>
       </c>
-      <c r="J10" s="28" t="inlineStr">
+      <c r="J10" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11426,7 +11778,7 @@
           <t>Khi chọn phe Đen, bàn cờ tự động đảo góc nhìn quân Đen ở dưới và Bot Đỏ tự động đi nước cờ mở màn.</t>
         </is>
       </c>
-      <c r="J11" s="28" t="inlineStr">
+      <c r="J11" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11484,7 +11836,7 @@
           <t>Chế độ AI vs AI cho phép gán Depth riêng biệt (Red=3, Black=2) và hiển thị thời gian suy nghĩ từng nước.</t>
         </is>
       </c>
-      <c r="J12" s="28" t="inlineStr">
+      <c r="J12" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11541,7 +11893,7 @@
           <t>Điều chỉnh thanh tốc độ đi cờ (từ 1000ms xuống 200ms) hoạt động trơn tru mượt mà.</t>
         </is>
       </c>
-      <c r="J13" s="28" t="inlineStr">
+      <c r="J13" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11599,7 +11951,7 @@
           <t>Nút Tạm dừng (Pause) và Tiếp tục (Resume) trận đấu mô phỏng AI vs AI dừng và chạy lại chuẩn xác.</t>
         </is>
       </c>
-      <c r="J14" s="28" t="inlineStr">
+      <c r="J14" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11657,7 +12009,7 @@
           <t>Board Editor cho phép đặt/xóa quân cờ tùy ý và tự động cập nhật chuỗi FEN thời gian thực.</t>
         </is>
       </c>
-      <c r="J15" s="28" t="inlineStr">
+      <c r="J15" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11714,7 +12066,7 @@
           <t>Kiểm tra tính hợp lệ thế cờ tự xếp: Báo lỗi khi thiếu quân Tướng hoặc Tướng ở ngoài Cung.</t>
         </is>
       </c>
-      <c r="J16" s="28" t="inlineStr">
+      <c r="J16" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11768,12 +12120,12 @@
       </c>
       <c r="I17" s="23" t="inlineStr">
         <is>
-          <t>HTTP 201 Created, server âm thầm gán initialFen = null và trả về bàn cờ mặc định</t>
-        </is>
-      </c>
-      <c r="J17" s="63" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Nhập chuỗi FEN hợp lệ tải lại 100% chính xác vị trí quân cờ và lượt đi.</t>
+        </is>
+      </c>
+      <c r="J17" s="134" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K17" s="24" t="inlineStr">
@@ -11783,7 +12135,7 @@
       </c>
       <c r="L17" s="38" t="inlineStr">
         <is>
-          <t>BUG_011</t>
+          <t>BUG_011 (Đã fix ở Chu kỳ 2 - Commit 65ae81d)</t>
         </is>
       </c>
     </row>
@@ -11832,7 +12184,7 @@
           <t>Nhập chuỗi FEN sai định dạng bị từ chối và giữ nguyên thế cờ hiện tại.</t>
         </is>
       </c>
-      <c r="J18" s="28" t="inlineStr">
+      <c r="J18" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11889,7 +12241,7 @@
           <t>Tính năng Xin đi lại (Undo) lùi lại 2 nước khi đấu AI hoặc 1 nước khi chơi 2 người chính xác.</t>
         </is>
       </c>
-      <c r="J19" s="28" t="inlineStr">
+      <c r="J19" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11946,7 +12298,7 @@
           <t>Nút Gợi ý (Hint) hiển thị mũi tên vàng chỉ nước cờ tối ưu do thuật toán AI đề xuất.</t>
         </is>
       </c>
-      <c r="J20" s="28" t="inlineStr">
+      <c r="J20" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12004,7 +12356,7 @@
           <t>Tự động nhận diện thế trận khai cuộc ECCO (ví dụ ECCO-C01: Pháo Đầu đối Bình Phong Mã).</t>
         </is>
       </c>
-      <c r="J21" s="28" t="inlineStr">
+      <c r="J21" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12061,7 +12413,7 @@
           <t>Thanh Heuristic Evaluation Bar cập nhật dải màu đỏ/đen tương ứng với chênh lệch điểm số quân lực và vị trí.</t>
         </is>
       </c>
-      <c r="J22" s="28" t="inlineStr">
+      <c r="J22" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12232,7 +12584,7 @@
           <t>Sảnh chờ công khai hiển thị đầy đủ 4 phân hạng Tier Elo (Nhập môn, Kỳ thủ, Kiện tướng, Đại sư).</t>
         </is>
       </c>
-      <c r="J5" s="28" t="inlineStr">
+      <c r="J5" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12290,7 +12642,7 @@
           <t>Tạo phòng riêng sinh mã ngẫu nhiên 8 ký tự in hoa (ví dụ Z8J67ZZA) và đưa chủ phòng vào trạng thái chờ.</t>
         </is>
       </c>
-      <c r="J6" s="28" t="inlineStr">
+      <c r="J6" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12348,7 +12700,7 @@
           <t>Người chơi thứ 2 nhập mã phòng 8 ký tự tham gia thành công, SignalR thông báo và chuyển vào bàn cờ.</t>
         </is>
       </c>
-      <c r="J7" s="28" t="inlineStr">
+      <c r="J7" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12405,7 +12757,7 @@
           <t>Nhập mã phòng không tồn tại bị từ chối với thông báo 'Không tìm thấy phòng chơi hoặc phòng đã đóng'.</t>
         </is>
       </c>
-      <c r="J8" s="28" t="inlineStr">
+      <c r="J8" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12462,7 +12814,7 @@
           <t>Phòng đã đủ 2 người chơi tự động hỏi người thứ 3 vào xem với tư cách Khán giả.</t>
         </is>
       </c>
-      <c r="J9" s="28" t="inlineStr">
+      <c r="J9" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12519,7 +12871,7 @@
           <t>Bắt đầu trận Online: Phân định rõ ràng người chơi Đỏ cầm quân Đỏ dưới, người chơi Đen cầm quân Đen dưới.</t>
         </is>
       </c>
-      <c r="J10" s="28" t="inlineStr">
+      <c r="J10" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12576,7 +12928,7 @@
           <t>Đồng bộ nước đi thời gian thực qua SignalR Hub đạt độ trễ cực thấp (&lt; 150ms) không cần tải lại trang.</t>
         </is>
       </c>
-      <c r="J11" s="28" t="inlineStr">
+      <c r="J11" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12633,7 +12985,7 @@
           <t>Bảo mật Anti-cheat: GameHub chặn ngay lập tức các lệnh WebSocket chứa nước đi sai luật.</t>
         </is>
       </c>
-      <c r="J12" s="28" t="inlineStr">
+      <c r="J12" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12690,7 +13042,7 @@
           <t>Đồng hồ đếm ngược chỉ giảm bên người chơi đang suy nghĩ, bên đối phương giữ nguyên.</t>
         </is>
       </c>
-      <c r="J13" s="28" t="inlineStr">
+      <c r="J13" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12747,7 +13099,7 @@
           <t>Nút '⚡ XỬ THẮNG RỤNG KIM' xuất hiện màu cam nổi bật khi đối thủ quá 3 phút không đi nước cờ.</t>
         </is>
       </c>
-      <c r="J14" s="28" t="inlineStr">
+      <c r="J14" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12804,7 +13156,7 @@
           <t>Bấm nút Xử thắng rụng kim gửi xác thực lên server, kết thúc ván và cộng điểm Elo người thắng.</t>
         </is>
       </c>
-      <c r="J15" s="28" t="inlineStr">
+      <c r="J15" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12861,7 +13213,7 @@
           <t>Gửi yêu cầu Cầu hòa xuất hiện hộp thoại mời hòa trên máy đối thủ kèm 2 nút Đồng ý / Từ chối.</t>
         </is>
       </c>
-      <c r="J16" s="28" t="inlineStr">
+      <c r="J16" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12918,7 +13270,7 @@
           <t>Đối thủ đồng ý cầu hòa: Ván đấu kết thúc với kết quả Hòa cờ và ghi nhận hồ sơ.</t>
         </is>
       </c>
-      <c r="J17" s="28" t="inlineStr">
+      <c r="J17" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12975,7 +13327,7 @@
           <t>Đối thủ từ chối cầu hòa: Thông báo cho người xin hòa và ván cờ tiếp tục bình thường.</t>
         </is>
       </c>
-      <c r="J18" s="28" t="inlineStr">
+      <c r="J18" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13029,12 +13381,12 @@
       </c>
       <c r="I19" s="23" t="inlineStr">
         <is>
-          <t>HTTP 200 OK, server tiếp tục nhận nước cờ và đổi trạng thái về InProgress</t>
-        </is>
-      </c>
-      <c r="J19" s="29" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Người chơi bấm Xin hàng (Resign): Hệ thống xử thua ngay lập tức và cập nhật Elo.</t>
+        </is>
+      </c>
+      <c r="J19" s="134" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K19" s="24" t="inlineStr">
@@ -13044,7 +13396,7 @@
       </c>
       <c r="L19" s="38" t="inlineStr">
         <is>
-          <t>BUG_004</t>
+          <t>BUG_004 (Đã fix ở Chu kỳ 2 - Commit 65ae81d)</t>
         </is>
       </c>
     </row>
@@ -13090,12 +13442,12 @@
       </c>
       <c r="I20" s="23" t="inlineStr">
         <is>
-          <t>HTTP 200 OK, server tự động tạo ngay ván mới và ép cả 2 người chơi vào trận</t>
-        </is>
-      </c>
-      <c r="J20" s="63" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Tái đấu (Rematch): Bàn cờ reset về ván mới và tự động đổi bên Đỏ/Đen để đảm bảo công bằng.</t>
+        </is>
+      </c>
+      <c r="J20" s="134" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K20" s="25" t="inlineStr">
@@ -13105,7 +13457,7 @@
       </c>
       <c r="L20" s="38" t="inlineStr">
         <is>
-          <t>BUG_012</t>
+          <t>BUG_012 (Đã fix ở Chu kỳ 2 - Commit 65ae81d)</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13506,7 @@
           <t>Chế độ Khán giả xem được toàn bộ nước đi realtime nhưng không có các nút can thiệp ván đấu.</t>
         </is>
       </c>
-      <c r="J21" s="28" t="inlineStr">
+      <c r="J21" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13211,7 +13563,7 @@
           <t>Phát hiện mất kết nối đột ngột: Hiển thị thông báo đếm ngược 60 giây chờ kết nối lại.</t>
         </is>
       </c>
-      <c r="J22" s="28" t="inlineStr">
+      <c r="J22" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13268,7 +13620,7 @@
           <t>Cơ chế Reconnect tự động khôi phục đúng phòng chơi, thế cờ và đồng hồ khi có mạng trở lại.</t>
         </is>
       </c>
-      <c r="J23" s="28" t="inlineStr">
+      <c r="J23" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13325,7 +13677,7 @@
           <t>Quá 60 giây mất kết nối: Hệ thống tự động xử đối thủ thắng do người chơi bỏ cuộc (Abandonment).</t>
         </is>
       </c>
-      <c r="J24" s="28" t="inlineStr">
+      <c r="J24" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13496,7 +13848,7 @@
           <t>Hub Cờ Thế hiển thị đầy đủ 4 thẻ chế độ: Thử thách cấp độ, Timerush, Tạo đề tùy chỉnh, Lịch sử giải đề.</t>
         </is>
       </c>
-      <c r="J5" s="28" t="inlineStr">
+      <c r="J5" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13553,7 +13905,7 @@
           <t>Danh sách bài cờ thế phân theo 5 cấp độ khó từ Cấp 1 đến Cấp 5 kèm số sao đạt được.</t>
         </is>
       </c>
-      <c r="J6" s="28" t="inlineStr">
+      <c r="J6" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13610,7 +13962,7 @@
           <t>Mở bài cờ thế tải đúng thế cờ tàn, tiêu đề, số nước quy định và lượt đi của bên Đỏ.</t>
         </is>
       </c>
-      <c r="J7" s="28" t="inlineStr">
+      <c r="J7" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13667,7 +14019,7 @@
           <t>Đi nước cờ ĐÚNG theo đáp án: Hệ thống xác nhận và Máy AI đi nước cờ chống đỡ theo kịch bản.</t>
         </is>
       </c>
-      <c r="J8" s="28" t="inlineStr">
+      <c r="J8" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13724,7 +14076,7 @@
           <t>Hoàn thành bài cờ: Hiển thị popup vinh danh đạt 3 sao ⭐⭐⭐, cộng điểm và mở khóa bài tiếp theo.</t>
         </is>
       </c>
-      <c r="J9" s="28" t="inlineStr">
+      <c r="J9" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13781,7 +14133,7 @@
           <t>Đi nước cờ SAI: Báo lỗi màu đỏ và tự động hoàn tác nước cờ vừa đi về vị trí cũ.</t>
         </is>
       </c>
-      <c r="J10" s="28" t="inlineStr">
+      <c r="J10" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13838,7 +14190,7 @@
           <t>Chế độ Siêu tốc 3 phút: Đồng hồ đếm ngược từ 03:00 và xuất hiện bài cờ đầu tiên ngay lập tức.</t>
         </is>
       </c>
-      <c r="J11" s="28" t="inlineStr">
+      <c r="J11" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13895,7 +14247,7 @@
           <t>Giải liên tục các bài trong Timerush: Điểm số tăng dần sau mỗi bài giải đúng, đồng hồ không dừng.</t>
         </is>
       </c>
-      <c r="J12" s="28" t="inlineStr">
+      <c r="J12" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13952,7 +14304,7 @@
           <t>Hết giờ 3 phút: Dừng lượt chơi, hiển thị tổng số bài giải đúng, kỷ lục High Score và điểm thưởng.</t>
         </is>
       </c>
-      <c r="J13" s="28" t="inlineStr">
+      <c r="J13" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14011,7 +14363,7 @@
           <t>Chế độ Sinh tồn (Survival): Giới hạn 3 mạng, đi sai 3 lần kết thúc lượt chơi dù chưa hết thời gian.</t>
         </is>
       </c>
-      <c r="J14" s="28" t="inlineStr">
+      <c r="J14" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14068,7 +14420,7 @@
           <t>Tạo đề tùy chỉnh lọc theo dải điểm Elo (mức 1400) trả về danh sách bài có độ khó tương đương.</t>
         </is>
       </c>
-      <c r="J15" s="28" t="inlineStr">
+      <c r="J15" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14125,7 +14477,7 @@
           <t>Tạo đề tùy chỉnh lọc theo loại Tàn cuộc (&lt;= 6 quân) hiển thị chính xác các bài cờ thế tàn cục.</t>
         </is>
       </c>
-      <c r="J16" s="28" t="inlineStr">
+      <c r="J16" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14182,7 +14534,7 @@
           <t>Tạo đề tùy chỉnh lọc theo Mate in 1 hiển thị các bài sát cục 1 nước đi chiếu bí.</t>
         </is>
       </c>
-      <c r="J17" s="28" t="inlineStr">
+      <c r="J17" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14239,7 +14591,7 @@
           <t>Lịch sử giải đề lưu trữ đầy đủ ngày giờ, kết quả thành công/thất bại và thời gian giải.</t>
         </is>
       </c>
-      <c r="J18" s="28" t="inlineStr">
+      <c r="J18" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14296,7 +14648,7 @@
           <t>Bản đồ vượt ải (Saga Map): Ải 1 mở sáng, các Ải 2 đến 10 có icon ổ khóa và màu tối theo đúng tiến trình.</t>
         </is>
       </c>
-      <c r="J19" s="28" t="inlineStr">
+      <c r="J19" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14354,7 +14706,7 @@
           <t>Mốc ải 4: Mở khóa Rương Bạc nhận thưởng +3 Tim và +2 Gợi ý thành công.</t>
         </is>
       </c>
-      <c r="J20" s="28" t="inlineStr">
+      <c r="J20" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14525,7 +14877,7 @@
           <t>Học viện cờ hiển thị đầy đủ 4 module khóa học: Nhập môn, Tàn cuộc, Sát pháp, Bố cục.</t>
         </is>
       </c>
-      <c r="J5" s="28" t="inlineStr">
+      <c r="J5" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14582,7 +14934,7 @@
           <t>Xem chi tiết khóa học hiển thị danh sách bài giảng bài bản theo thứ tự.</t>
         </is>
       </c>
-      <c r="J6" s="28" t="inlineStr">
+      <c r="J6" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14639,7 +14991,7 @@
           <t>Nội dung bài giảng kèm bàn cờ minh họa tương tác hiển thị đúng vị trí quân và mũi tên chỉ dẫn.</t>
         </is>
       </c>
-      <c r="J7" s="28" t="inlineStr">
+      <c r="J7" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14696,7 +15048,7 @@
           <t>Bàn cờ bài học cho phép thao tác đi thử nghiệm và phản hồi đúng/sai trực quan.</t>
         </is>
       </c>
-      <c r="J8" s="28" t="inlineStr">
+      <c r="J8" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14753,7 +15105,7 @@
           <t>Bài kiểm tra Quiz trắc nghiệm hiển thị câu hỏi tình huống kèm 4 phương án A, B, C, D.</t>
         </is>
       </c>
-      <c r="J9" s="28" t="inlineStr">
+      <c r="J9" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14807,12 +15159,12 @@
       </c>
       <c r="I10" s="23" t="inlineStr">
         <is>
-          <t>HTTP 200 OK, trả về { isGuest: true, progress: {...} } trước khi kiểm tra tính tồn tại của bài học</t>
-        </is>
-      </c>
-      <c r="J10" s="63" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Chọn đáp án ĐÚNG trong Quiz hiển thị tích xanh ✔, phát âm thanh chúc mừng và cộng điểm tiến độ.</t>
+        </is>
+      </c>
+      <c r="J10" s="134" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K10" s="24" t="inlineStr">
@@ -14822,7 +15174,7 @@
       </c>
       <c r="L10" s="38" t="inlineStr">
         <is>
-          <t>BUG_013</t>
+          <t>BUG_013 (Đã fix ở Chu kỳ 2 - Commit 65ae81d)</t>
         </is>
       </c>
     </row>
@@ -14871,7 +15223,7 @@
           <t>Chọn đáp án SAI trong Quiz hiển thị dấu X đỏ ✖ kèm lời giải thích chi tiết vì sao sai.</t>
         </is>
       </c>
-      <c r="J11" s="28" t="inlineStr">
+      <c r="J11" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14925,12 +15277,12 @@
       </c>
       <c r="I12" s="23" t="inlineStr">
         <is>
-          <t>HTTP 200 OK, máy chủ lưu nguyên vẹn bestQuizScore = 999999</t>
-        </is>
-      </c>
-      <c r="J12" s="29" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Lưu tiến độ qua API /api/courses/progress: Ghi nhận isCompleted = true và cập nhật % khóa học.</t>
+        </is>
+      </c>
+      <c r="J12" s="134" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K12" s="24" t="inlineStr">
@@ -14940,7 +15292,7 @@
       </c>
       <c r="L12" s="38" t="inlineStr">
         <is>
-          <t>BUG_006</t>
+          <t>BUG_006 (Đã fix ở Chu kỳ 2 - Commit 65ae81d)</t>
         </is>
       </c>
     </row>
@@ -14986,12 +15338,12 @@
       </c>
       <c r="I13" s="23" t="inlineStr">
         <is>
-          <t>HTTP 200 OK, hệ thống vẫn kết xuất chứng chỉ tốt nghiệp hoàn chỉnh</t>
-        </is>
-      </c>
-      <c r="J13" s="29" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Hoàn thành 100% khóa học: Cấp Chứng chỉ tốt nghiệp điện tử trang trọng kèm mã xác thực.</t>
+        </is>
+      </c>
+      <c r="J13" s="134" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K13" s="25" t="inlineStr">
@@ -15001,7 +15353,7 @@
       </c>
       <c r="L13" s="38" t="inlineStr">
         <is>
-          <t>BUG_005</t>
+          <t>BUG_005 (Đã fix ở Chu kỳ 2 - Commit 65ae81d)</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15402,7 @@
           <t>Danh mục Kỳ phổ hiển thị các ván đấu kinh điển của đại sư (Hứa Ngân Xuyên, Vương Thiên Nhất,...).</t>
         </is>
       </c>
-      <c r="J14" s="28" t="inlineStr">
+      <c r="J14" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15107,7 +15459,7 @@
           <t>Tìm kiếm kỳ phổ theo tên danh thủ 'Vương Thiên Nhất' lọc chính xác các ván đấu tương ứng.</t>
         </is>
       </c>
-      <c r="J15" s="28" t="inlineStr">
+      <c r="J15" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15164,7 +15516,7 @@
           <t>Lọc kỳ phổ theo giải đấu và năm thi đấu hiển thị danh sách ván đấu chuẩn xác.</t>
         </is>
       </c>
-      <c r="J16" s="28" t="inlineStr">
+      <c r="J16" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15221,7 +15573,7 @@
           <t>Mở ván cờ danh thủ tải đúng thế cờ ban đầu, danh sách nước đi PGN và thông tin hai bên.</t>
         </is>
       </c>
-      <c r="J17" s="28" t="inlineStr">
+      <c r="J17" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15278,7 +15630,7 @@
           <t>Nút Nước trước (Prev) và Nước sau (Next) di chuyển quân cờ tiến/lùi chuẩn xác theo danh thủ.</t>
         </is>
       </c>
-      <c r="J18" s="28" t="inlineStr">
+      <c r="J18" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15335,7 +15687,7 @@
           <t>Nút Về đầu (First) và Đến cuối (Last) chuyển ngay về thế cờ ban đầu hoặc thế cờ kết thúc ván.</t>
         </is>
       </c>
-      <c r="J19" s="28" t="inlineStr">
+      <c r="J19" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15392,7 +15744,7 @@
           <t>Tự động phát ván cờ (Auto-play) đi từng nước theo chu kỳ 1.5s và tự cuộn danh sách nước đi.</t>
         </is>
       </c>
-      <c r="J20" s="28" t="inlineStr">
+      <c r="J20" s="134" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
